--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7236557F-447A-41B7-B0F1-A63B864D2E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A97AA16A-3EC8-4C6C-A7E1-FA3757259D14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A97AA16A-3EC8-4C6C-A7E1-FA3757259D14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CFD9E8C2-9929-4B59-B84C-F8BB640943FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="120">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -129,7 +129,7 @@
     <t>T001</t>
   </si>
   <si>
-    <t>Milton /keynes Thunder</t>
+    <t>Milton keynes Thunder</t>
   </si>
   <si>
     <t>MK Thunder</t>
@@ -178,6 +178,21 @@
   </si>
   <si>
     <t>Romford</t>
+  </si>
+  <si>
+    <t>T004</t>
+  </si>
+  <si>
+    <t>Chelmsford Warriors</t>
+  </si>
+  <si>
+    <t>Chelmsford</t>
+  </si>
+  <si>
+    <t>chelmsford.png</t>
+  </si>
+  <si>
+    <t>Riverside Leisure Centre</t>
   </si>
   <si>
     <t>Player ID</t>
@@ -285,7 +300,13 @@
     <t>G002</t>
   </si>
   <si>
-    <t xml:space="preserve">	Sapphire Ice and Leisure Centre</t>
+    <t>G003</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>League</t>
   </si>
   <si>
     <t>Player Game Stats – one row per player per game</t>
@@ -906,15 +927,29 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+    <row r="7" spans="1:8">
+      <c r="A7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
+      <c r="H7" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="8" spans="1:8" ht="15">
       <c r="A8" s="2"/>
@@ -2889,39 +2924,39 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C4" s="2">
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>35</v>
@@ -2931,16 +2966,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C5" s="2">
         <v>97</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>35</v>
@@ -2950,37 +2985,37 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C6" s="2">
         <v>74</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>35</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C7" s="2">
         <v>29</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>35</v>
@@ -4781,48 +4816,48 @@
     <row r="2" spans="1:13"/>
     <row r="3" spans="1:13" ht="33">
       <c r="A3" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B4" s="8">
         <v>46264</v>
@@ -4834,10 +4869,10 @@
         <v>36</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -4850,28 +4885,28 @@
         <v>40</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B5" s="8">
         <v>46270</v>
       </c>
       <c r="C5" s="7">
-        <v>0.76041666666666696</v>
+        <v>0.76041666666666663</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -4881,20 +4916,32 @@
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="2"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="8">
+        <v>46278</v>
+      </c>
+      <c r="C6" s="7">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>89</v>
+      </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="3" t="str">
@@ -4902,8 +4949,12 @@
         <v/>
       </c>
       <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
+      <c r="K6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>85</v>
+      </c>
       <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13">
@@ -8436,7 +8487,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="9" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -8450,34 +8501,34 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -17477,7 +17528,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="9" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -17492,37 +17543,37 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -21914,7 +21965,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="9" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -21928,45 +21979,45 @@
     </row>
     <row r="2" spans="1:13">
       <c r="L2" s="1" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="L3" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M3">
         <f>COUNT(Games!$A$4:$A$200)</f>
@@ -22015,7 +22066,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="M4">
         <f>SUM(Games!$G$4:$G$200)</f>
@@ -22064,7 +22115,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="M5">
         <f>SUM(Games!$H$4:$H$200)</f>
@@ -22113,7 +22164,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="M6">
         <f>COUNTIF(Games!$I$4:$I$200,"W")</f>
@@ -22162,7 +22213,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="M7">
         <f>COUNTIF(Games!$I$4:$I$200,"L")</f>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CFD9E8C2-9929-4B59-B84C-F8BB640943FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE479F6A-7E35-42DD-BB79-2A44C0E4247A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="3" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -189,7 +189,7 @@
     <t>Chelmsford</t>
   </si>
   <si>
-    <t>chelmsford.png</t>
+    <t>Chelmsford.png</t>
   </si>
   <si>
     <t>Riverside Leisure Centre</t>
@@ -481,11 +481,11 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="15" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -827,7 +827,7 @@
       <c r="E1" s="9"/>
       <c r="F1" s="9"/>
       <c r="G1" s="9"/>
-      <c r="H1" s="6"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="3" spans="1:8" ht="33">
       <c r="A3" s="1" t="s">
@@ -4859,10 +4859,10 @@
       <c r="A4" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="7">
         <v>46264</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="6">
         <v>0.71875</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -4893,10 +4893,10 @@
       <c r="A5" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="7">
         <v>46270</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
         <v>0.76041666666666663</v>
       </c>
       <c r="D5" s="2" t="s">
@@ -4927,10 +4927,10 @@
       <c r="A6" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="7">
         <v>46278</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="6">
         <v>0.77083333333333337</v>
       </c>
       <c r="D6" s="2" t="s">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE479F6A-7E35-42DD-BB79-2A44C0E4247A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{352F7E50-08A7-4185-B403-B21CB6A5DAB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="3" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -261,7 +261,7 @@
     <t>Opponent ID</t>
   </si>
   <si>
-    <t xml:space="preserve">H/A </t>
+    <t>H/A</t>
   </si>
   <si>
     <t>Competition</t>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ABC1F2E-E04B-410D-835C-BA3FD3EF8A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B08FA6F-2EC7-4A50-8396-6334F0083A84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34785" yWindow="3585" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="182">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -171,9 +171,6 @@
   </si>
   <si>
     <t>Romford Buccaneers</t>
-  </si>
-  <si>
-    <t>Buccaneers</t>
   </si>
   <si>
     <t>romford.png</t>
@@ -308,9 +305,6 @@
     <t>G003</t>
   </si>
   <si>
-    <t>H</t>
-  </si>
-  <si>
     <t>League</t>
   </si>
   <si>
@@ -427,6 +421,174 @@
   <si>
     <t>Away</t>
   </si>
+  <si>
+    <t>T006</t>
+  </si>
+  <si>
+    <t>T007</t>
+  </si>
+  <si>
+    <t>T008</t>
+  </si>
+  <si>
+    <t>T009</t>
+  </si>
+  <si>
+    <t>T010</t>
+  </si>
+  <si>
+    <t>T011</t>
+  </si>
+  <si>
+    <t>T012</t>
+  </si>
+  <si>
+    <t>T013</t>
+  </si>
+  <si>
+    <t>T014</t>
+  </si>
+  <si>
+    <t>T015</t>
+  </si>
+  <si>
+    <t>Guildford Phoenix</t>
+  </si>
+  <si>
+    <t>Guildford</t>
+  </si>
+  <si>
+    <t>guildford.png</t>
+  </si>
+  <si>
+    <t>Guildford Spectrum</t>
+  </si>
+  <si>
+    <t>Peterborough Phantoms 2</t>
+  </si>
+  <si>
+    <t>Peterborough</t>
+  </si>
+  <si>
+    <t>Peterborough.png</t>
+  </si>
+  <si>
+    <t>Planet Ice Peterborough</t>
+  </si>
+  <si>
+    <t>Haringey Huskies</t>
+  </si>
+  <si>
+    <t>Cardiff Canucks</t>
+  </si>
+  <si>
+    <t>Oxford Stars</t>
+  </si>
+  <si>
+    <t>Bristol Pitbulls 2</t>
+  </si>
+  <si>
+    <t>Slough Spitfires</t>
+  </si>
+  <si>
+    <t>Solent Junior Devils</t>
+  </si>
+  <si>
+    <t>Lee Valley Lions</t>
+  </si>
+  <si>
+    <t>Haringey</t>
+  </si>
+  <si>
+    <t>Cardiff</t>
+  </si>
+  <si>
+    <t>Oxford</t>
+  </si>
+  <si>
+    <t>Bristol</t>
+  </si>
+  <si>
+    <t>Slough</t>
+  </si>
+  <si>
+    <t>Solent</t>
+  </si>
+  <si>
+    <t>haringey.png</t>
+  </si>
+  <si>
+    <t>Alexandra Palace Ice Rink</t>
+  </si>
+  <si>
+    <t>London</t>
+  </si>
+  <si>
+    <t>https://thundericehockey.co.uk/</t>
+  </si>
+  <si>
+    <t>cardiff.png</t>
+  </si>
+  <si>
+    <t>Carfiff</t>
+  </si>
+  <si>
+    <t>Vindico Arena</t>
+  </si>
+  <si>
+    <t>oxford.png</t>
+  </si>
+  <si>
+    <t>Oxford Ice Rink</t>
+  </si>
+  <si>
+    <t>bristol.png</t>
+  </si>
+  <si>
+    <t>Planet Ice Bristol</t>
+  </si>
+  <si>
+    <t>slough.png</t>
+  </si>
+  <si>
+    <t>Slough Ice Arena</t>
+  </si>
+  <si>
+    <t>Solent.png</t>
+  </si>
+  <si>
+    <t>Planet Ice Gosport</t>
+  </si>
+  <si>
+    <t>Gosport</t>
+  </si>
+  <si>
+    <t>lee.png</t>
+  </si>
+  <si>
+    <t>Lee Valley</t>
+  </si>
+  <si>
+    <t>Lee Valley Ice Centre</t>
+  </si>
+  <si>
+    <t>Basingstoke Bison 2</t>
+  </si>
+  <si>
+    <t>Basingstoke</t>
+  </si>
+  <si>
+    <t>basingstoke.png</t>
+  </si>
+  <si>
+    <t>Planet Ice Basingstoke</t>
+  </si>
+  <si>
+    <t>G005</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
 </sst>
 </file>
 
@@ -436,7 +598,7 @@
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -451,6 +613,12 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF0B1F26"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -498,10 +666,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -518,8 +687,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -838,12 +1009,12 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="8.5" customWidth="1"/>
-    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.25">
@@ -903,7 +1074,9 @@
       <c r="F4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="2"/>
+      <c r="G4" s="10" t="s">
+        <v>160</v>
+      </c>
       <c r="H4" s="2" t="s">
         <v>35</v>
       </c>
@@ -940,16 +1113,16 @@
         <v>42</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
@@ -958,22 +1131,22 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
@@ -982,22 +1155,22 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
@@ -1005,104 +1178,244 @@
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>137</v>
+      </c>
       <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="H9" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+      <c r="A10" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>141</v>
+      </c>
       <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
+      <c r="A11" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>159</v>
+      </c>
       <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+      <c r="H11" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+      <c r="A12" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>152</v>
+      </c>
       <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
+      <c r="H12" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+      <c r="A13" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>153</v>
+      </c>
       <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+      <c r="H13" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
+      <c r="A14" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>154</v>
+      </c>
       <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="H14" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+      <c r="A15" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>155</v>
+      </c>
       <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
+      <c r="H15" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
+      <c r="A16" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>172</v>
+      </c>
       <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
+      <c r="H16" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
+      <c r="A17" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>159</v>
+      </c>
       <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
+      <c r="H17" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
+      <c r="A18" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>177</v>
+      </c>
       <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
+      <c r="H18" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="2"/>
@@ -2936,6 +3249,9 @@
       <formula1>"Forward,Defence,Netminder"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="G4" r:id="rId1" xr:uid="{D7BA5F28-8504-47F7-A426-9C3C42E6D228}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2967,39 +3283,39 @@
     </row>
     <row r="3" spans="1:7" ht="30">
       <c r="A3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="C4" s="2">
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>35</v>
@@ -3009,16 +3325,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="C5" s="2">
         <v>97</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>35</v>
@@ -3028,37 +3344,37 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="C6" s="2">
         <v>74</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>35</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="C7" s="2">
         <v>29</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>35</v>
@@ -4859,48 +5175,48 @@
     <row r="2" spans="1:13"/>
     <row r="3" spans="1:13" ht="30">
       <c r="A3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="M3" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" s="7">
         <v>46264</v>
@@ -4912,10 +5228,10 @@
         <v>36</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -4928,13 +5244,13 @@
         <v>40</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B5" s="7">
         <v>46270</v>
@@ -4946,10 +5262,10 @@
         <v>41</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -4959,16 +5275,16 @@
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B6" s="7">
         <v>46278</v>
@@ -4977,13 +5293,13 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>88</v>
+        <v>181</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -4993,31 +5309,31 @@
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B7" s="7">
         <v>46284</v>
       </c>
       <c r="C7" s="6">
-        <v>0.79166666666666663</v>
+        <v>0.77083333333333337</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -5027,20 +5343,32 @@
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="2"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="A8" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B8" s="7">
+        <v>46285</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="3" t="str">
@@ -5048,8 +5376,12 @@
         <v/>
       </c>
       <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
+      <c r="K8" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13">
@@ -8428,7 +8760,7 @@
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
       <c r="I196" s="3" t="str">
-        <f t="shared" ref="I196:I227" si="6">IF(OR(G196="",H196=""),"",IF(G196&gt;H196,"W",IF(G196&lt;H196,"L","T")))</f>
+        <f t="shared" ref="I196:I200" si="6">IF(OR(G196="",H196=""),"",IF(G196&gt;H196,"W",IF(G196&lt;H196,"L","T")))</f>
         <v/>
       </c>
       <c r="J196" s="2"/>
@@ -8546,7 +8878,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
       <c r="A1" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -8560,34 +8892,34 @@
     </row>
     <row r="3" spans="1:10" ht="30">
       <c r="A3" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="J3" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -16665,7 +16997,7 @@
       <c r="E452" s="2"/>
       <c r="F452" s="2"/>
       <c r="G452" s="3" t="str">
-        <f t="shared" ref="G452:G515" si="7">IF(AND(E452="",F452=""),"",SUM(E452:F452))</f>
+        <f t="shared" ref="G452:G500" si="7">IF(AND(E452="",F452=""),"",SUM(E452:F452))</f>
         <v/>
       </c>
       <c r="H452" s="2"/>
@@ -17587,7 +17919,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20.25">
       <c r="A1" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -17602,37 +17934,37 @@
     </row>
     <row r="3" spans="1:11" ht="30">
       <c r="A3" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -21870,11 +22202,11 @@
       <c r="E196" s="2"/>
       <c r="F196" s="2"/>
       <c r="G196" s="3" t="str">
-        <f t="shared" ref="G196:G227" si="12">IF(E196="","",E196-F196)</f>
+        <f t="shared" ref="G196:G200" si="12">IF(E196="","",E196-F196)</f>
         <v/>
       </c>
       <c r="H196" s="5" t="str">
-        <f t="shared" ref="H196:H227" si="13">IF(OR(E196="",E196=0),"",G196/E196)</f>
+        <f t="shared" ref="H196:H200" si="13">IF(OR(E196="",E196=0),"",G196/E196)</f>
         <v/>
       </c>
       <c r="I196" s="2"/>
@@ -22024,7 +22356,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
       <c r="A1" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -22038,45 +22370,45 @@
     </row>
     <row r="2" spans="1:13" ht="30">
       <c r="L2" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="45">
       <c r="A3" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="I3" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="L3" t="s">
         <v>113</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="L3" t="s">
-        <v>115</v>
       </c>
       <c r="M3">
         <f>COUNT(Games!$A$4:$A$200)</f>
@@ -22125,7 +22457,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M4">
         <f>SUM(Games!$G$4:$G$200)</f>
@@ -22174,7 +22506,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M5">
         <f>SUM(Games!$H$4:$H$200)</f>
@@ -22223,7 +22555,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M6">
         <f>COUNTIF(Games!$I$4:$I$200,"W")</f>
@@ -22272,7 +22604,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M7">
         <f>COUNTIF(Games!$I$4:$I$200,"L")</f>
@@ -26173,7 +26505,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <f t="shared" ref="H100:H131" si="3">IF(A100="","",F100+G100)</f>
+        <f t="shared" ref="H100:H103" si="3">IF(A100="","",F100+G100)</f>
         <v/>
       </c>
       <c r="I100" t="str">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B08FA6F-2EC7-4A50-8396-6334F0083A84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E589E4B-9348-4849-87F0-800E2BB459CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34785" yWindow="3585" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="185">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -589,6 +589,15 @@
   <si>
     <t>Home</t>
   </si>
+  <si>
+    <t>G006</t>
+  </si>
+  <si>
+    <t>G007</t>
+  </si>
+  <si>
+    <t>Planet ice Milton keynes</t>
+  </si>
 </sst>
 </file>
 
@@ -684,10 +693,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -910,14 +919,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
     </row>
     <row r="3" spans="1:6" ht="30">
       <c r="A3" s="1" t="s">
@@ -1018,18 +1027,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
       <c r="H1" s="8"/>
     </row>
-    <row r="3" spans="1:8" ht="30">
+    <row r="3" spans="1:8" ht="15">
       <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
@@ -1074,7 +1083,7 @@
       <c r="F4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="9" t="s">
         <v>160</v>
       </c>
       <c r="H4" s="2" t="s">
@@ -3271,15 +3280,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
     </row>
     <row r="3" spans="1:7" ht="30">
       <c r="A3" s="1" t="s">
@@ -5156,21 +5165,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
     </row>
     <row r="2" spans="1:13"/>
     <row r="3" spans="1:13" ht="30">
@@ -5256,7 +5265,7 @@
         <v>46270</v>
       </c>
       <c r="C5" s="6">
-        <v>0.76041666666666663</v>
+        <v>0.71875</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>41</v>
@@ -5309,7 +5318,7 @@
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>84</v>
@@ -5324,7 +5333,7 @@
         <v>46284</v>
       </c>
       <c r="C7" s="6">
-        <v>0.77083333333333337</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>118</v>
@@ -5358,7 +5367,7 @@
         <v>46285</v>
       </c>
       <c r="C8" s="6">
-        <v>0.83333333333333304</v>
+        <v>0.77083333333333337</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>126</v>
@@ -5377,7 +5386,7 @@
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2" t="s">
-        <v>139</v>
+        <v>33</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>84</v>
@@ -5385,12 +5394,24 @@
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="2"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B9" s="7">
+        <v>46291</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.78125</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="3" t="str">
@@ -5398,17 +5419,33 @@
         <v/>
       </c>
       <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
+      <c r="K9" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="M9" s="2"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="2"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+      <c r="A10" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B10" s="7">
+        <v>46298</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="3" t="str">
@@ -5416,7 +5453,9 @@
         <v/>
       </c>
       <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
+      <c r="K10" s="2" t="s">
+        <v>184</v>
+      </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
     </row>
@@ -8877,18 +8916,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
     </row>
     <row r="3" spans="1:10" ht="30">
       <c r="A3" s="1" t="s">
@@ -17918,19 +17957,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
     </row>
     <row r="3" spans="1:11" ht="30">
       <c r="A3" s="1" t="s">
@@ -22355,18 +22394,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
     </row>
     <row r="2" spans="1:13" ht="30">
       <c r="L2" s="1" t="s">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E589E4B-9348-4849-87F0-800E2BB459CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C66FE3A5-F7F9-4B4C-9CB2-6F767407D6D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="184">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -419,9 +419,6 @@
     <t>G004</t>
   </si>
   <si>
-    <t>Away</t>
-  </si>
-  <si>
     <t>T006</t>
   </si>
   <si>
@@ -587,9 +584,6 @@
     <t>G005</t>
   </si>
   <si>
-    <t>Home</t>
-  </si>
-  <si>
     <t>G006</t>
   </si>
   <si>
@@ -597,6 +591,9 @@
   </si>
   <si>
     <t>Planet ice Milton keynes</t>
+  </si>
+  <si>
+    <t>H</t>
   </si>
 </sst>
 </file>
@@ -1084,7 +1081,7 @@
         <v>34</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>35</v>
@@ -1188,22 +1185,22 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2" t="s">
@@ -1212,22 +1209,22 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>143</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
@@ -1236,22 +1233,22 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>159</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
@@ -1260,22 +1257,22 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>163</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2" t="s">
@@ -1284,22 +1281,22 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="F13" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2" t="s">
@@ -1308,22 +1305,22 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="F14" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2" t="s">
@@ -1332,22 +1329,22 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>169</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2" t="s">
@@ -1356,22 +1353,22 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2" t="s">
@@ -1380,22 +1377,22 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>175</v>
-      </c>
       <c r="F17" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2" t="s">
@@ -1404,22 +1401,22 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="F18" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2" t="s">
@@ -5237,7 +5234,7 @@
         <v>36</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>83</v>
@@ -5271,7 +5268,7 @@
         <v>41</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>83</v>
@@ -5305,7 +5302,7 @@
         <v>46</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
@@ -5339,7 +5336,7 @@
         <v>118</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>87</v>
@@ -5361,7 +5358,7 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B8" s="7">
         <v>46285</v>
@@ -5370,10 +5367,10 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
@@ -5395,7 +5392,7 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B9" s="7">
         <v>46291</v>
@@ -5404,10 +5401,10 @@
         <v>0.78125</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
@@ -5420,7 +5417,7 @@
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>84</v>
@@ -5429,7 +5426,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B10" s="7">
         <v>46298</v>
@@ -5438,10 +5435,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
@@ -5454,7 +5451,7 @@
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
@@ -8883,10 +8880,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation type="list" sqref="E4:E200" xr:uid="{00000000-0002-0000-0200-000000000000}">
-      <formula1>"Home,Away"</formula1>
-    </dataValidation>
+  <dataValidations count="2">
     <dataValidation type="list" sqref="F4:F200" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Pre-season,League,Cup,Playoff"</formula1>
     </dataValidation>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/mark_ward_rockwellautomation_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CF5C09A-9023-44CE-AE8A-B4FCB4DB3AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4998DDD0-F0E7-4E2A-84E8-E9E9967E6E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="127">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -171,6 +171,9 @@
   </si>
   <si>
     <t>Romford Buccaneers</t>
+  </si>
+  <si>
+    <t>Buccaneers</t>
   </si>
   <si>
     <t>romford.png</t>
@@ -305,6 +308,9 @@
     <t>G003</t>
   </si>
   <si>
+    <t>H</t>
+  </si>
+  <si>
     <t>League</t>
   </si>
   <si>
@@ -401,52 +407,7 @@
     <t>T005</t>
   </si>
   <si>
-    <t>Invicta Mustangs</t>
-  </si>
-  <si>
-    <t>Invicta</t>
-  </si>
-  <si>
-    <t>invicta.png</t>
-  </si>
-  <si>
-    <t>Planet Ice Gillingham</t>
-  </si>
-  <si>
-    <t>Gillingham</t>
-  </si>
-  <si>
-    <t>G004</t>
-  </si>
-  <si>
-    <t>T006</t>
-  </si>
-  <si>
-    <t>T007</t>
-  </si>
-  <si>
-    <t>T008</t>
-  </si>
-  <si>
-    <t>T009</t>
-  </si>
-  <si>
-    <t>T010</t>
-  </si>
-  <si>
-    <t>T011</t>
-  </si>
-  <si>
-    <t>T012</t>
-  </si>
-  <si>
-    <t>T013</t>
-  </si>
-  <si>
-    <t>T014</t>
-  </si>
-  <si>
-    <t>T015</t>
+    <t>guilford.png</t>
   </si>
   <si>
     <t>Guildford Phoenix</t>
@@ -455,145 +416,13 @@
     <t>Guildford</t>
   </si>
   <si>
-    <t>guildford.png</t>
-  </si>
-  <si>
     <t>Guildford Spectrum</t>
   </si>
   <si>
-    <t>Peterborough Phantoms 2</t>
+    <t>G004</t>
   </si>
   <si>
-    <t>Peterborough</t>
-  </si>
-  <si>
-    <t>Peterborough.png</t>
-  </si>
-  <si>
-    <t>Planet Ice Peterborough</t>
-  </si>
-  <si>
-    <t>Haringey Huskies</t>
-  </si>
-  <si>
-    <t>Cardiff Canucks</t>
-  </si>
-  <si>
-    <t>Oxford Stars</t>
-  </si>
-  <si>
-    <t>Bristol Pitbulls 2</t>
-  </si>
-  <si>
-    <t>Slough Spitfires</t>
-  </si>
-  <si>
-    <t>Solent Junior Devils</t>
-  </si>
-  <si>
-    <t>Lee Valley Lions</t>
-  </si>
-  <si>
-    <t>Haringey</t>
-  </si>
-  <si>
-    <t>Cardiff</t>
-  </si>
-  <si>
-    <t>Oxford</t>
-  </si>
-  <si>
-    <t>Bristol</t>
-  </si>
-  <si>
-    <t>Slough</t>
-  </si>
-  <si>
-    <t>Solent</t>
-  </si>
-  <si>
-    <t>haringey.png</t>
-  </si>
-  <si>
-    <t>Alexandra Palace Ice Rink</t>
-  </si>
-  <si>
-    <t>London</t>
-  </si>
-  <si>
-    <t>https://thundericehockey.co.uk/</t>
-  </si>
-  <si>
-    <t>cardiff.png</t>
-  </si>
-  <si>
-    <t>Carfiff</t>
-  </si>
-  <si>
-    <t>Vindico Arena</t>
-  </si>
-  <si>
-    <t>oxford.png</t>
-  </si>
-  <si>
-    <t>Oxford Ice Rink</t>
-  </si>
-  <si>
-    <t>bristol.png</t>
-  </si>
-  <si>
-    <t>Planet Ice Bristol</t>
-  </si>
-  <si>
-    <t>slough.png</t>
-  </si>
-  <si>
-    <t>Slough Ice Arena</t>
-  </si>
-  <si>
-    <t>Solent.png</t>
-  </si>
-  <si>
-    <t>Planet Ice Gosport</t>
-  </si>
-  <si>
-    <t>Gosport</t>
-  </si>
-  <si>
-    <t>lee.png</t>
-  </si>
-  <si>
-    <t>Lee Valley</t>
-  </si>
-  <si>
-    <t>Lee Valley Ice Centre</t>
-  </si>
-  <si>
-    <t>Basingstoke Bison 2</t>
-  </si>
-  <si>
-    <t>Basingstoke</t>
-  </si>
-  <si>
-    <t>basingstoke.png</t>
-  </si>
-  <si>
-    <t>Planet Ice Basingstoke</t>
-  </si>
-  <si>
-    <t>G005</t>
-  </si>
-  <si>
-    <t>G006</t>
-  </si>
-  <si>
-    <t>G007</t>
-  </si>
-  <si>
-    <t>Planet ice Milton keynes</t>
-  </si>
-  <si>
-    <t>H</t>
+    <t>Home</t>
   </si>
 </sst>
 </file>
@@ -604,7 +433,7 @@
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -619,12 +448,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF0B1F26"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -672,11 +495,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -690,13 +512,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -916,14 +736,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
     </row>
     <row r="3" spans="1:6" ht="30">
       <c r="A3" s="1" t="s">
@@ -1015,27 +835,27 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="8.5" customWidth="1"/>
-    <col min="2" max="2" width="22.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
       <c r="H1" s="8"/>
     </row>
-    <row r="3" spans="1:8" ht="15">
+    <row r="3" spans="1:8" ht="30">
       <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
@@ -1080,9 +900,7 @@
       <c r="F4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="9" t="s">
-        <v>159</v>
-      </c>
+      <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
         <v>35</v>
       </c>
@@ -1119,16 +937,16 @@
         <v>42</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
@@ -1137,22 +955,22 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
@@ -1161,19 +979,19 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>121</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>123</v>
@@ -1184,244 +1002,104 @@
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>136</v>
-      </c>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>140</v>
-      </c>
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="H10" s="2"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>158</v>
-      </c>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>151</v>
-      </c>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>152</v>
-      </c>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-      <c r="H13" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>153</v>
-      </c>
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="H14" s="2"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>154</v>
-      </c>
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-      <c r="H15" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="H15" s="2"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>171</v>
-      </c>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="H16" s="2"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>158</v>
-      </c>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
       <c r="G17" s="2"/>
-      <c r="H17" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="H17" s="2"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>176</v>
-      </c>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-      <c r="H18" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="H18" s="2"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="2"/>
@@ -3255,9 +2933,6 @@
       <formula1>"Forward,Defence,Netminder"</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="G4" r:id="rId1" xr:uid="{D7BA5F28-8504-47F7-A426-9C3C42E6D228}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3277,51 +2952,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="3" spans="1:7" ht="30">
       <c r="A3" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C4" s="2">
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>35</v>
@@ -3331,16 +3006,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C5" s="2">
         <v>97</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>35</v>
@@ -3350,37 +3025,37 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C6" s="2">
         <v>74</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>35</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C7" s="2">
         <v>29</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>35</v>
@@ -5162,67 +4837,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
     </row>
     <row r="2" spans="1:13"/>
     <row r="3" spans="1:13" ht="30">
       <c r="A3" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" s="7">
         <v>46264</v>
@@ -5234,10 +4909,10 @@
         <v>36</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -5250,28 +4925,28 @@
         <v>40</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B5" s="7">
         <v>46270</v>
       </c>
       <c r="C5" s="6">
-        <v>0.71875</v>
+        <v>0.76041666666666663</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -5281,16 +4956,16 @@
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B6" s="7">
         <v>46278</v>
@@ -5299,13 +4974,13 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>183</v>
+        <v>88</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -5315,31 +4990,31 @@
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B7" s="7">
         <v>46284</v>
       </c>
       <c r="C7" s="6">
-        <v>0.79166666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -5349,32 +5024,20 @@
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B8" s="7">
-        <v>46285</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>87</v>
-      </c>
+      <c r="A8" s="2"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="3" t="str">
@@ -5382,33 +5045,17 @@
         <v/>
       </c>
       <c r="J8" s="2"/>
-      <c r="K8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>84</v>
-      </c>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="B9" s="7">
-        <v>46291</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0.78125</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>87</v>
-      </c>
+      <c r="A9" s="2"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="3" t="str">
@@ -5416,33 +5063,17 @@
         <v/>
       </c>
       <c r="J9" s="2"/>
-      <c r="K9" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>84</v>
-      </c>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
       <c r="M9" s="2"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B10" s="7">
-        <v>46298</v>
-      </c>
-      <c r="C10" s="6">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>87</v>
-      </c>
+      <c r="A10" s="2"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="3" t="str">
@@ -5450,9 +5081,7 @@
         <v/>
       </c>
       <c r="J10" s="2"/>
-      <c r="K10" s="2" t="s">
-        <v>182</v>
-      </c>
+      <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
     </row>
@@ -8796,7 +8425,7 @@
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
       <c r="I196" s="3" t="str">
-        <f t="shared" ref="I196:I200" si="6">IF(OR(G196="",H196=""),"",IF(G196&gt;H196,"W",IF(G196&lt;H196,"L","T")))</f>
+        <f t="shared" ref="I196:I227" si="6">IF(OR(G196="",H196=""),"",IF(G196&gt;H196,"W",IF(G196&lt;H196,"L","T")))</f>
         <v/>
       </c>
       <c r="J196" s="2"/>
@@ -8880,7 +8509,10 @@
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
+    <dataValidation type="list" sqref="E4:E200" xr:uid="{00000000-0002-0000-0200-000000000000}">
+      <formula1>"Home,Away"</formula1>
+    </dataValidation>
     <dataValidation type="list" sqref="F4:F200" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Pre-season,League,Cup,Playoff"</formula1>
     </dataValidation>
@@ -8910,49 +8542,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
-      <c r="A1" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
+      <c r="A1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
     </row>
     <row r="3" spans="1:10" ht="30">
       <c r="A3" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -17030,7 +16662,7 @@
       <c r="E452" s="2"/>
       <c r="F452" s="2"/>
       <c r="G452" s="3" t="str">
-        <f t="shared" ref="G452:G500" si="7">IF(AND(E452="",F452=""),"",SUM(E452:F452))</f>
+        <f t="shared" ref="G452:G515" si="7">IF(AND(E452="",F452=""),"",SUM(E452:F452))</f>
         <v/>
       </c>
       <c r="H452" s="2"/>
@@ -17951,53 +17583,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20.25">
-      <c r="A1" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
+      <c r="A1" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="30">
       <c r="A3" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -22235,11 +21867,11 @@
       <c r="E196" s="2"/>
       <c r="F196" s="2"/>
       <c r="G196" s="3" t="str">
-        <f t="shared" ref="G196:G200" si="12">IF(E196="","",E196-F196)</f>
+        <f t="shared" ref="G196:G227" si="12">IF(E196="","",E196-F196)</f>
         <v/>
       </c>
       <c r="H196" s="5" t="str">
-        <f t="shared" ref="H196:H200" si="13">IF(OR(E196="",E196=0),"",G196/E196)</f>
+        <f t="shared" ref="H196:H227" si="13">IF(OR(E196="",E196=0),"",G196/E196)</f>
         <v/>
       </c>
       <c r="I196" s="2"/>
@@ -22388,60 +22020,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
-      <c r="A1" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
+      <c r="A1" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
     </row>
     <row r="2" spans="1:13" ht="30">
       <c r="L2" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="45">
       <c r="A3" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M3">
         <f>COUNT(Games!$A$4:$A$200)</f>
@@ -22490,7 +22122,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="M4">
         <f>SUM(Games!$G$4:$G$200)</f>
@@ -22539,7 +22171,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="M5">
         <f>SUM(Games!$H$4:$H$200)</f>
@@ -22588,7 +22220,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="M6">
         <f>COUNTIF(Games!$I$4:$I$200,"W")</f>
@@ -22637,7 +22269,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M7">
         <f>COUNTIF(Games!$I$4:$I$200,"L")</f>
@@ -26538,7 +26170,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <f t="shared" ref="H100:H103" si="3">IF(A100="","",F100+G100)</f>
+        <f t="shared" ref="H100:H131" si="3">IF(A100="","",F100+G100)</f>
         <v/>
       </c>
       <c r="I100" t="str">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4998DDD0-F0E7-4E2A-84E8-E9E9967E6E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D8CC27-C0A0-46D9-8AE3-5A707B200651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -407,9 +407,6 @@
     <t>T005</t>
   </si>
   <si>
-    <t>guilford.png</t>
-  </si>
-  <si>
     <t>Guildford Phoenix</t>
   </si>
   <si>
@@ -423,6 +420,9 @@
   </si>
   <si>
     <t>Home</t>
+  </si>
+  <si>
+    <t>guildford.png</t>
   </si>
 </sst>
 </file>
@@ -982,19 +982,19 @@
         <v>120</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
@@ -4999,7 +4999,7 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B7" s="7">
         <v>46284</v>
@@ -5011,7 +5011,7 @@
         <v>120</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>89</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>85</v>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D8CC27-C0A0-46D9-8AE3-5A707B200651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C15C1F21-875F-4AD7-BD0D-D2902D980155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="180">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -171,9 +171,6 @@
   </si>
   <si>
     <t>Romford Buccaneers</t>
-  </si>
-  <si>
-    <t>Buccaneers</t>
   </si>
   <si>
     <t>romford.png</t>
@@ -419,10 +416,172 @@
     <t>G004</t>
   </si>
   <si>
-    <t>Home</t>
+    <t>guildford.png</t>
   </si>
   <si>
-    <t>guildford.png</t>
+    <t>https://thundericehockey.co.uk/</t>
+  </si>
+  <si>
+    <t>Invicta Mustangs</t>
+  </si>
+  <si>
+    <t>Invicta</t>
+  </si>
+  <si>
+    <t>invicta.png</t>
+  </si>
+  <si>
+    <t>Planet Ice Gillingham</t>
+  </si>
+  <si>
+    <t>Gillingham</t>
+  </si>
+  <si>
+    <t>T006</t>
+  </si>
+  <si>
+    <t>T007</t>
+  </si>
+  <si>
+    <t>Peterborough Phantoms 2</t>
+  </si>
+  <si>
+    <t>Peterborough</t>
+  </si>
+  <si>
+    <t>Peterborough.png</t>
+  </si>
+  <si>
+    <t>Planet Ice Peterborough</t>
+  </si>
+  <si>
+    <t>T008</t>
+  </si>
+  <si>
+    <t>Haringey Huskies</t>
+  </si>
+  <si>
+    <t>Haringey</t>
+  </si>
+  <si>
+    <t>haringey.png</t>
+  </si>
+  <si>
+    <t>Alexandra Palace Ice Rink</t>
+  </si>
+  <si>
+    <t>London</t>
+  </si>
+  <si>
+    <t>T009</t>
+  </si>
+  <si>
+    <t>Cardiff Canucks</t>
+  </si>
+  <si>
+    <t>Carfiff</t>
+  </si>
+  <si>
+    <t>cardiff.png</t>
+  </si>
+  <si>
+    <t>Vindico Arena</t>
+  </si>
+  <si>
+    <t>Cardiff</t>
+  </si>
+  <si>
+    <t>T010</t>
+  </si>
+  <si>
+    <t>Oxford Stars</t>
+  </si>
+  <si>
+    <t>Oxford</t>
+  </si>
+  <si>
+    <t>oxford.png</t>
+  </si>
+  <si>
+    <t>Oxford Ice Rink</t>
+  </si>
+  <si>
+    <t>T011</t>
+  </si>
+  <si>
+    <t>Bristol Pitbulls 2</t>
+  </si>
+  <si>
+    <t>Bristol</t>
+  </si>
+  <si>
+    <t>bristol.png</t>
+  </si>
+  <si>
+    <t>Planet Ice Bristol</t>
+  </si>
+  <si>
+    <t>T012</t>
+  </si>
+  <si>
+    <t>Slough Spitfires</t>
+  </si>
+  <si>
+    <t>Slough</t>
+  </si>
+  <si>
+    <t>slough.png</t>
+  </si>
+  <si>
+    <t>Slough Ice Arena</t>
+  </si>
+  <si>
+    <t>T013</t>
+  </si>
+  <si>
+    <t>Solent Junior Devils</t>
+  </si>
+  <si>
+    <t>Solent</t>
+  </si>
+  <si>
+    <t>Solent.png</t>
+  </si>
+  <si>
+    <t>Planet Ice Gosport</t>
+  </si>
+  <si>
+    <t>Gosport</t>
+  </si>
+  <si>
+    <t>T014</t>
+  </si>
+  <si>
+    <t>Lee Valley Lions</t>
+  </si>
+  <si>
+    <t>Lee Valley</t>
+  </si>
+  <si>
+    <t>lee.png</t>
+  </si>
+  <si>
+    <t>Lee Valley Ice Centre</t>
+  </si>
+  <si>
+    <t>T015</t>
+  </si>
+  <si>
+    <t>Basingstoke Bison 2</t>
+  </si>
+  <si>
+    <t>Basingstoke</t>
+  </si>
+  <si>
+    <t>basingstoke.png</t>
+  </si>
+  <si>
+    <t>Planet Ice Basingstoke</t>
   </si>
 </sst>
 </file>
@@ -840,7 +999,7 @@
     <col min="4" max="4" width="15.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.25">
@@ -900,7 +1059,9 @@
       <c r="F4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="2"/>
+      <c r="G4" s="2" t="s">
+        <v>125</v>
+      </c>
       <c r="H4" s="2" t="s">
         <v>35</v>
       </c>
@@ -937,16 +1098,16 @@
         <v>42</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
@@ -955,22 +1116,22 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
@@ -979,22 +1140,22 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
@@ -1002,104 +1163,244 @@
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>121</v>
+      </c>
       <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="H9" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+      <c r="A10" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
+      <c r="A11" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>142</v>
+      </c>
       <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+      <c r="H11" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+      <c r="A12" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
+      <c r="H12" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+      <c r="A13" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>151</v>
+      </c>
       <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+      <c r="H13" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
+      <c r="A14" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>156</v>
+      </c>
       <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="H14" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+      <c r="A15" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>161</v>
+      </c>
       <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
+      <c r="H15" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
+      <c r="A16" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>169</v>
+      </c>
       <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
+      <c r="H16" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
+      <c r="A17" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>142</v>
+      </c>
       <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
+      <c r="H17" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
+      <c r="A18" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>177</v>
+      </c>
       <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
+      <c r="H18" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="2"/>
@@ -2964,39 +3265,39 @@
     </row>
     <row r="3" spans="1:7" ht="30">
       <c r="A3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="C4" s="2">
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>35</v>
@@ -3006,16 +3307,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="C5" s="2">
         <v>97</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>35</v>
@@ -3025,37 +3326,37 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="C6" s="2">
         <v>74</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>35</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="C7" s="2">
         <v>29</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>35</v>
@@ -4856,48 +5157,48 @@
     <row r="2" spans="1:13"/>
     <row r="3" spans="1:13" ht="30">
       <c r="A3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="M3" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" s="7">
         <v>46264</v>
@@ -4909,10 +5210,10 @@
         <v>36</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -4925,13 +5226,13 @@
         <v>40</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B5" s="7">
         <v>46270</v>
@@ -4943,10 +5244,10 @@
         <v>41</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -4956,16 +5257,16 @@
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B6" s="7">
         <v>46278</v>
@@ -4974,13 +5275,13 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -4990,44 +5291,41 @@
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B7" s="7">
         <v>46284</v>
       </c>
       <c r="C7" s="6">
-        <v>0.8125</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="I7" s="3"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M7" s="2"/>
     </row>
@@ -8425,7 +8723,7 @@
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
       <c r="I196" s="3" t="str">
-        <f t="shared" ref="I196:I227" si="6">IF(OR(G196="",H196=""),"",IF(G196&gt;H196,"W",IF(G196&lt;H196,"L","T")))</f>
+        <f t="shared" ref="I196:I200" si="6">IF(OR(G196="",H196=""),"",IF(G196&gt;H196,"W",IF(G196&lt;H196,"L","T")))</f>
         <v/>
       </c>
       <c r="J196" s="2"/>
@@ -8510,7 +8808,7 @@
     <mergeCell ref="A1:M1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" sqref="E4:E200" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" sqref="E4:E6 E8:E200" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Home,Away"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="F4:F200" xr:uid="{00000000-0002-0000-0200-000001000000}">
@@ -8543,7 +8841,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
       <c r="A1" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -8557,34 +8855,34 @@
     </row>
     <row r="3" spans="1:10" ht="30">
       <c r="A3" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="J3" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -16662,7 +16960,7 @@
       <c r="E452" s="2"/>
       <c r="F452" s="2"/>
       <c r="G452" s="3" t="str">
-        <f t="shared" ref="G452:G515" si="7">IF(AND(E452="",F452=""),"",SUM(E452:F452))</f>
+        <f t="shared" ref="G452:G500" si="7">IF(AND(E452="",F452=""),"",SUM(E452:F452))</f>
         <v/>
       </c>
       <c r="H452" s="2"/>
@@ -17584,7 +17882,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20.25">
       <c r="A1" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -17599,37 +17897,37 @@
     </row>
     <row r="3" spans="1:11" ht="30">
       <c r="A3" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -21867,11 +22165,11 @@
       <c r="E196" s="2"/>
       <c r="F196" s="2"/>
       <c r="G196" s="3" t="str">
-        <f t="shared" ref="G196:G227" si="12">IF(E196="","",E196-F196)</f>
+        <f t="shared" ref="G196:G200" si="12">IF(E196="","",E196-F196)</f>
         <v/>
       </c>
       <c r="H196" s="5" t="str">
-        <f t="shared" ref="H196:H227" si="13">IF(OR(E196="",E196=0),"",G196/E196)</f>
+        <f t="shared" ref="H196:H200" si="13">IF(OR(E196="",E196=0),"",G196/E196)</f>
         <v/>
       </c>
       <c r="I196" s="2"/>
@@ -22021,7 +22319,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
       <c r="A1" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -22035,45 +22333,45 @@
     </row>
     <row r="2" spans="1:13" ht="30">
       <c r="L2" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="45">
       <c r="A3" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="L3" t="s">
         <v>114</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="L3" t="s">
-        <v>115</v>
       </c>
       <c r="M3">
         <f>COUNT(Games!$A$4:$A$200)</f>
@@ -22122,7 +22420,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M4">
         <f>SUM(Games!$G$4:$G$200)</f>
@@ -22171,7 +22469,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M5">
         <f>SUM(Games!$H$4:$H$200)</f>
@@ -22220,7 +22518,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M6">
         <f>COUNTIF(Games!$I$4:$I$200,"W")</f>
@@ -22269,7 +22567,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M7">
         <f>COUNTIF(Games!$I$4:$I$200,"L")</f>
@@ -26170,7 +26468,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <f t="shared" ref="H100:H131" si="3">IF(A100="","",F100+G100)</f>
+        <f t="shared" ref="H100:H103" si="3">IF(A100="","",F100+G100)</f>
         <v/>
       </c>
       <c r="I100" t="str">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C15C1F21-875F-4AD7-BD0D-D2902D980155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D1058F0-716E-4F73-A8B0-77499C57E4DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="181">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -583,6 +583,9 @@
   <si>
     <t>Planet Ice Basingstoke</t>
   </si>
+  <si>
+    <t>G005</t>
+  </si>
 </sst>
 </file>
 
@@ -1014,7 +1017,7 @@
       <c r="G1" s="9"/>
       <c r="H1" s="8"/>
     </row>
-    <row r="3" spans="1:8" ht="30">
+    <row r="3" spans="1:8" ht="15">
       <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
@@ -5291,7 +5294,7 @@
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>84</v>
@@ -5330,12 +5333,24 @@
       <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="2"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="A8" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B8" s="7">
+        <v>46285</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="3" t="str">
@@ -5343,8 +5358,12 @@
         <v/>
       </c>
       <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
+      <c r="K8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13">
@@ -8808,7 +8827,7 @@
     <mergeCell ref="A1:M1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" sqref="E4:E6 E8:E200" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" sqref="E4:E6 E9:E200" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Home,Away"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="F4:F200" xr:uid="{00000000-0002-0000-0200-000001000000}">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D1058F0-716E-4F73-A8B0-77499C57E4DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49874F30-50EF-4048-8836-89A3E1841C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="183">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -586,6 +586,12 @@
   <si>
     <t>G005</t>
   </si>
+  <si>
+    <t>G006</t>
+  </si>
+  <si>
+    <t>G007</t>
+  </si>
 </sst>
 </file>
 
@@ -5340,7 +5346,7 @@
         <v>46285</v>
       </c>
       <c r="C8" s="6">
-        <v>0.79166666666666663</v>
+        <v>0.77083333333333337</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>131</v>
@@ -5367,12 +5373,24 @@
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="2"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B9" s="7">
+        <v>46291</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.78125</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="3" t="str">
@@ -5380,17 +5398,33 @@
         <v/>
       </c>
       <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
+      <c r="K9" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="M9" s="2"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="2"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+      <c r="A10" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B10" s="7">
+        <v>46298</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="3" t="str">
@@ -5398,8 +5432,12 @@
         <v/>
       </c>
       <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
+      <c r="K10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="M10" s="2"/>
     </row>
     <row r="11" spans="1:13">
@@ -8826,10 +8864,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation type="list" sqref="E4:E6 E9:E200" xr:uid="{00000000-0002-0000-0200-000000000000}">
-      <formula1>"Home,Away"</formula1>
-    </dataValidation>
+  <dataValidations count="2">
     <dataValidation type="list" sqref="F4:F200" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Pre-season,League,Cup,Playoff"</formula1>
     </dataValidation>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49874F30-50EF-4048-8836-89A3E1841C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB06B03-BF7A-4745-A4D3-8E79EA40F35C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="187">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -592,6 +592,18 @@
   <si>
     <t>G007</t>
   </si>
+  <si>
+    <t>G008</t>
+  </si>
+  <si>
+    <t>Planet Ice Milton Keynes</t>
+  </si>
+  <si>
+    <t>G009</t>
+  </si>
+  <si>
+    <t>G010</t>
+  </si>
 </sst>
 </file>
 
@@ -5300,7 +5312,7 @@
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
-        <v>33</v>
+        <v>184</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>84</v>
@@ -5365,7 +5377,7 @@
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2" t="s">
-        <v>33</v>
+        <v>184</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>84</v>
@@ -5414,7 +5426,7 @@
         <v>46298</v>
       </c>
       <c r="C10" s="6">
-        <v>0.79166666666666663</v>
+        <v>0.77083333333333337</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>170</v>
@@ -5433,7 +5445,7 @@
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2" t="s">
-        <v>33</v>
+        <v>184</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>84</v>
@@ -5441,12 +5453,24 @@
       <c r="M10" s="2"/>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="2"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
+      <c r="A11" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B11" s="7">
+        <v>46306</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="3" t="str">
@@ -5454,17 +5478,33 @@
         <v/>
       </c>
       <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
+      <c r="K11" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="M11" s="2"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="2"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+      <c r="A12" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B12" s="7">
+        <v>46312</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="3" t="str">
@@ -5472,17 +5512,33 @@
         <v/>
       </c>
       <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
+      <c r="K12" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="M12" s="2"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="2"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+      <c r="A13" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B13" s="7">
+        <v>46320</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="3" t="str">
@@ -5490,8 +5546,12 @@
         <v/>
       </c>
       <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
+      <c r="K13" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="M13" s="2"/>
     </row>
     <row r="14" spans="1:13">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB06B03-BF7A-4745-A4D3-8E79EA40F35C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8E363C-0C7F-4A01-9ED0-0C0552B40694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -545,9 +545,6 @@
     <t>Solent</t>
   </si>
   <si>
-    <t>Solent.png</t>
-  </si>
-  <si>
     <t>Planet Ice Gosport</t>
   </si>
   <si>
@@ -603,6 +600,9 @@
   </si>
   <si>
     <t>G010</t>
+  </si>
+  <si>
+    <t>solent.png</t>
   </si>
 </sst>
 </file>
@@ -1362,13 +1362,13 @@
         <v>166</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>169</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2" t="s">
@@ -1377,19 +1377,19 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>142</v>
@@ -1401,22 +1401,22 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="F18" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2" t="s">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>84</v>
@@ -5352,7 +5352,7 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B8" s="7">
         <v>46285</v>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>84</v>
@@ -5386,7 +5386,7 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B9" s="7">
         <v>46291</v>
@@ -5420,7 +5420,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B10" s="7">
         <v>46298</v>
@@ -5429,7 +5429,7 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>87</v>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>84</v>
@@ -5454,7 +5454,7 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B11" s="7">
         <v>46306</v>
@@ -5463,7 +5463,7 @@
         <v>0.83333333333333304</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>87</v>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>84</v>
@@ -5488,7 +5488,7 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B12" s="7">
         <v>46312</v>
@@ -5497,7 +5497,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>82</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>84</v>
@@ -5522,7 +5522,7 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B13" s="7">
         <v>46320</v>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>84</v>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8E363C-0C7F-4A01-9ED0-0C0552B40694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2513FB0-1F72-49FB-AC4C-2298586801B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="196">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -604,6 +604,33 @@
   <si>
     <t>solent.png</t>
   </si>
+  <si>
+    <t>G011</t>
+  </si>
+  <si>
+    <t>G012</t>
+  </si>
+  <si>
+    <t>G013</t>
+  </si>
+  <si>
+    <t>G014</t>
+  </si>
+  <si>
+    <t>G015</t>
+  </si>
+  <si>
+    <t>G016</t>
+  </si>
+  <si>
+    <t>G017</t>
+  </si>
+  <si>
+    <t>G018</t>
+  </si>
+  <si>
+    <t>G019</t>
+  </si>
 </sst>
 </file>
 
@@ -5555,12 +5582,24 @@
       <c r="M13" s="2"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="2"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
+      <c r="A14" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B14" s="7">
+        <v>46327</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="3" t="str">
@@ -5568,17 +5607,33 @@
         <v/>
       </c>
       <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
+      <c r="K14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="M14" s="2"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="2"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+      <c r="A15" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B15" s="7">
+        <v>46334</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="3" t="str">
@@ -5586,17 +5641,33 @@
         <v/>
       </c>
       <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
+      <c r="K15" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="M15" s="2"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="2"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
+      <c r="A16" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B16" s="7">
+        <v>46340</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="3" t="str">
@@ -5604,17 +5675,33 @@
         <v/>
       </c>
       <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
+      <c r="K16" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="M16" s="2"/>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="2"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
+      <c r="A17" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B17" s="7">
+        <v>46341</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="3" t="str">
@@ -5622,17 +5709,33 @@
         <v/>
       </c>
       <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
+      <c r="K17" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="M17" s="2"/>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="2"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
+      <c r="A18" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B18" s="7">
+        <v>46354</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="3" t="str">
@@ -5640,17 +5743,33 @@
         <v/>
       </c>
       <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
+      <c r="K18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="M18" s="2"/>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="2"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
+      <c r="A19" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B19" s="7">
+        <v>46355</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="3" t="str">
@@ -5658,17 +5777,33 @@
         <v/>
       </c>
       <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
+      <c r="K19" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="M19" s="2"/>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="2"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
+      <c r="A20" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B20" s="7">
+        <v>46368</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.8125</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="3" t="str">
@@ -5676,17 +5811,33 @@
         <v/>
       </c>
       <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
+      <c r="K20" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="M20" s="2"/>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="2"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
+      <c r="A21" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B21" s="7">
+        <v>46369</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="3" t="str">
@@ -5694,17 +5845,33 @@
         <v/>
       </c>
       <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
+      <c r="K21" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="M21" s="2"/>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="2"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
+      <c r="A22" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B22" s="7">
+        <v>46376</v>
+      </c>
+      <c r="C22" s="6">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="3" t="str">
@@ -5712,8 +5879,12 @@
         <v/>
       </c>
       <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
+      <c r="K22" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="M22" s="2"/>
     </row>
     <row r="23" spans="1:13">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2513FB0-1F72-49FB-AC4C-2298586801B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{019826CC-BC6C-4E6D-A8E8-E7A0E957F6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="203">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -631,6 +631,27 @@
   <si>
     <t>G019</t>
   </si>
+  <si>
+    <t>G020</t>
+  </si>
+  <si>
+    <t>G021</t>
+  </si>
+  <si>
+    <t>G022</t>
+  </si>
+  <si>
+    <t>G023</t>
+  </si>
+  <si>
+    <t>G024</t>
+  </si>
+  <si>
+    <t>G025</t>
+  </si>
+  <si>
+    <t>G026</t>
+  </si>
 </sst>
 </file>
 
@@ -5846,7 +5867,7 @@
       </c>
       <c r="J21" s="2"/>
       <c r="K21" s="2" t="s">
-        <v>141</v>
+        <v>183</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>84</v>
@@ -5880,7 +5901,7 @@
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>84</v>
@@ -5888,12 +5909,24 @@
       <c r="M22" s="2"/>
     </row>
     <row r="23" spans="1:13">
-      <c r="A23" s="2"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
+      <c r="A23" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B23" s="7">
+        <v>46397</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="3" t="str">
@@ -5901,17 +5934,33 @@
         <v/>
       </c>
       <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
+      <c r="K23" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="M23" s="2"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="2"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
+      <c r="A24" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B24" s="7">
+        <v>46417</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="3" t="str">
@@ -5919,17 +5968,33 @@
         <v/>
       </c>
       <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
+      <c r="K24" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="M24" s="2"/>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="2"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
+      <c r="A25" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B25" s="7">
+        <v>46425</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="3" t="str">
@@ -5937,17 +6002,33 @@
         <v/>
       </c>
       <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
+      <c r="K25" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="M25" s="2"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="2"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
+      <c r="A26" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B26" s="7">
+        <v>46446</v>
+      </c>
+      <c r="C26" s="6">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="3" t="str">
@@ -5955,17 +6036,33 @@
         <v/>
       </c>
       <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
+      <c r="K26" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="M26" s="2"/>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" s="2"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
+      <c r="A27" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B27" s="7">
+        <v>46452</v>
+      </c>
+      <c r="C27" s="6">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="3" t="str">
@@ -5973,17 +6070,33 @@
         <v/>
       </c>
       <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
+      <c r="K27" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="M27" s="2"/>
     </row>
     <row r="28" spans="1:13">
-      <c r="A28" s="2"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
+      <c r="A28" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B28" s="7">
+        <v>46459</v>
+      </c>
+      <c r="C28" s="6">
+        <v>0.78125</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="3" t="str">
@@ -5991,17 +6104,33 @@
         <v/>
       </c>
       <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
+      <c r="K28" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="M28" s="2"/>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="2"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
+      <c r="A29" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B29" s="7">
+        <v>46467</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="3" t="str">
@@ -6009,7 +6138,9 @@
         <v/>
       </c>
       <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
+      <c r="K29" s="2" t="s">
+        <v>163</v>
+      </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
     </row>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{019826CC-BC6C-4E6D-A8E8-E7A0E957F6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156F467B-DB3C-421D-BAB7-DD15C1633979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="208">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -652,6 +652,21 @@
   <si>
     <t>G026</t>
   </si>
+  <si>
+    <t>P005</t>
+  </si>
+  <si>
+    <t>Charlie Russell</t>
+  </si>
+  <si>
+    <t>P006</t>
+  </si>
+  <si>
+    <t>Lewis Smith</t>
+  </si>
+  <si>
+    <t>Peters.png</t>
+  </si>
 </sst>
 </file>
 
@@ -707,7 +722,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -722,11 +737,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -735,14 +765,22 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="15" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -964,14 +1002,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
     </row>
     <row r="3" spans="1:6" ht="30">
       <c r="A3" s="1" t="s">
@@ -1072,402 +1110,402 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="8"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="6"/>
     </row>
     <row r="3" spans="1:8" ht="15">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="7" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="s">
+      <c r="G5" s="8"/>
+      <c r="H5" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="s">
+      <c r="G6" s="8"/>
+      <c r="H6" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="s">
+      <c r="G7" s="8"/>
+      <c r="H7" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="s">
+      <c r="G8" s="8"/>
+      <c r="H8" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="s">
+      <c r="G9" s="8"/>
+      <c r="H9" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="s">
+      <c r="G10" s="8"/>
+      <c r="H10" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="s">
+      <c r="G11" s="8"/>
+      <c r="H11" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2" t="s">
+      <c r="G12" s="8"/>
+      <c r="H12" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="s">
+      <c r="G13" s="8"/>
+      <c r="H13" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="s">
+      <c r="G14" s="8"/>
+      <c r="H14" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2" t="s">
+      <c r="G15" s="8"/>
+      <c r="H15" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2" t="s">
+      <c r="G16" s="8"/>
+      <c r="H16" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2" t="s">
+      <c r="G17" s="8"/>
+      <c r="H17" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2" t="s">
+      <c r="G18" s="8"/>
+      <c r="H18" s="8" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3314,142 +3352,164 @@
   <cols>
     <col min="1" max="1" width="8.5" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="6.75" customWidth="1"/>
+    <col min="3" max="3" width="8.875" customWidth="1"/>
     <col min="4" max="4" width="10.625" customWidth="1"/>
     <col min="5" max="5" width="6.125" customWidth="1"/>
-    <col min="6" max="6" width="9.75" customWidth="1"/>
-    <col min="7" max="7" width="6.25" customWidth="1"/>
+    <col min="6" max="6" width="11.625" customWidth="1"/>
+    <col min="7" max="7" width="9.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="3" spans="1:7" ht="30">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="7" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="8">
         <v>9</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="F4" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="G4" s="8"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="8">
         <v>97</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="8">
         <v>74</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2" t="s">
+      <c r="F6" s="8"/>
+      <c r="G6" s="8" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="8">
         <v>29</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+      <c r="A8" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="C8" s="8">
+        <v>12</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
+      <c r="A9" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="C9" s="8">
+        <v>13</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2"/>
@@ -5207,942 +5267,944 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
     </row>
     <row r="2" spans="1:13"/>
     <row r="3" spans="1:13" ht="30">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" s="7" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="9">
         <v>46264</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="10">
         <v>0.71875</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="3" t="str">
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="11" t="str">
         <f t="shared" ref="I4:I35" si="0">IF(OR(G4="",H4=""),"",IF(G4&gt;H4,"W",IF(G4&lt;H4,"L","T")))</f>
         <v/>
       </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2" t="s">
+      <c r="J4" s="8"/>
+      <c r="K4" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="M4" s="2"/>
+      <c r="M4" s="8"/>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="9">
         <v>46270</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="10">
         <v>0.76041666666666663</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="3" t="str">
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2" t="s">
+      <c r="J5" s="8"/>
+      <c r="K5" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="L5" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="M5" s="2"/>
+      <c r="M5" s="8"/>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="9">
         <v>46278</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="10">
         <v>0.77083333333333337</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="3" t="str">
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2" t="s">
+      <c r="J6" s="8"/>
+      <c r="K6" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="L6" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="M6" s="2"/>
+      <c r="M6" s="8"/>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="9">
         <v>46284</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="10">
         <v>0.79166666666666663</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2" t="s">
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="L7" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="M7" s="2"/>
+      <c r="M7" s="8"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="9">
         <v>46285</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="10">
         <v>0.77083333333333337</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="3" t="str">
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2" t="s">
+      <c r="J8" s="8"/>
+      <c r="K8" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="L8" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="M8" s="2"/>
+      <c r="M8" s="8"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="9">
         <v>46291</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="10">
         <v>0.78125</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="3" t="str">
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2" t="s">
+      <c r="J9" s="8"/>
+      <c r="K9" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="L9" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="M9" s="2"/>
+      <c r="M9" s="8"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="9">
         <v>46298</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="10">
         <v>0.77083333333333337</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="3" t="str">
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2" t="s">
+      <c r="J10" s="8"/>
+      <c r="K10" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="L10" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="M10" s="2"/>
+      <c r="M10" s="8"/>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="9">
         <v>46306</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="10">
         <v>0.83333333333333304</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="3" t="str">
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2" t="s">
+      <c r="J11" s="8"/>
+      <c r="K11" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="L11" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="M11" s="2"/>
+      <c r="M11" s="8"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="9">
         <v>46312</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="10">
         <v>0.72916666666666663</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="3" t="str">
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2" t="s">
+      <c r="J12" s="8"/>
+      <c r="K12" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="L12" s="2" t="s">
+      <c r="L12" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="M12" s="2"/>
+      <c r="M12" s="8"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="9">
         <v>46320</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="10">
         <v>0.77083333333333304</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="3" t="str">
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2" t="s">
+      <c r="J13" s="8"/>
+      <c r="K13" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="L13" s="2" t="s">
+      <c r="L13" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="M13" s="2"/>
+      <c r="M13" s="8"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="9">
         <v>46327</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="10">
         <v>0.75</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="3" t="str">
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2" t="s">
+      <c r="J14" s="8"/>
+      <c r="K14" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="L14" s="2" t="s">
+      <c r="L14" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="M14" s="2"/>
+      <c r="M14" s="8"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="9">
         <v>46334</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="10">
         <v>0.75</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="3" t="str">
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2" t="s">
+      <c r="J15" s="8"/>
+      <c r="K15" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="L15" s="2" t="s">
+      <c r="L15" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="M15" s="2"/>
+      <c r="M15" s="8"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="9">
         <v>46340</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="10">
         <v>0.79166666666666696</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="3" t="str">
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2" t="s">
+      <c r="J16" s="8"/>
+      <c r="K16" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="L16" s="2" t="s">
+      <c r="L16" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="M16" s="2"/>
+      <c r="M16" s="8"/>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="9">
         <v>46341</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="10">
         <v>0.70833333333333337</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="3" t="str">
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2" t="s">
+      <c r="J17" s="8"/>
+      <c r="K17" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="L17" s="2" t="s">
+      <c r="L17" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="M17" s="2"/>
+      <c r="M17" s="8"/>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="9">
         <v>46354</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="10">
         <v>0.79166666666666663</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="3" t="str">
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2" t="s">
+      <c r="J18" s="8"/>
+      <c r="K18" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="L18" s="2" t="s">
+      <c r="L18" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="M18" s="2"/>
+      <c r="M18" s="8"/>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="9">
         <v>46355</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="10">
         <v>0.72916666666666663</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="3" t="str">
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2" t="s">
+      <c r="J19" s="8"/>
+      <c r="K19" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="L19" s="2" t="s">
+      <c r="L19" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="M19" s="2"/>
+      <c r="M19" s="8"/>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="9">
         <v>46368</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="10">
         <v>0.8125</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="3" t="str">
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2" t="s">
+      <c r="J20" s="8"/>
+      <c r="K20" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="L20" s="2" t="s">
+      <c r="L20" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="M20" s="2"/>
+      <c r="M20" s="8"/>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="9">
         <v>46369</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="10">
         <v>0.77083333333333337</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="3" t="str">
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2" t="s">
+      <c r="J21" s="8"/>
+      <c r="K21" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="L21" s="2" t="s">
+      <c r="L21" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="M21" s="2"/>
+      <c r="M21" s="8"/>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="9">
         <v>46376</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="10">
         <v>0.77083333333333337</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="3" t="str">
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2" t="s">
+      <c r="J22" s="8"/>
+      <c r="K22" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="L22" s="2" t="s">
+      <c r="L22" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="M22" s="2"/>
+      <c r="M22" s="8"/>
     </row>
     <row r="23" spans="1:13">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="9">
         <v>46397</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="10">
         <v>0.77083333333333337</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="3" t="str">
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2" t="s">
+      <c r="J23" s="8"/>
+      <c r="K23" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="L23" s="2" t="s">
+      <c r="L23" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="M23" s="2"/>
+      <c r="M23" s="8"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="9">
         <v>46417</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="10">
         <v>0.79166666666666663</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="3" t="str">
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2" t="s">
+      <c r="J24" s="8"/>
+      <c r="K24" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="L24" s="2" t="s">
+      <c r="L24" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="M24" s="2"/>
+      <c r="M24" s="8"/>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="9">
         <v>46425</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="10">
         <v>0.77083333333333337</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="3" t="str">
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2" t="s">
+      <c r="J25" s="8"/>
+      <c r="K25" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="L25" s="2" t="s">
+      <c r="L25" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="M25" s="2"/>
+      <c r="M25" s="8"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="9">
         <v>46446</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="10">
         <v>0.76041666666666663</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="3" t="str">
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2" t="s">
+      <c r="J26" s="8"/>
+      <c r="K26" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="L26" s="2" t="s">
+      <c r="L26" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="M26" s="2"/>
+      <c r="M26" s="8"/>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="9">
         <v>46452</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="10">
         <v>0.72916666666666663</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="3" t="str">
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2" t="s">
+      <c r="J27" s="8"/>
+      <c r="K27" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="L27" s="2" t="s">
+      <c r="L27" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="M27" s="2"/>
+      <c r="M27" s="8"/>
     </row>
     <row r="28" spans="1:13">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="9">
         <v>46459</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="10">
         <v>0.78125</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="3" t="str">
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2" t="s">
+      <c r="J28" s="8"/>
+      <c r="K28" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="L28" s="2" t="s">
+      <c r="L28" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="M28" s="2"/>
+      <c r="M28" s="8"/>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="9">
         <v>46467</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="10">
         <v>0.73958333333333337</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="3" t="str">
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2" t="s">
+      <c r="J29" s="8"/>
+      <c r="K29" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="L29" s="2"/>
-      <c r="M29" s="2"/>
+      <c r="L29" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="M29" s="8"/>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="2"/>
@@ -9256,446 +9318,446 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
     </row>
     <row r="3" spans="1:10" ht="30">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="7" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3" t="str">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="11" t="str">
         <f>IF(B4="","",IFERROR(VLOOKUP(B4,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="3" t="str">
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="11" t="str">
         <f t="shared" ref="G4:G67" si="0">IF(AND(E4="",F4=""),"",SUM(E4:F4))</f>
         <v/>
       </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3" t="str">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="11" t="str">
         <f>IF(B5="","",IFERROR(VLOOKUP(B5,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="3" t="str">
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3" t="str">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="11" t="str">
         <f>IF(B6="","",IFERROR(VLOOKUP(B6,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="3" t="str">
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="3" t="str">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="11" t="str">
         <f>IF(B7="","",IFERROR(VLOOKUP(B7,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="3" t="str">
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="3" t="str">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="11" t="str">
         <f>IF(B8="","",IFERROR(VLOOKUP(B8,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="3" t="str">
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="3" t="str">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="11" t="str">
         <f>IF(B9="","",IFERROR(VLOOKUP(B9,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="3" t="str">
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="3" t="str">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="11" t="str">
         <f>IF(B10="","",IFERROR(VLOOKUP(B10,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="3" t="str">
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="3" t="str">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="11" t="str">
         <f>IF(B11="","",IFERROR(VLOOKUP(B11,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="3" t="str">
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="3" t="str">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="11" t="str">
         <f>IF(B12="","",IFERROR(VLOOKUP(B12,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="3" t="str">
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="3" t="str">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="11" t="str">
         <f>IF(B13="","",IFERROR(VLOOKUP(B13,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="3" t="str">
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="3" t="str">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="11" t="str">
         <f>IF(B14="","",IFERROR(VLOOKUP(B14,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="3" t="str">
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="3" t="str">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="11" t="str">
         <f>IF(B15="","",IFERROR(VLOOKUP(B15,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="3" t="str">
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="3" t="str">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="11" t="str">
         <f>IF(B16="","",IFERROR(VLOOKUP(B16,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="3" t="str">
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="3" t="str">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="11" t="str">
         <f>IF(B17="","",IFERROR(VLOOKUP(B17,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="3" t="str">
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="3" t="str">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="11" t="str">
         <f>IF(B18="","",IFERROR(VLOOKUP(B18,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="3" t="str">
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="3" t="str">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="11" t="str">
         <f>IF(B19="","",IFERROR(VLOOKUP(B19,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="3" t="str">
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="3" t="str">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="11" t="str">
         <f>IF(B20="","",IFERROR(VLOOKUP(B20,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="3" t="str">
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="3" t="str">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="11" t="str">
         <f>IF(B21="","",IFERROR(VLOOKUP(B21,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="3" t="str">
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="3" t="str">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="11" t="str">
         <f>IF(B22="","",IFERROR(VLOOKUP(B22,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="3" t="str">
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="3" t="str">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="11" t="str">
         <f>IF(B23="","",IFERROR(VLOOKUP(B23,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="3" t="str">
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="3" t="str">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="11" t="str">
         <f>IF(B24="","",IFERROR(VLOOKUP(B24,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="3" t="str">
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="3" t="str">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="11" t="str">
         <f>IF(B25="","",IFERROR(VLOOKUP(B25,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="3" t="str">
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2"/>
@@ -18297,450 +18359,450 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
     </row>
     <row r="3" spans="1:11" ht="30">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="7" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3" t="str">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="11" t="str">
         <f>IF(B4="","",IFERROR(VLOOKUP(B4,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="3" t="str">
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="11" t="str">
         <f t="shared" ref="G4:G35" si="0">IF(E4="","",E4-F4)</f>
         <v/>
       </c>
-      <c r="H4" s="5" t="str">
+      <c r="H4" s="12" t="str">
         <f t="shared" ref="H4:H35" si="1">IF(OR(E4="",E4=0),"",G4/E4)</f>
         <v/>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3" t="str">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="11" t="str">
         <f>IF(B5="","",IFERROR(VLOOKUP(B5,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="3" t="str">
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H5" s="5" t="str">
+      <c r="H5" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3" t="str">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="11" t="str">
         <f>IF(B6="","",IFERROR(VLOOKUP(B6,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="3" t="str">
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H6" s="5" t="str">
+      <c r="H6" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="3" t="str">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="11" t="str">
         <f>IF(B7="","",IFERROR(VLOOKUP(B7,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="3" t="str">
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H7" s="5" t="str">
+      <c r="H7" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="3" t="str">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="11" t="str">
         <f>IF(B8="","",IFERROR(VLOOKUP(B8,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="3" t="str">
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H8" s="5" t="str">
+      <c r="H8" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="3" t="str">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="11" t="str">
         <f>IF(B9="","",IFERROR(VLOOKUP(B9,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="3" t="str">
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H9" s="5" t="str">
+      <c r="H9" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="3" t="str">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="11" t="str">
         <f>IF(B10="","",IFERROR(VLOOKUP(B10,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="3" t="str">
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H10" s="5" t="str">
+      <c r="H10" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="3" t="str">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="11" t="str">
         <f>IF(B11="","",IFERROR(VLOOKUP(B11,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="3" t="str">
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H11" s="5" t="str">
+      <c r="H11" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="3" t="str">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="11" t="str">
         <f>IF(B12="","",IFERROR(VLOOKUP(B12,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="3" t="str">
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H12" s="5" t="str">
+      <c r="H12" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="3" t="str">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="11" t="str">
         <f>IF(B13="","",IFERROR(VLOOKUP(B13,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="3" t="str">
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H13" s="5" t="str">
+      <c r="H13" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="3" t="str">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="11" t="str">
         <f>IF(B14="","",IFERROR(VLOOKUP(B14,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="3" t="str">
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H14" s="5" t="str">
+      <c r="H14" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="3" t="str">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="11" t="str">
         <f>IF(B15="","",IFERROR(VLOOKUP(B15,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="3" t="str">
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H15" s="5" t="str">
+      <c r="H15" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="3" t="str">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="11" t="str">
         <f>IF(B16="","",IFERROR(VLOOKUP(B16,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="3" t="str">
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H16" s="5" t="str">
+      <c r="H16" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="3" t="str">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="11" t="str">
         <f>IF(B17="","",IFERROR(VLOOKUP(B17,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="3" t="str">
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H17" s="5" t="str">
+      <c r="H17" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="3" t="str">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="11" t="str">
         <f>IF(B18="","",IFERROR(VLOOKUP(B18,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="3" t="str">
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H18" s="5" t="str">
+      <c r="H18" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="3" t="str">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="11" t="str">
         <f>IF(B19="","",IFERROR(VLOOKUP(B19,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="3" t="str">
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H19" s="5" t="str">
+      <c r="H19" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="3" t="str">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="11" t="str">
         <f>IF(B20="","",IFERROR(VLOOKUP(B20,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="3" t="str">
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H20" s="5" t="str">
+      <c r="H20" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="3" t="str">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="11" t="str">
         <f>IF(B21="","",IFERROR(VLOOKUP(B21,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="3" t="str">
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H21" s="5" t="str">
+      <c r="H21" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="2"/>
@@ -22721,41 +22783,41 @@
   <cols>
     <col min="1" max="1" width="37.25" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="2.375" customWidth="1"/>
+    <col min="3" max="3" width="4" customWidth="1"/>
     <col min="4" max="4" width="8.625" customWidth="1"/>
-    <col min="5" max="5" width="2.75" customWidth="1"/>
-    <col min="6" max="6" width="1.75" customWidth="1"/>
-    <col min="7" max="7" width="1.625" customWidth="1"/>
-    <col min="8" max="8" width="3.25" customWidth="1"/>
-    <col min="9" max="9" width="3.625" customWidth="1"/>
-    <col min="10" max="10" width="2.875" customWidth="1"/>
+    <col min="5" max="5" width="5.25" customWidth="1"/>
+    <col min="6" max="6" width="3.625" customWidth="1"/>
+    <col min="7" max="7" width="3" customWidth="1"/>
+    <col min="8" max="8" width="4.5" customWidth="1"/>
+    <col min="9" max="9" width="4.625" customWidth="1"/>
+    <col min="10" max="10" width="4.875" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="4.75" customWidth="1"/>
+    <col min="13" max="13" width="9.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-    </row>
-    <row r="2" spans="1:13" ht="30">
-      <c r="L2" s="1" t="s">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+    </row>
+    <row r="2" spans="1:13" ht="15">
+      <c r="L2" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="7" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="45">
+    <row r="3" spans="1:13" ht="30">
       <c r="A3" s="1" t="s">
         <v>51</v>
       </c>
@@ -22786,293 +22848,303 @@
       <c r="J3" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="L3" t="s">
+      <c r="K3" s="15"/>
+      <c r="L3" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="13">
         <f>COUNT(Games!$A$4:$A$200)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" t="str">
+      <c r="A4" s="13" t="str">
         <f>IF(Players!A4="","",Players!A4)</f>
         <v>P001</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B4" s="13" t="str">
         <f>IF(A4="","",IFERROR(VLOOKUP(A4,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Sam Peters</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="13">
         <f>IF(A4="","",IFERROR(VLOOKUP(A4,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>9</v>
       </c>
-      <c r="D4" t="str">
+      <c r="D4" s="13" t="str">
         <f>IF(A4="","",IFERROR(VLOOKUP(A4,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="13">
         <f>IF(A4="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A4,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="13">
         <f>IF(A4="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A4))</f>
         <v>0</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="13">
         <f>IF(A4="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A4))</f>
         <v>0</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="13">
         <f t="shared" ref="H4:H35" si="0">IF(A4="","",F4+G4)</f>
         <v>0</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="13">
         <f>IF(A4="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A4))</f>
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="13">
         <f>IF(A4="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A4))</f>
         <v>0</v>
       </c>
-      <c r="L4" t="s">
+      <c r="K4" s="15"/>
+      <c r="L4" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="13">
         <f>SUM(Games!$G$4:$G$200)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" t="str">
+      <c r="A5" s="13" t="str">
         <f>IF(Players!A5="","",Players!A5)</f>
         <v>P002</v>
       </c>
-      <c r="B5" t="str">
+      <c r="B5" s="13" t="str">
         <f>IF(A5="","",IFERROR(VLOOKUP(A5,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Marks Kanins</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="13">
         <f>IF(A5="","",IFERROR(VLOOKUP(A5,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>97</v>
       </c>
-      <c r="D5" t="str">
+      <c r="D5" s="13" t="str">
         <f>IF(A5="","",IFERROR(VLOOKUP(A5,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="13">
         <f>IF(A5="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A5,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="13">
         <f>IF(A5="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A5))</f>
         <v>0</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="13">
         <f>IF(A5="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A5))</f>
         <v>0</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="13">
         <f>IF(A5="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A5))</f>
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="13">
         <f>IF(A5="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A5))</f>
         <v>0</v>
       </c>
-      <c r="L5" t="s">
+      <c r="K5" s="15"/>
+      <c r="L5" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="13">
         <f>SUM(Games!$H$4:$H$200)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" t="str">
+      <c r="A6" s="13" t="str">
         <f>IF(Players!A6="","",Players!A6)</f>
         <v>P003</v>
       </c>
-      <c r="B6" t="str">
+      <c r="B6" s="13" t="str">
         <f>IF(A6="","",IFERROR(VLOOKUP(A6,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Dominic Wealthall</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="13">
         <f>IF(A6="","",IFERROR(VLOOKUP(A6,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>74</v>
       </c>
-      <c r="D6" t="str">
+      <c r="D6" s="13" t="str">
         <f>IF(A6="","",IFERROR(VLOOKUP(A6,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="13">
         <f>IF(A6="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A6,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="13">
         <f>IF(A6="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A6))</f>
         <v>0</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="13">
         <f>IF(A6="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A6))</f>
         <v>0</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="13">
         <f>IF(A6="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A6))</f>
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="13">
         <f>IF(A6="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A6))</f>
         <v>0</v>
       </c>
-      <c r="L6" t="s">
+      <c r="K6" s="15"/>
+      <c r="L6" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="13">
         <f>COUNTIF(Games!$I$4:$I$200,"W")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" t="str">
+      <c r="A7" s="13" t="str">
         <f>IF(Players!A7="","",Players!A7)</f>
         <v>P004</v>
       </c>
-      <c r="B7" t="str">
+      <c r="B7" s="13" t="str">
         <f>IF(A7="","",IFERROR(VLOOKUP(A7,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Aaron Burton</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="13">
         <f>IF(A7="","",IFERROR(VLOOKUP(A7,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>29</v>
       </c>
-      <c r="D7" t="str">
+      <c r="D7" s="13" t="str">
         <f>IF(A7="","",IFERROR(VLOOKUP(A7,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Netminder</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="13">
         <f>IF(A7="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A7,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="13">
         <f>IF(A7="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A7))</f>
         <v>0</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="13">
         <f>IF(A7="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A7))</f>
         <v>0</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="13">
         <f>IF(A7="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A7))</f>
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="13">
         <f>IF(A7="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A7))</f>
         <v>0</v>
       </c>
-      <c r="L7" t="s">
+      <c r="K7" s="15"/>
+      <c r="L7" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="13">
         <f>COUNTIF(Games!$I$4:$I$200,"L")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" t="str">
+      <c r="A8" s="13" t="str">
         <f>IF(Players!A8="","",Players!A8)</f>
-        <v/>
-      </c>
-      <c r="B8" t="str">
+        <v>P005</v>
+      </c>
+      <c r="B8" s="13" t="str">
         <f>IF(A8="","",IFERROR(VLOOKUP(A8,Players!$A$4:$D$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="C8" t="str">
+        <v>Charlie Russell</v>
+      </c>
+      <c r="C8" s="13">
         <f>IF(A8="","",IFERROR(VLOOKUP(A8,Players!$A$4:$D$200,3,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="D8" t="str">
+        <v>12</v>
+      </c>
+      <c r="D8" s="13" t="str">
         <f>IF(A8="","",IFERROR(VLOOKUP(A8,Players!$A$4:$D$200,4,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="E8" t="str">
+        <v>Forward</v>
+      </c>
+      <c r="E8" s="13">
         <f>IF(A8="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A8,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v/>
-      </c>
-      <c r="F8" t="str">
+        <v>0</v>
+      </c>
+      <c r="F8" s="13">
         <f>IF(A8="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A8))</f>
-        <v/>
-      </c>
-      <c r="G8" t="str">
+        <v>0</v>
+      </c>
+      <c r="G8" s="13">
         <f>IF(A8="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A8))</f>
-        <v/>
-      </c>
-      <c r="H8" t="str">
+        <v>0</v>
+      </c>
+      <c r="H8" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I8" t="str">
+        <v>0</v>
+      </c>
+      <c r="I8" s="13">
         <f>IF(A8="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A8))</f>
-        <v/>
-      </c>
-      <c r="J8" t="str">
+        <v>0</v>
+      </c>
+      <c r="J8" s="13">
         <f>IF(A8="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A8))</f>
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K8" s="15"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" t="str">
+      <c r="A9" s="13" t="str">
         <f>IF(Players!A9="","",Players!A9)</f>
-        <v/>
-      </c>
-      <c r="B9" t="str">
+        <v>P006</v>
+      </c>
+      <c r="B9" s="13" t="str">
         <f>IF(A9="","",IFERROR(VLOOKUP(A9,Players!$A$4:$D$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="C9" t="str">
+        <v>Lewis Smith</v>
+      </c>
+      <c r="C9" s="13">
         <f>IF(A9="","",IFERROR(VLOOKUP(A9,Players!$A$4:$D$200,3,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="D9" t="str">
+        <v>13</v>
+      </c>
+      <c r="D9" s="13" t="str">
         <f>IF(A9="","",IFERROR(VLOOKUP(A9,Players!$A$4:$D$200,4,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="E9" t="str">
+        <v>Forward</v>
+      </c>
+      <c r="E9" s="13">
         <f>IF(A9="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A9,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v/>
-      </c>
-      <c r="F9" t="str">
+        <v>0</v>
+      </c>
+      <c r="F9" s="13">
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
-        <v/>
-      </c>
-      <c r="G9" t="str">
+        <v>0</v>
+      </c>
+      <c r="G9" s="13">
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
-        <v/>
-      </c>
-      <c r="H9" t="str">
+        <v>0</v>
+      </c>
+      <c r="H9" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I9" t="str">
+        <v>0</v>
+      </c>
+      <c r="I9" s="13">
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
-        <v/>
-      </c>
-      <c r="J9" t="str">
+        <v>0</v>
+      </c>
+      <c r="J9" s="13">
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="str">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156F467B-DB3C-421D-BAB7-DD15C1633979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{338B66D0-EB23-4EEC-950B-F563E2DC83D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="209">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -667,6 +667,9 @@
   <si>
     <t>Peters.png</t>
   </si>
+  <si>
+    <t>League/Cup</t>
+  </si>
 </sst>
 </file>
 
@@ -777,10 +780,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1002,14 +1005,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="3" spans="1:6" ht="30">
       <c r="A3" s="1" t="s">
@@ -1110,15 +1113,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
       <c r="H1" s="6"/>
     </row>
     <row r="3" spans="1:8" ht="15">
@@ -3360,15 +3363,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="3" spans="1:7" ht="30">
       <c r="A3" s="7" t="s">
@@ -5267,21 +5270,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
     </row>
     <row r="2" spans="1:13"/>
     <row r="3" spans="1:13" ht="30">
@@ -5410,7 +5413,7 @@
         <v>87</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>88</v>
+        <v>208</v>
       </c>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
@@ -9289,11 +9292,11 @@
     <mergeCell ref="A1:M1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="F4:F200" xr:uid="{00000000-0002-0000-0200-000001000000}">
-      <formula1>"Pre-season,League,Cup,Playoff"</formula1>
-    </dataValidation>
     <dataValidation type="list" sqref="J4:J200" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>"No,OT,SO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="F1:F1048576" xr:uid="{F7BC15CE-D381-4D67-9A40-6CEF31A03920}">
+      <formula1>"Pre-season,League,Cup,Playoff,League/Cup"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9318,18 +9321,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
     </row>
     <row r="3" spans="1:10" ht="30">
       <c r="A3" s="7" t="s">
@@ -18359,19 +18362,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
     </row>
     <row r="3" spans="1:11" ht="30">
       <c r="A3" s="7" t="s">
@@ -22796,18 +22799,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
     </row>
     <row r="2" spans="1:13" ht="15">
       <c r="L2" s="7" t="s">
@@ -22848,7 +22851,7 @@
       <c r="J3" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="K3" s="15"/>
+      <c r="K3" s="14"/>
       <c r="L3" s="13" t="s">
         <v>114</v>
       </c>
@@ -22898,7 +22901,7 @@
         <f>IF(A4="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A4))</f>
         <v>0</v>
       </c>
-      <c r="K4" s="15"/>
+      <c r="K4" s="14"/>
       <c r="L4" s="13" t="s">
         <v>115</v>
       </c>
@@ -22948,7 +22951,7 @@
         <f>IF(A5="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A5))</f>
         <v>0</v>
       </c>
-      <c r="K5" s="15"/>
+      <c r="K5" s="14"/>
       <c r="L5" s="13" t="s">
         <v>116</v>
       </c>
@@ -22998,7 +23001,7 @@
         <f>IF(A6="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A6))</f>
         <v>0</v>
       </c>
-      <c r="K6" s="15"/>
+      <c r="K6" s="14"/>
       <c r="L6" s="13" t="s">
         <v>117</v>
       </c>
@@ -23048,7 +23051,7 @@
         <f>IF(A7="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A7))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="15"/>
+      <c r="K7" s="14"/>
       <c r="L7" s="13" t="s">
         <v>118</v>
       </c>
@@ -23098,7 +23101,7 @@
         <f>IF(A8="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A8))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="15"/>
+      <c r="K8" s="14"/>
       <c r="L8" s="13"/>
       <c r="M8" s="13"/>
     </row>
@@ -23143,8 +23146,8 @@
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="str">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{338B66D0-EB23-4EEC-950B-F563E2DC83D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB643CF7-0313-4DAA-BA95-2254A5BB4F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5447,7 +5447,7 @@
         <v>82</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>88</v>
+        <v>208</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
@@ -5546,7 +5546,7 @@
         <v>87</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>88</v>
+        <v>208</v>
       </c>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
@@ -5614,7 +5614,7 @@
         <v>82</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>88</v>
+        <v>208</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
@@ -5648,7 +5648,7 @@
         <v>87</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>88</v>
+        <v>208</v>
       </c>
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
@@ -5682,7 +5682,7 @@
         <v>82</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>88</v>
+        <v>208</v>
       </c>
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
@@ -5716,7 +5716,7 @@
         <v>87</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>88</v>
+        <v>208</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
@@ -5784,7 +5784,7 @@
         <v>82</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>88</v>
+        <v>208</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
@@ -5818,7 +5818,7 @@
         <v>82</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>88</v>
+        <v>208</v>
       </c>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
@@ -5954,7 +5954,7 @@
         <v>87</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>88</v>
+        <v>208</v>
       </c>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB643CF7-0313-4DAA-BA95-2254A5BB4F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C011ACD5-4A63-44D3-BF46-7FF2151DB41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="210">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -670,6 +670,9 @@
   <si>
     <t>League/Cup</t>
   </si>
+  <si>
+    <t>russell.png</t>
+  </si>
 </sst>
 </file>
 
@@ -3492,7 +3495,9 @@
       <c r="E8" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="8"/>
+      <c r="F8" s="8" t="s">
+        <v>209</v>
+      </c>
       <c r="G8" s="8"/>
     </row>
     <row r="9" spans="1:7">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C011ACD5-4A63-44D3-BF46-7FF2151DB41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C67875-5956-455A-9738-BDDF63E379FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="214">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -673,6 +673,18 @@
   <si>
     <t>russell.png</t>
   </si>
+  <si>
+    <t>arron.png</t>
+  </si>
+  <si>
+    <t>marks.png</t>
+  </si>
+  <si>
+    <t>dom.png</t>
+  </si>
+  <si>
+    <t>smith.png</t>
+  </si>
 </sst>
 </file>
 
@@ -3436,7 +3448,9 @@
       <c r="E5" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="8"/>
+      <c r="F5" s="8" t="s">
+        <v>211</v>
+      </c>
       <c r="G5" s="8"/>
     </row>
     <row r="6" spans="1:7">
@@ -3455,7 +3469,9 @@
       <c r="E6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="8"/>
+      <c r="F6" s="8" t="s">
+        <v>212</v>
+      </c>
       <c r="G6" s="8" t="s">
         <v>65</v>
       </c>
@@ -3476,7 +3492,9 @@
       <c r="E7" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="8"/>
+      <c r="F7" s="8" t="s">
+        <v>210</v>
+      </c>
       <c r="G7" s="8"/>
     </row>
     <row r="8" spans="1:7">
@@ -3516,7 +3534,9 @@
       <c r="E9" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="8"/>
+      <c r="F9" s="8" t="s">
+        <v>213</v>
+      </c>
       <c r="G9" s="8"/>
     </row>
     <row r="10" spans="1:7">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C67875-5956-455A-9738-BDDF63E379FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E69095DC-37C0-4841-A08C-B2449AED152F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4290" yWindow="2385" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="220">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -685,6 +685,24 @@
   <si>
     <t>smith.png</t>
   </si>
+  <si>
+    <t>P007</t>
+  </si>
+  <si>
+    <t>Robert Oxley</t>
+  </si>
+  <si>
+    <t>rob.png</t>
+  </si>
+  <si>
+    <t>P008</t>
+  </si>
+  <si>
+    <t>Madi Wright</t>
+  </si>
+  <si>
+    <t>madi.png</t>
+  </si>
 </sst>
 </file>
 
@@ -3540,22 +3558,46 @@
       <c r="G9" s="8"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
+      <c r="A10" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="C10" s="8">
+        <v>5</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="G10" s="8"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
+      <c r="A11" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="C11" s="8">
+        <v>10</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="G11" s="8"/>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2"/>
@@ -23177,85 +23219,85 @@
     <row r="10" spans="1:13">
       <c r="A10" t="str">
         <f>IF(Players!A10="","",Players!A10)</f>
-        <v/>
+        <v>P007</v>
       </c>
       <c r="B10" t="str">
         <f>IF(A10="","",IFERROR(VLOOKUP(A10,Players!$A$4:$D$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="C10" t="str">
+        <v>Robert Oxley</v>
+      </c>
+      <c r="C10">
         <f>IF(A10="","",IFERROR(VLOOKUP(A10,Players!$A$4:$D$200,3,FALSE),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="D10" t="str">
         <f>IF(A10="","",IFERROR(VLOOKUP(A10,Players!$A$4:$D$200,4,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="E10" t="str">
+        <v>Defence</v>
+      </c>
+      <c r="E10">
         <f>IF(A10="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A10,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v/>
-      </c>
-      <c r="F10" t="str">
+        <v>0</v>
+      </c>
+      <c r="F10">
         <f>IF(A10="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A10))</f>
-        <v/>
-      </c>
-      <c r="G10" t="str">
+        <v>0</v>
+      </c>
+      <c r="G10">
         <f>IF(A10="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A10))</f>
-        <v/>
-      </c>
-      <c r="H10" t="str">
+        <v>0</v>
+      </c>
+      <c r="H10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I10" t="str">
+        <v>0</v>
+      </c>
+      <c r="I10">
         <f>IF(A10="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A10))</f>
-        <v/>
-      </c>
-      <c r="J10" t="str">
+        <v>0</v>
+      </c>
+      <c r="J10">
         <f>IF(A10="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A10))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="str">
         <f>IF(Players!A11="","",Players!A11)</f>
-        <v/>
+        <v>P008</v>
       </c>
       <c r="B11" t="str">
         <f>IF(A11="","",IFERROR(VLOOKUP(A11,Players!$A$4:$D$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="C11" t="str">
+        <v>Madi Wright</v>
+      </c>
+      <c r="C11">
         <f>IF(A11="","",IFERROR(VLOOKUP(A11,Players!$A$4:$D$200,3,FALSE),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="D11" t="str">
         <f>IF(A11="","",IFERROR(VLOOKUP(A11,Players!$A$4:$D$200,4,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="E11" t="str">
+        <v>Defence</v>
+      </c>
+      <c r="E11">
         <f>IF(A11="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A11,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v/>
-      </c>
-      <c r="F11" t="str">
+        <v>0</v>
+      </c>
+      <c r="F11">
         <f>IF(A11="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A11))</f>
-        <v/>
-      </c>
-      <c r="G11" t="str">
+        <v>0</v>
+      </c>
+      <c r="G11">
         <f>IF(A11="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A11))</f>
-        <v/>
-      </c>
-      <c r="H11" t="str">
+        <v>0</v>
+      </c>
+      <c r="H11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I11" t="str">
+        <v>0</v>
+      </c>
+      <c r="I11">
         <f>IF(A11="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A11))</f>
-        <v/>
-      </c>
-      <c r="J11" t="str">
+        <v>0</v>
+      </c>
+      <c r="J11">
         <f>IF(A11="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A11))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:13">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E69095DC-37C0-4841-A08C-B2449AED152F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{447C7740-29F0-4EDE-8A4B-F018A92FE78E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="2385" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="226">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -703,6 +703,24 @@
   <si>
     <t>madi.png</t>
   </si>
+  <si>
+    <t>P009</t>
+  </si>
+  <si>
+    <t>P010</t>
+  </si>
+  <si>
+    <t>Lizzie Nowik</t>
+  </si>
+  <si>
+    <t>lizzie.png</t>
+  </si>
+  <si>
+    <t>Nicole Jackson</t>
+  </si>
+  <si>
+    <t>nicole.png</t>
+  </si>
 </sst>
 </file>
 
@@ -3600,31 +3618,55 @@
       <c r="G11" s="8"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
+      <c r="A12" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="C12" s="8">
+        <v>2</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="G12" s="8"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
+      <c r="A13" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="C13" s="8">
+        <v>86</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="G13" s="8"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2"/>
@@ -23303,85 +23345,85 @@
     <row r="12" spans="1:13">
       <c r="A12" t="str">
         <f>IF(Players!A12="","",Players!A12)</f>
-        <v/>
+        <v>P009</v>
       </c>
       <c r="B12" t="str">
         <f>IF(A12="","",IFERROR(VLOOKUP(A12,Players!$A$4:$D$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="C12" t="str">
+        <v>Lizzie Nowik</v>
+      </c>
+      <c r="C12">
         <f>IF(A12="","",IFERROR(VLOOKUP(A12,Players!$A$4:$D$200,3,FALSE),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D12" t="str">
         <f>IF(A12="","",IFERROR(VLOOKUP(A12,Players!$A$4:$D$200,4,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="E12" t="str">
+        <v>Netminder</v>
+      </c>
+      <c r="E12">
         <f>IF(A12="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A12,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v/>
-      </c>
-      <c r="F12" t="str">
+        <v>0</v>
+      </c>
+      <c r="F12">
         <f>IF(A12="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A12))</f>
-        <v/>
-      </c>
-      <c r="G12" t="str">
+        <v>0</v>
+      </c>
+      <c r="G12">
         <f>IF(A12="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A12))</f>
-        <v/>
-      </c>
-      <c r="H12" t="str">
+        <v>0</v>
+      </c>
+      <c r="H12">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I12" t="str">
+        <v>0</v>
+      </c>
+      <c r="I12">
         <f>IF(A12="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A12))</f>
-        <v/>
-      </c>
-      <c r="J12" t="str">
+        <v>0</v>
+      </c>
+      <c r="J12">
         <f>IF(A12="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A12))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="str">
         <f>IF(Players!A13="","",Players!A13)</f>
-        <v/>
+        <v>P010</v>
       </c>
       <c r="B13" t="str">
         <f>IF(A13="","",IFERROR(VLOOKUP(A13,Players!$A$4:$D$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="C13" t="str">
+        <v>Nicole Jackson</v>
+      </c>
+      <c r="C13">
         <f>IF(A13="","",IFERROR(VLOOKUP(A13,Players!$A$4:$D$200,3,FALSE),""))</f>
-        <v/>
+        <v>86</v>
       </c>
       <c r="D13" t="str">
         <f>IF(A13="","",IFERROR(VLOOKUP(A13,Players!$A$4:$D$200,4,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="E13" t="str">
+        <v>Netminder</v>
+      </c>
+      <c r="E13">
         <f>IF(A13="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A13,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v/>
-      </c>
-      <c r="F13" t="str">
+        <v>0</v>
+      </c>
+      <c r="F13">
         <f>IF(A13="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A13))</f>
-        <v/>
-      </c>
-      <c r="G13" t="str">
+        <v>0</v>
+      </c>
+      <c r="G13">
         <f>IF(A13="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A13))</f>
-        <v/>
-      </c>
-      <c r="H13" t="str">
+        <v>0</v>
+      </c>
+      <c r="H13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I13" t="str">
+        <v>0</v>
+      </c>
+      <c r="I13">
         <f>IF(A13="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A13))</f>
-        <v/>
-      </c>
-      <c r="J13" t="str">
+        <v>0</v>
+      </c>
+      <c r="J13">
         <f>IF(A13="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A13))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:13">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{447C7740-29F0-4EDE-8A4B-F018A92FE78E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E40E3CC2-8932-48A3-80C9-9D746030D9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4905" yWindow="3375" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="248">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -721,6 +721,72 @@
   <si>
     <t>nicole.png</t>
   </si>
+  <si>
+    <t>P011</t>
+  </si>
+  <si>
+    <t>Xander Robinson</t>
+  </si>
+  <si>
+    <t>P012</t>
+  </si>
+  <si>
+    <t>Joshua Blackwood</t>
+  </si>
+  <si>
+    <t>P013</t>
+  </si>
+  <si>
+    <t>P014</t>
+  </si>
+  <si>
+    <t>P015</t>
+  </si>
+  <si>
+    <t>P016</t>
+  </si>
+  <si>
+    <t>P017</t>
+  </si>
+  <si>
+    <t>P018</t>
+  </si>
+  <si>
+    <t>P019</t>
+  </si>
+  <si>
+    <t>P020</t>
+  </si>
+  <si>
+    <t>P021</t>
+  </si>
+  <si>
+    <t>Harry MacGarvery</t>
+  </si>
+  <si>
+    <t>Chalie Conroy</t>
+  </si>
+  <si>
+    <t>Oliver Broyd</t>
+  </si>
+  <si>
+    <t>Connor Mellett</t>
+  </si>
+  <si>
+    <t>Hayden Hagger</t>
+  </si>
+  <si>
+    <t>Sam Purcell</t>
+  </si>
+  <si>
+    <t>Samuel Rickard</t>
+  </si>
+  <si>
+    <t>Oscar Lee</t>
+  </si>
+  <si>
+    <t>Jacob Maidment</t>
+  </si>
 </sst>
 </file>
 
@@ -3660,112 +3726,222 @@
       <c r="G13" s="8"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
+      <c r="A14" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="C14" s="8">
+        <v>14</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>35</v>
+      </c>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
+      <c r="A15" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="C15" s="8">
+        <v>18</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
+      <c r="A16" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="C16" s="8">
+        <v>22</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
+      <c r="A17" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="C17" s="8">
+        <v>24</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
+      <c r="A18" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="C18" s="8">
+        <v>33</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
+      <c r="A19" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="C19" s="8">
+        <v>37</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
+      <c r="A20" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="C20" s="8">
+        <v>45</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
+      <c r="A21" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="C21" s="8">
+        <v>64</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
+      <c r="A22" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="C22" s="8">
+        <v>65</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
+      <c r="A23" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C23" s="8">
+        <v>68</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
+      <c r="A24" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="C24" s="8">
+        <v>89</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2"/>
@@ -23429,463 +23605,463 @@
     <row r="14" spans="1:13">
       <c r="A14" t="str">
         <f>IF(Players!A14="","",Players!A14)</f>
-        <v/>
+        <v>P011</v>
       </c>
       <c r="B14" t="str">
         <f>IF(A14="","",IFERROR(VLOOKUP(A14,Players!$A$4:$D$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="C14" t="str">
+        <v>Xander Robinson</v>
+      </c>
+      <c r="C14">
         <f>IF(A14="","",IFERROR(VLOOKUP(A14,Players!$A$4:$D$200,3,FALSE),""))</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="D14" t="str">
         <f>IF(A14="","",IFERROR(VLOOKUP(A14,Players!$A$4:$D$200,4,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="E14" t="str">
+        <v>Forward</v>
+      </c>
+      <c r="E14">
         <f>IF(A14="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A14,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v/>
-      </c>
-      <c r="F14" t="str">
+        <v>0</v>
+      </c>
+      <c r="F14">
         <f>IF(A14="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A14))</f>
-        <v/>
-      </c>
-      <c r="G14" t="str">
+        <v>0</v>
+      </c>
+      <c r="G14">
         <f>IF(A14="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A14))</f>
-        <v/>
-      </c>
-      <c r="H14" t="str">
+        <v>0</v>
+      </c>
+      <c r="H14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I14" t="str">
+        <v>0</v>
+      </c>
+      <c r="I14">
         <f>IF(A14="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A14))</f>
-        <v/>
-      </c>
-      <c r="J14" t="str">
+        <v>0</v>
+      </c>
+      <c r="J14">
         <f>IF(A14="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A14))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="str">
         <f>IF(Players!A15="","",Players!A15)</f>
-        <v/>
+        <v>P012</v>
       </c>
       <c r="B15" t="str">
         <f>IF(A15="","",IFERROR(VLOOKUP(A15,Players!$A$4:$D$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="C15" t="str">
+        <v>Joshua Blackwood</v>
+      </c>
+      <c r="C15">
         <f>IF(A15="","",IFERROR(VLOOKUP(A15,Players!$A$4:$D$200,3,FALSE),""))</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="D15" t="str">
         <f>IF(A15="","",IFERROR(VLOOKUP(A15,Players!$A$4:$D$200,4,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="E15" t="str">
+        <v>Forward</v>
+      </c>
+      <c r="E15">
         <f>IF(A15="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A15,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v/>
-      </c>
-      <c r="F15" t="str">
+        <v>0</v>
+      </c>
+      <c r="F15">
         <f>IF(A15="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A15))</f>
-        <v/>
-      </c>
-      <c r="G15" t="str">
+        <v>0</v>
+      </c>
+      <c r="G15">
         <f>IF(A15="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A15))</f>
-        <v/>
-      </c>
-      <c r="H15" t="str">
+        <v>0</v>
+      </c>
+      <c r="H15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I15" t="str">
+        <v>0</v>
+      </c>
+      <c r="I15">
         <f>IF(A15="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A15))</f>
-        <v/>
-      </c>
-      <c r="J15" t="str">
+        <v>0</v>
+      </c>
+      <c r="J15">
         <f>IF(A15="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A15))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="str">
         <f>IF(Players!A16="","",Players!A16)</f>
-        <v/>
+        <v>P013</v>
       </c>
       <c r="B16" t="str">
         <f>IF(A16="","",IFERROR(VLOOKUP(A16,Players!$A$4:$D$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="C16" t="str">
+        <v>Harry MacGarvery</v>
+      </c>
+      <c r="C16">
         <f>IF(A16="","",IFERROR(VLOOKUP(A16,Players!$A$4:$D$200,3,FALSE),""))</f>
-        <v/>
+        <v>22</v>
       </c>
       <c r="D16" t="str">
         <f>IF(A16="","",IFERROR(VLOOKUP(A16,Players!$A$4:$D$200,4,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="E16" t="str">
+        <v>Forward</v>
+      </c>
+      <c r="E16">
         <f>IF(A16="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A16,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v/>
-      </c>
-      <c r="F16" t="str">
+        <v>0</v>
+      </c>
+      <c r="F16">
         <f>IF(A16="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A16))</f>
-        <v/>
-      </c>
-      <c r="G16" t="str">
+        <v>0</v>
+      </c>
+      <c r="G16">
         <f>IF(A16="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A16))</f>
-        <v/>
-      </c>
-      <c r="H16" t="str">
+        <v>0</v>
+      </c>
+      <c r="H16">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I16" t="str">
+        <v>0</v>
+      </c>
+      <c r="I16">
         <f>IF(A16="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A16))</f>
-        <v/>
-      </c>
-      <c r="J16" t="str">
+        <v>0</v>
+      </c>
+      <c r="J16">
         <f>IF(A16="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A16))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="str">
         <f>IF(Players!A17="","",Players!A17)</f>
-        <v/>
+        <v>P014</v>
       </c>
       <c r="B17" t="str">
         <f>IF(A17="","",IFERROR(VLOOKUP(A17,Players!$A$4:$D$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="C17" t="str">
+        <v>Chalie Conroy</v>
+      </c>
+      <c r="C17">
         <f>IF(A17="","",IFERROR(VLOOKUP(A17,Players!$A$4:$D$200,3,FALSE),""))</f>
-        <v/>
+        <v>24</v>
       </c>
       <c r="D17" t="str">
         <f>IF(A17="","",IFERROR(VLOOKUP(A17,Players!$A$4:$D$200,4,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="E17" t="str">
+        <v>Forward</v>
+      </c>
+      <c r="E17">
         <f>IF(A17="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A17,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v/>
-      </c>
-      <c r="F17" t="str">
+        <v>0</v>
+      </c>
+      <c r="F17">
         <f>IF(A17="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A17))</f>
-        <v/>
-      </c>
-      <c r="G17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G17">
         <f>IF(A17="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A17))</f>
-        <v/>
-      </c>
-      <c r="H17" t="str">
+        <v>0</v>
+      </c>
+      <c r="H17">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I17">
         <f>IF(A17="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A17))</f>
-        <v/>
-      </c>
-      <c r="J17" t="str">
+        <v>0</v>
+      </c>
+      <c r="J17">
         <f>IF(A17="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A17))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="str">
         <f>IF(Players!A18="","",Players!A18)</f>
-        <v/>
+        <v>P015</v>
       </c>
       <c r="B18" t="str">
         <f>IF(A18="","",IFERROR(VLOOKUP(A18,Players!$A$4:$D$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="C18" t="str">
+        <v>Oliver Broyd</v>
+      </c>
+      <c r="C18">
         <f>IF(A18="","",IFERROR(VLOOKUP(A18,Players!$A$4:$D$200,3,FALSE),""))</f>
-        <v/>
+        <v>33</v>
       </c>
       <c r="D18" t="str">
         <f>IF(A18="","",IFERROR(VLOOKUP(A18,Players!$A$4:$D$200,4,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="E18" t="str">
+        <v>Forward</v>
+      </c>
+      <c r="E18">
         <f>IF(A18="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A18,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v/>
-      </c>
-      <c r="F18" t="str">
+        <v>0</v>
+      </c>
+      <c r="F18">
         <f>IF(A18="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A18))</f>
-        <v/>
-      </c>
-      <c r="G18" t="str">
+        <v>0</v>
+      </c>
+      <c r="G18">
         <f>IF(A18="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A18))</f>
-        <v/>
-      </c>
-      <c r="H18" t="str">
+        <v>0</v>
+      </c>
+      <c r="H18">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I18" t="str">
+        <v>0</v>
+      </c>
+      <c r="I18">
         <f>IF(A18="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A18))</f>
-        <v/>
-      </c>
-      <c r="J18" t="str">
+        <v>0</v>
+      </c>
+      <c r="J18">
         <f>IF(A18="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A18))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="str">
         <f>IF(Players!A19="","",Players!A19)</f>
-        <v/>
+        <v>P016</v>
       </c>
       <c r="B19" t="str">
         <f>IF(A19="","",IFERROR(VLOOKUP(A19,Players!$A$4:$D$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="C19" t="str">
+        <v>Connor Mellett</v>
+      </c>
+      <c r="C19">
         <f>IF(A19="","",IFERROR(VLOOKUP(A19,Players!$A$4:$D$200,3,FALSE),""))</f>
-        <v/>
+        <v>37</v>
       </c>
       <c r="D19" t="str">
         <f>IF(A19="","",IFERROR(VLOOKUP(A19,Players!$A$4:$D$200,4,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="E19" t="str">
+        <v>Forward</v>
+      </c>
+      <c r="E19">
         <f>IF(A19="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A19,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v/>
-      </c>
-      <c r="F19" t="str">
+        <v>0</v>
+      </c>
+      <c r="F19">
         <f>IF(A19="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A19))</f>
-        <v/>
-      </c>
-      <c r="G19" t="str">
+        <v>0</v>
+      </c>
+      <c r="G19">
         <f>IF(A19="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A19))</f>
-        <v/>
-      </c>
-      <c r="H19" t="str">
+        <v>0</v>
+      </c>
+      <c r="H19">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I19" t="str">
+        <v>0</v>
+      </c>
+      <c r="I19">
         <f>IF(A19="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A19))</f>
-        <v/>
-      </c>
-      <c r="J19" t="str">
+        <v>0</v>
+      </c>
+      <c r="J19">
         <f>IF(A19="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A19))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="str">
         <f>IF(Players!A20="","",Players!A20)</f>
-        <v/>
+        <v>P017</v>
       </c>
       <c r="B20" t="str">
         <f>IF(A20="","",IFERROR(VLOOKUP(A20,Players!$A$4:$D$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="C20" t="str">
+        <v>Hayden Hagger</v>
+      </c>
+      <c r="C20">
         <f>IF(A20="","",IFERROR(VLOOKUP(A20,Players!$A$4:$D$200,3,FALSE),""))</f>
-        <v/>
+        <v>45</v>
       </c>
       <c r="D20" t="str">
         <f>IF(A20="","",IFERROR(VLOOKUP(A20,Players!$A$4:$D$200,4,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="E20" t="str">
+        <v>Forward</v>
+      </c>
+      <c r="E20">
         <f>IF(A20="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A20,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v/>
-      </c>
-      <c r="F20" t="str">
+        <v>0</v>
+      </c>
+      <c r="F20">
         <f>IF(A20="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A20))</f>
-        <v/>
-      </c>
-      <c r="G20" t="str">
+        <v>0</v>
+      </c>
+      <c r="G20">
         <f>IF(A20="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A20))</f>
-        <v/>
-      </c>
-      <c r="H20" t="str">
+        <v>0</v>
+      </c>
+      <c r="H20">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I20" t="str">
+        <v>0</v>
+      </c>
+      <c r="I20">
         <f>IF(A20="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A20))</f>
-        <v/>
-      </c>
-      <c r="J20" t="str">
+        <v>0</v>
+      </c>
+      <c r="J20">
         <f>IF(A20="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A20))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="str">
         <f>IF(Players!A21="","",Players!A21)</f>
-        <v/>
+        <v>P018</v>
       </c>
       <c r="B21" t="str">
         <f>IF(A21="","",IFERROR(VLOOKUP(A21,Players!$A$4:$D$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="C21" t="str">
+        <v>Sam Purcell</v>
+      </c>
+      <c r="C21">
         <f>IF(A21="","",IFERROR(VLOOKUP(A21,Players!$A$4:$D$200,3,FALSE),""))</f>
-        <v/>
+        <v>64</v>
       </c>
       <c r="D21" t="str">
         <f>IF(A21="","",IFERROR(VLOOKUP(A21,Players!$A$4:$D$200,4,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="E21" t="str">
+        <v>Forward</v>
+      </c>
+      <c r="E21">
         <f>IF(A21="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A21,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v/>
-      </c>
-      <c r="F21" t="str">
+        <v>0</v>
+      </c>
+      <c r="F21">
         <f>IF(A21="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A21))</f>
-        <v/>
-      </c>
-      <c r="G21" t="str">
+        <v>0</v>
+      </c>
+      <c r="G21">
         <f>IF(A21="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A21))</f>
-        <v/>
-      </c>
-      <c r="H21" t="str">
+        <v>0</v>
+      </c>
+      <c r="H21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I21" t="str">
+        <v>0</v>
+      </c>
+      <c r="I21">
         <f>IF(A21="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A21))</f>
-        <v/>
-      </c>
-      <c r="J21" t="str">
+        <v>0</v>
+      </c>
+      <c r="J21">
         <f>IF(A21="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A21))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="str">
         <f>IF(Players!A22="","",Players!A22)</f>
-        <v/>
+        <v>P019</v>
       </c>
       <c r="B22" t="str">
         <f>IF(A22="","",IFERROR(VLOOKUP(A22,Players!$A$4:$D$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="C22" t="str">
+        <v>Samuel Rickard</v>
+      </c>
+      <c r="C22">
         <f>IF(A22="","",IFERROR(VLOOKUP(A22,Players!$A$4:$D$200,3,FALSE),""))</f>
-        <v/>
+        <v>65</v>
       </c>
       <c r="D22" t="str">
         <f>IF(A22="","",IFERROR(VLOOKUP(A22,Players!$A$4:$D$200,4,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="E22" t="str">
+        <v>Forward</v>
+      </c>
+      <c r="E22">
         <f>IF(A22="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A22,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v/>
-      </c>
-      <c r="F22" t="str">
+        <v>0</v>
+      </c>
+      <c r="F22">
         <f>IF(A22="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A22))</f>
-        <v/>
-      </c>
-      <c r="G22" t="str">
+        <v>0</v>
+      </c>
+      <c r="G22">
         <f>IF(A22="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A22))</f>
-        <v/>
-      </c>
-      <c r="H22" t="str">
+        <v>0</v>
+      </c>
+      <c r="H22">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I22" t="str">
+        <v>0</v>
+      </c>
+      <c r="I22">
         <f>IF(A22="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A22))</f>
-        <v/>
-      </c>
-      <c r="J22" t="str">
+        <v>0</v>
+      </c>
+      <c r="J22">
         <f>IF(A22="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A22))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="str">
         <f>IF(Players!A23="","",Players!A23)</f>
-        <v/>
+        <v>P020</v>
       </c>
       <c r="B23" t="str">
         <f>IF(A23="","",IFERROR(VLOOKUP(A23,Players!$A$4:$D$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="C23" t="str">
+        <v>Oscar Lee</v>
+      </c>
+      <c r="C23">
         <f>IF(A23="","",IFERROR(VLOOKUP(A23,Players!$A$4:$D$200,3,FALSE),""))</f>
-        <v/>
+        <v>68</v>
       </c>
       <c r="D23" t="str">
         <f>IF(A23="","",IFERROR(VLOOKUP(A23,Players!$A$4:$D$200,4,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="E23" t="str">
+        <v>Forward</v>
+      </c>
+      <c r="E23">
         <f>IF(A23="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A23,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v/>
-      </c>
-      <c r="F23" t="str">
+        <v>0</v>
+      </c>
+      <c r="F23">
         <f>IF(A23="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A23))</f>
-        <v/>
-      </c>
-      <c r="G23" t="str">
+        <v>0</v>
+      </c>
+      <c r="G23">
         <f>IF(A23="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A23))</f>
-        <v/>
-      </c>
-      <c r="H23" t="str">
+        <v>0</v>
+      </c>
+      <c r="H23">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I23" t="str">
+        <v>0</v>
+      </c>
+      <c r="I23">
         <f>IF(A23="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A23))</f>
-        <v/>
-      </c>
-      <c r="J23" t="str">
+        <v>0</v>
+      </c>
+      <c r="J23">
         <f>IF(A23="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A23))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="str">
         <f>IF(Players!A24="","",Players!A24)</f>
-        <v/>
+        <v>P021</v>
       </c>
       <c r="B24" t="str">
         <f>IF(A24="","",IFERROR(VLOOKUP(A24,Players!$A$4:$D$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="C24" t="str">
+        <v>Jacob Maidment</v>
+      </c>
+      <c r="C24">
         <f>IF(A24="","",IFERROR(VLOOKUP(A24,Players!$A$4:$D$200,3,FALSE),""))</f>
-        <v/>
+        <v>89</v>
       </c>
       <c r="D24" t="str">
         <f>IF(A24="","",IFERROR(VLOOKUP(A24,Players!$A$4:$D$200,4,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="E24" t="str">
+        <v>Forward</v>
+      </c>
+      <c r="E24">
         <f>IF(A24="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A24,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v/>
-      </c>
-      <c r="F24" t="str">
+        <v>0</v>
+      </c>
+      <c r="F24">
         <f>IF(A24="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A24))</f>
-        <v/>
-      </c>
-      <c r="G24" t="str">
+        <v>0</v>
+      </c>
+      <c r="G24">
         <f>IF(A24="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A24))</f>
-        <v/>
-      </c>
-      <c r="H24" t="str">
+        <v>0</v>
+      </c>
+      <c r="H24">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I24" t="str">
+        <v>0</v>
+      </c>
+      <c r="I24">
         <f>IF(A24="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A24))</f>
-        <v/>
-      </c>
-      <c r="J24" t="str">
+        <v>0</v>
+      </c>
+      <c r="J24">
         <f>IF(A24="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A24))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E40E3CC2-8932-48A3-80C9-9D746030D9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A12AE8-F91E-45AB-B53B-845DAEFA5EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4905" yWindow="3375" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7605" yWindow="3165" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="260">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -787,6 +787,42 @@
   <si>
     <t>Jacob Maidment</t>
   </si>
+  <si>
+    <t>P022</t>
+  </si>
+  <si>
+    <t>P023</t>
+  </si>
+  <si>
+    <t>P024</t>
+  </si>
+  <si>
+    <t>P025</t>
+  </si>
+  <si>
+    <t>P026</t>
+  </si>
+  <si>
+    <t>P027</t>
+  </si>
+  <si>
+    <t>Corey Taylor</t>
+  </si>
+  <si>
+    <t>James Bryan</t>
+  </si>
+  <si>
+    <t>Josh Furnell</t>
+  </si>
+  <si>
+    <t>Josh Hickman</t>
+  </si>
+  <si>
+    <t>Ryan Wonfor</t>
+  </si>
+  <si>
+    <t>Charles Coney</t>
+  </si>
 </sst>
 </file>
 
@@ -3935,58 +3971,118 @@
       <c r="G24" s="8"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
+      <c r="A25" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="C25" s="8">
+        <v>16</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>35</v>
+      </c>
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
+      <c r="A26" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="C26" s="8">
+        <v>23</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
+      <c r="A27" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="C27" s="8">
+        <v>33</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
+      <c r="A28" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C28" s="8">
+        <v>40</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
+      <c r="A29" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="C29" s="8">
+        <v>77</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
+      <c r="A30" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="C30" s="8">
+        <v>88</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2"/>
@@ -24067,253 +24163,253 @@
     <row r="25" spans="1:10">
       <c r="A25" t="str">
         <f>IF(Players!A25="","",Players!A25)</f>
-        <v/>
+        <v>P022</v>
       </c>
       <c r="B25" t="str">
         <f>IF(A25="","",IFERROR(VLOOKUP(A25,Players!$A$4:$D$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="C25" t="str">
+        <v>Corey Taylor</v>
+      </c>
+      <c r="C25">
         <f>IF(A25="","",IFERROR(VLOOKUP(A25,Players!$A$4:$D$200,3,FALSE),""))</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="D25" t="str">
         <f>IF(A25="","",IFERROR(VLOOKUP(A25,Players!$A$4:$D$200,4,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="E25" t="str">
+        <v>Defence</v>
+      </c>
+      <c r="E25">
         <f>IF(A25="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A25,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v/>
-      </c>
-      <c r="F25" t="str">
+        <v>0</v>
+      </c>
+      <c r="F25">
         <f>IF(A25="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A25))</f>
-        <v/>
-      </c>
-      <c r="G25" t="str">
+        <v>0</v>
+      </c>
+      <c r="G25">
         <f>IF(A25="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A25))</f>
-        <v/>
-      </c>
-      <c r="H25" t="str">
+        <v>0</v>
+      </c>
+      <c r="H25">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I25" t="str">
+        <v>0</v>
+      </c>
+      <c r="I25">
         <f>IF(A25="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A25))</f>
-        <v/>
-      </c>
-      <c r="J25" t="str">
+        <v>0</v>
+      </c>
+      <c r="J25">
         <f>IF(A25="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A25))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="str">
         <f>IF(Players!A26="","",Players!A26)</f>
-        <v/>
+        <v>P023</v>
       </c>
       <c r="B26" t="str">
         <f>IF(A26="","",IFERROR(VLOOKUP(A26,Players!$A$4:$D$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="C26" t="str">
+        <v>James Bryan</v>
+      </c>
+      <c r="C26">
         <f>IF(A26="","",IFERROR(VLOOKUP(A26,Players!$A$4:$D$200,3,FALSE),""))</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="D26" t="str">
         <f>IF(A26="","",IFERROR(VLOOKUP(A26,Players!$A$4:$D$200,4,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="E26" t="str">
+        <v>Defence</v>
+      </c>
+      <c r="E26">
         <f>IF(A26="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A26,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v/>
-      </c>
-      <c r="F26" t="str">
+        <v>0</v>
+      </c>
+      <c r="F26">
         <f>IF(A26="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A26))</f>
-        <v/>
-      </c>
-      <c r="G26" t="str">
+        <v>0</v>
+      </c>
+      <c r="G26">
         <f>IF(A26="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A26))</f>
-        <v/>
-      </c>
-      <c r="H26" t="str">
+        <v>0</v>
+      </c>
+      <c r="H26">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I26" t="str">
+        <v>0</v>
+      </c>
+      <c r="I26">
         <f>IF(A26="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A26))</f>
-        <v/>
-      </c>
-      <c r="J26" t="str">
+        <v>0</v>
+      </c>
+      <c r="J26">
         <f>IF(A26="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A26))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="str">
         <f>IF(Players!A27="","",Players!A27)</f>
-        <v/>
+        <v>P024</v>
       </c>
       <c r="B27" t="str">
         <f>IF(A27="","",IFERROR(VLOOKUP(A27,Players!$A$4:$D$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="C27" t="str">
+        <v>Josh Furnell</v>
+      </c>
+      <c r="C27">
         <f>IF(A27="","",IFERROR(VLOOKUP(A27,Players!$A$4:$D$200,3,FALSE),""))</f>
-        <v/>
+        <v>33</v>
       </c>
       <c r="D27" t="str">
         <f>IF(A27="","",IFERROR(VLOOKUP(A27,Players!$A$4:$D$200,4,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="E27" t="str">
+        <v>Defence</v>
+      </c>
+      <c r="E27">
         <f>IF(A27="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A27,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v/>
-      </c>
-      <c r="F27" t="str">
+        <v>0</v>
+      </c>
+      <c r="F27">
         <f>IF(A27="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A27))</f>
-        <v/>
-      </c>
-      <c r="G27" t="str">
+        <v>0</v>
+      </c>
+      <c r="G27">
         <f>IF(A27="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A27))</f>
-        <v/>
-      </c>
-      <c r="H27" t="str">
+        <v>0</v>
+      </c>
+      <c r="H27">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I27" t="str">
+        <v>0</v>
+      </c>
+      <c r="I27">
         <f>IF(A27="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A27))</f>
-        <v/>
-      </c>
-      <c r="J27" t="str">
+        <v>0</v>
+      </c>
+      <c r="J27">
         <f>IF(A27="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A27))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="str">
         <f>IF(Players!A28="","",Players!A28)</f>
-        <v/>
+        <v>P025</v>
       </c>
       <c r="B28" t="str">
         <f>IF(A28="","",IFERROR(VLOOKUP(A28,Players!$A$4:$D$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="C28" t="str">
+        <v>Josh Hickman</v>
+      </c>
+      <c r="C28">
         <f>IF(A28="","",IFERROR(VLOOKUP(A28,Players!$A$4:$D$200,3,FALSE),""))</f>
-        <v/>
+        <v>40</v>
       </c>
       <c r="D28" t="str">
         <f>IF(A28="","",IFERROR(VLOOKUP(A28,Players!$A$4:$D$200,4,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="E28" t="str">
+        <v>Defence</v>
+      </c>
+      <c r="E28">
         <f>IF(A28="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A28,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v/>
-      </c>
-      <c r="F28" t="str">
+        <v>0</v>
+      </c>
+      <c r="F28">
         <f>IF(A28="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A28))</f>
-        <v/>
-      </c>
-      <c r="G28" t="str">
+        <v>0</v>
+      </c>
+      <c r="G28">
         <f>IF(A28="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A28))</f>
-        <v/>
-      </c>
-      <c r="H28" t="str">
+        <v>0</v>
+      </c>
+      <c r="H28">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I28" t="str">
+        <v>0</v>
+      </c>
+      <c r="I28">
         <f>IF(A28="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A28))</f>
-        <v/>
-      </c>
-      <c r="J28" t="str">
+        <v>0</v>
+      </c>
+      <c r="J28">
         <f>IF(A28="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A28))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="str">
         <f>IF(Players!A29="","",Players!A29)</f>
-        <v/>
+        <v>P026</v>
       </c>
       <c r="B29" t="str">
         <f>IF(A29="","",IFERROR(VLOOKUP(A29,Players!$A$4:$D$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="C29" t="str">
+        <v>Ryan Wonfor</v>
+      </c>
+      <c r="C29">
         <f>IF(A29="","",IFERROR(VLOOKUP(A29,Players!$A$4:$D$200,3,FALSE),""))</f>
-        <v/>
+        <v>77</v>
       </c>
       <c r="D29" t="str">
         <f>IF(A29="","",IFERROR(VLOOKUP(A29,Players!$A$4:$D$200,4,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="E29" t="str">
+        <v>Defence</v>
+      </c>
+      <c r="E29">
         <f>IF(A29="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A29,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v/>
-      </c>
-      <c r="F29" t="str">
+        <v>0</v>
+      </c>
+      <c r="F29">
         <f>IF(A29="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A29))</f>
-        <v/>
-      </c>
-      <c r="G29" t="str">
+        <v>0</v>
+      </c>
+      <c r="G29">
         <f>IF(A29="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A29))</f>
-        <v/>
-      </c>
-      <c r="H29" t="str">
+        <v>0</v>
+      </c>
+      <c r="H29">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I29" t="str">
+        <v>0</v>
+      </c>
+      <c r="I29">
         <f>IF(A29="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A29))</f>
-        <v/>
-      </c>
-      <c r="J29" t="str">
+        <v>0</v>
+      </c>
+      <c r="J29">
         <f>IF(A29="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A29))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="str">
         <f>IF(Players!A30="","",Players!A30)</f>
-        <v/>
+        <v>P027</v>
       </c>
       <c r="B30" t="str">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Players!$A$4:$D$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="C30" t="str">
+        <v>Charles Coney</v>
+      </c>
+      <c r="C30">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Players!$A$4:$D$200,3,FALSE),""))</f>
-        <v/>
+        <v>88</v>
       </c>
       <c r="D30" t="str">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Players!$A$4:$D$200,4,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="E30" t="str">
+        <v>Defence</v>
+      </c>
+      <c r="E30">
         <f>IF(A30="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A30,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v/>
-      </c>
-      <c r="F30" t="str">
+        <v>0</v>
+      </c>
+      <c r="F30">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
-        <v/>
-      </c>
-      <c r="G30" t="str">
+        <v>0</v>
+      </c>
+      <c r="G30">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
-        <v/>
-      </c>
-      <c r="H30" t="str">
+        <v>0</v>
+      </c>
+      <c r="H30">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I30" t="str">
+        <v>0</v>
+      </c>
+      <c r="I30">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
-        <v/>
-      </c>
-      <c r="J30" t="str">
+        <v>0</v>
+      </c>
+      <c r="J30">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A12AE8-F91E-45AB-B53B-845DAEFA5EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349D8F48-AD85-4D88-8922-EE07FCD805AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7605" yWindow="3165" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="260">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -9689,16 +9689,16 @@
   <dimension ref="A1:J500"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="55" customWidth="1"/>
+    <col min="1" max="1" width="23.75" customWidth="1"/>
     <col min="2" max="2" width="7.375" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="7.5" customWidth="1"/>
-    <col min="5" max="5" width="4.75" customWidth="1"/>
-    <col min="6" max="6" width="5.625" customWidth="1"/>
-    <col min="7" max="7" width="5.25" customWidth="1"/>
-    <col min="8" max="8" width="3.625" customWidth="1"/>
-    <col min="9" max="9" width="2.875" customWidth="1"/>
-    <col min="10" max="10" width="5" customWidth="1"/>
+    <col min="4" max="4" width="11.25" customWidth="1"/>
+    <col min="5" max="5" width="6.5" customWidth="1"/>
+    <col min="6" max="6" width="7.625" customWidth="1"/>
+    <col min="7" max="7" width="6.375" customWidth="1"/>
+    <col min="8" max="8" width="5" customWidth="1"/>
+    <col min="9" max="9" width="3.5" customWidth="1"/>
+    <col min="10" max="10" width="7.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
@@ -9748,20 +9748,32 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
+      <c r="A4" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>57</v>
+      </c>
       <c r="C4" s="11" t="str">
         <f>IF(B4="","",IFERROR(VLOOKUP(B4,Players!$A$4:$B$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="11" t="str">
+        <v>Sam Peters</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="8">
+        <v>1</v>
+      </c>
+      <c r="F4" s="8">
+        <v>1</v>
+      </c>
+      <c r="G4" s="11">
         <f t="shared" ref="G4:G67" si="0">IF(AND(E4="",F4=""),"",SUM(E4:F4))</f>
-        <v/>
-      </c>
-      <c r="H4" s="8"/>
+        <v>2</v>
+      </c>
+      <c r="H4" s="8">
+        <v>2</v>
+      </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
     </row>
@@ -23260,23 +23272,23 @@
       </c>
       <c r="E4" s="13">
         <f>IF(A4="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A4,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="13">
         <f>IF(A4="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A4))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="13">
         <f>IF(A4="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A4))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="13">
         <f t="shared" ref="H4:H35" si="0">IF(A4="","",F4+G4)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" s="13">
         <f>IF(A4="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A4))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="13">
         <f>IF(A4="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A4))</f>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349D8F48-AD85-4D88-8922-EE07FCD805AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{94DD3027-AC4A-4501-886E-F93BFC0C04B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="261">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -149,6 +149,9 @@
     <t>Milton Keynes</t>
   </si>
   <si>
+    <t>https://thundericehockey.co.uk/</t>
+  </si>
+  <si>
     <t>Yes</t>
   </si>
   <si>
@@ -173,13 +176,13 @@
     <t>Romford Buccaneers</t>
   </si>
   <si>
+    <t>Romford</t>
+  </si>
+  <si>
     <t>romford.png</t>
   </si>
   <si>
     <t>Sapphire Ice and Leisure Centre</t>
-  </si>
-  <si>
-    <t>Romford</t>
   </si>
   <si>
     <t>T004</t>
@@ -197,229 +200,7 @@
     <t>Riverside Leisure Centre</t>
   </si>
   <si>
-    <t>Player ID</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Number</t>
-  </si>
-  <si>
-    <t>Position</t>
-  </si>
-  <si>
-    <t>Photo / URL</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>P001</t>
-  </si>
-  <si>
-    <t>Sam Peters</t>
-  </si>
-  <si>
-    <t>Forward</t>
-  </si>
-  <si>
-    <t>P002</t>
-  </si>
-  <si>
-    <t>Marks Kanins</t>
-  </si>
-  <si>
-    <t>P003</t>
-  </si>
-  <si>
-    <t>Dominic Wealthall</t>
-  </si>
-  <si>
-    <t>Defence</t>
-  </si>
-  <si>
-    <t>Captain</t>
-  </si>
-  <si>
-    <t>P004</t>
-  </si>
-  <si>
-    <t>Aaron Burton</t>
-  </si>
-  <si>
-    <t>Netminder</t>
-  </si>
-  <si>
-    <t>Game ID</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Face-off</t>
-  </si>
-  <si>
-    <t>Opponent ID</t>
-  </si>
-  <si>
-    <t>H/A</t>
-  </si>
-  <si>
-    <t>Competition</t>
-  </si>
-  <si>
-    <t>Thunder Score</t>
-  </si>
-  <si>
-    <t>Opponent Score</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>OT/SO?</t>
-  </si>
-  <si>
-    <t>Venue</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>G001</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Pre-season</t>
-  </si>
-  <si>
-    <t>Upcoming</t>
-  </si>
-  <si>
-    <t>G002</t>
-  </si>
-  <si>
-    <t>G003</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>League</t>
-  </si>
-  <si>
-    <t>Player Game Stats – one row per player per game</t>
-  </si>
-  <si>
-    <t>Player Name</t>
-  </si>
-  <si>
-    <t>Dressed?</t>
-  </si>
-  <si>
-    <t>Goals</t>
-  </si>
-  <si>
-    <t>Assists</t>
-  </si>
-  <si>
-    <t>Points</t>
-  </si>
-  <si>
-    <t>PIM</t>
-  </si>
-  <si>
-    <t>+/-</t>
-  </si>
-  <si>
-    <t>Netminder Game Stats</t>
-  </si>
-  <si>
-    <t>Minutes</t>
-  </si>
-  <si>
-    <t>Shots Against</t>
-  </si>
-  <si>
-    <t>Goals Against</t>
-  </si>
-  <si>
-    <t>Saves</t>
-  </si>
-  <si>
-    <t>Save %</t>
-  </si>
-  <si>
-    <t>Shutout?</t>
-  </si>
-  <si>
-    <t>Decision</t>
-  </si>
-  <si>
-    <t>MK Thunder Season Player Totals</t>
-  </si>
-  <si>
-    <t>Team KPIs</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Player</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>Pos</t>
-  </si>
-  <si>
-    <t>GP</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>PTS</t>
-  </si>
-  <si>
-    <t>Games entered</t>
-  </si>
-  <si>
-    <t>Goals scored</t>
-  </si>
-  <si>
-    <t>Goals against</t>
-  </si>
-  <si>
-    <t>Wins</t>
-  </si>
-  <si>
-    <t>Losses</t>
-  </si>
-  <si>
     <t>T005</t>
-  </si>
-  <si>
-    <t>Guildford Phoenix</t>
-  </si>
-  <si>
-    <t>Guildford</t>
-  </si>
-  <si>
-    <t>Guildford Spectrum</t>
-  </si>
-  <si>
-    <t>G004</t>
-  </si>
-  <si>
-    <t>guildford.png</t>
-  </si>
-  <si>
-    <t>https://thundericehockey.co.uk/</t>
   </si>
   <si>
     <t>Invicta Mustangs</t>
@@ -438,6 +219,18 @@
   </si>
   <si>
     <t>T006</t>
+  </si>
+  <si>
+    <t>Guildford Phoenix</t>
+  </si>
+  <si>
+    <t>Guildford</t>
+  </si>
+  <si>
+    <t>guildford.png</t>
+  </si>
+  <si>
+    <t>Guildford Spectrum</t>
   </si>
   <si>
     <t>T007</t>
@@ -545,6 +338,9 @@
     <t>Solent</t>
   </si>
   <si>
+    <t>solent.png</t>
+  </si>
+  <si>
     <t>Planet Ice Gosport</t>
   </si>
   <si>
@@ -581,7 +377,298 @@
     <t>Planet Ice Basingstoke</t>
   </si>
   <si>
+    <t>Player ID</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>Position</t>
+  </si>
+  <si>
+    <t>Photo / URL</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>P001</t>
+  </si>
+  <si>
+    <t>Sam Peters</t>
+  </si>
+  <si>
+    <t>Forward</t>
+  </si>
+  <si>
+    <t>Peters.png</t>
+  </si>
+  <si>
+    <t>P002</t>
+  </si>
+  <si>
+    <t>Marks Kanins</t>
+  </si>
+  <si>
+    <t>marks.png</t>
+  </si>
+  <si>
+    <t>P003</t>
+  </si>
+  <si>
+    <t>Dominic Wealthall</t>
+  </si>
+  <si>
+    <t>Defence</t>
+  </si>
+  <si>
+    <t>dom.png</t>
+  </si>
+  <si>
+    <t>Captain</t>
+  </si>
+  <si>
+    <t>P004</t>
+  </si>
+  <si>
+    <t>Aaron Burton</t>
+  </si>
+  <si>
+    <t>Netminder</t>
+  </si>
+  <si>
+    <t>arron.png</t>
+  </si>
+  <si>
+    <t>P005</t>
+  </si>
+  <si>
+    <t>Charlie Russell</t>
+  </si>
+  <si>
+    <t>russell.png</t>
+  </si>
+  <si>
+    <t>P006</t>
+  </si>
+  <si>
+    <t>Lewis Smith</t>
+  </si>
+  <si>
+    <t>smith.png</t>
+  </si>
+  <si>
+    <t>P007</t>
+  </si>
+  <si>
+    <t>Robert Oxley</t>
+  </si>
+  <si>
+    <t>rob.png</t>
+  </si>
+  <si>
+    <t>P008</t>
+  </si>
+  <si>
+    <t>Madi Wright</t>
+  </si>
+  <si>
+    <t>madi.png</t>
+  </si>
+  <si>
+    <t>P009</t>
+  </si>
+  <si>
+    <t>Lizzie Nowik</t>
+  </si>
+  <si>
+    <t>lizzie.png</t>
+  </si>
+  <si>
+    <t>P010</t>
+  </si>
+  <si>
+    <t>Nicole Jackson</t>
+  </si>
+  <si>
+    <t>nicole.png</t>
+  </si>
+  <si>
+    <t>P011</t>
+  </si>
+  <si>
+    <t>Xander Robinson</t>
+  </si>
+  <si>
+    <t>P012</t>
+  </si>
+  <si>
+    <t>Joshua Blackwood</t>
+  </si>
+  <si>
+    <t>P013</t>
+  </si>
+  <si>
+    <t>Harry MacGarvery</t>
+  </si>
+  <si>
+    <t>P014</t>
+  </si>
+  <si>
+    <t>Chalie Conroy</t>
+  </si>
+  <si>
+    <t>P015</t>
+  </si>
+  <si>
+    <t>Oliver Broyd</t>
+  </si>
+  <si>
+    <t>P016</t>
+  </si>
+  <si>
+    <t>Connor Mellett</t>
+  </si>
+  <si>
+    <t>P017</t>
+  </si>
+  <si>
+    <t>Hayden Hagger</t>
+  </si>
+  <si>
+    <t>P018</t>
+  </si>
+  <si>
+    <t>Sam Purcell</t>
+  </si>
+  <si>
+    <t>P019</t>
+  </si>
+  <si>
+    <t>Samuel Rickard</t>
+  </si>
+  <si>
+    <t>P020</t>
+  </si>
+  <si>
+    <t>Oscar Lee</t>
+  </si>
+  <si>
+    <t>P021</t>
+  </si>
+  <si>
+    <t>Jacob Maidment</t>
+  </si>
+  <si>
+    <t>P022</t>
+  </si>
+  <si>
+    <t>Corey Taylor</t>
+  </si>
+  <si>
+    <t>P023</t>
+  </si>
+  <si>
+    <t>James Bryan</t>
+  </si>
+  <si>
+    <t>P024</t>
+  </si>
+  <si>
+    <t>Josh Furnell</t>
+  </si>
+  <si>
+    <t>P025</t>
+  </si>
+  <si>
+    <t>Josh Hickman</t>
+  </si>
+  <si>
+    <t>P026</t>
+  </si>
+  <si>
+    <t>Ryan Wonfor</t>
+  </si>
+  <si>
+    <t>P027</t>
+  </si>
+  <si>
+    <t>Charles Coney</t>
+  </si>
+  <si>
+    <t>Game ID</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Face-off</t>
+  </si>
+  <si>
+    <t>Opponent ID</t>
+  </si>
+  <si>
+    <t>H/A</t>
+  </si>
+  <si>
+    <t>Competition</t>
+  </si>
+  <si>
+    <t>Thunder Score</t>
+  </si>
+  <si>
+    <t>Opponent Score</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>OT/SO?</t>
+  </si>
+  <si>
+    <t>Venue</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>G001</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Pre-season</t>
+  </si>
+  <si>
+    <t>Upcoming</t>
+  </si>
+  <si>
+    <t>G002</t>
+  </si>
+  <si>
+    <t>G003</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>League/Cup</t>
+  </si>
+  <si>
+    <t>Planet Ice Milton Keynes</t>
+  </si>
+  <si>
+    <t>G004</t>
+  </si>
+  <si>
     <t>G005</t>
+  </si>
+  <si>
+    <t>League</t>
   </si>
   <si>
     <t>G006</t>
@@ -593,16 +680,10 @@
     <t>G008</t>
   </si>
   <si>
-    <t>Planet Ice Milton Keynes</t>
-  </si>
-  <si>
     <t>G009</t>
   </si>
   <si>
     <t>G010</t>
-  </si>
-  <si>
-    <t>solent.png</t>
   </si>
   <si>
     <t>G011</t>
@@ -653,175 +734,97 @@
     <t>G026</t>
   </si>
   <si>
-    <t>P005</t>
+    <t>Player Game Stats – one row per player per game</t>
   </si>
   <si>
-    <t>Charlie Russell</t>
+    <t>Player Name</t>
   </si>
   <si>
-    <t>P006</t>
+    <t>Dressed?</t>
   </si>
   <si>
-    <t>Lewis Smith</t>
+    <t>Goals</t>
   </si>
   <si>
-    <t>Peters.png</t>
+    <t>Assists</t>
   </si>
   <si>
-    <t>League/Cup</t>
+    <t>Points</t>
   </si>
   <si>
-    <t>russell.png</t>
+    <t>PIM</t>
   </si>
   <si>
-    <t>arron.png</t>
+    <t>+/-</t>
   </si>
   <si>
-    <t>marks.png</t>
+    <t>Netminder Game Stats</t>
   </si>
   <si>
-    <t>dom.png</t>
+    <t>Minutes</t>
   </si>
   <si>
-    <t>smith.png</t>
+    <t>Shots Against</t>
   </si>
   <si>
-    <t>P007</t>
+    <t>Goals Against</t>
   </si>
   <si>
-    <t>Robert Oxley</t>
+    <t>Saves</t>
   </si>
   <si>
-    <t>rob.png</t>
+    <t>Save %</t>
   </si>
   <si>
-    <t>P008</t>
+    <t>Shutout?</t>
   </si>
   <si>
-    <t>Madi Wright</t>
+    <t>Decision</t>
   </si>
   <si>
-    <t>madi.png</t>
+    <t>Aaron burton</t>
   </si>
   <si>
-    <t>P009</t>
+    <t>MK Thunder Season Player Totals</t>
   </si>
   <si>
-    <t>P010</t>
+    <t>Team KPIs</t>
   </si>
   <si>
-    <t>Lizzie Nowik</t>
+    <t>Value</t>
   </si>
   <si>
-    <t>lizzie.png</t>
+    <t>Player</t>
   </si>
   <si>
-    <t>Nicole Jackson</t>
+    <t>#</t>
   </si>
   <si>
-    <t>nicole.png</t>
+    <t>Pos</t>
   </si>
   <si>
-    <t>P011</t>
+    <t>GP</t>
   </si>
   <si>
-    <t>Xander Robinson</t>
+    <t>G</t>
   </si>
   <si>
-    <t>P012</t>
+    <t>PTS</t>
   </si>
   <si>
-    <t>Joshua Blackwood</t>
+    <t>Games entered</t>
   </si>
   <si>
-    <t>P013</t>
+    <t>Goals scored</t>
   </si>
   <si>
-    <t>P014</t>
+    <t>Goals against</t>
   </si>
   <si>
-    <t>P015</t>
+    <t>Wins</t>
   </si>
   <si>
-    <t>P016</t>
-  </si>
-  <si>
-    <t>P017</t>
-  </si>
-  <si>
-    <t>P018</t>
-  </si>
-  <si>
-    <t>P019</t>
-  </si>
-  <si>
-    <t>P020</t>
-  </si>
-  <si>
-    <t>P021</t>
-  </si>
-  <si>
-    <t>Harry MacGarvery</t>
-  </si>
-  <si>
-    <t>Chalie Conroy</t>
-  </si>
-  <si>
-    <t>Oliver Broyd</t>
-  </si>
-  <si>
-    <t>Connor Mellett</t>
-  </si>
-  <si>
-    <t>Hayden Hagger</t>
-  </si>
-  <si>
-    <t>Sam Purcell</t>
-  </si>
-  <si>
-    <t>Samuel Rickard</t>
-  </si>
-  <si>
-    <t>Oscar Lee</t>
-  </si>
-  <si>
-    <t>Jacob Maidment</t>
-  </si>
-  <si>
-    <t>P022</t>
-  </si>
-  <si>
-    <t>P023</t>
-  </si>
-  <si>
-    <t>P024</t>
-  </si>
-  <si>
-    <t>P025</t>
-  </si>
-  <si>
-    <t>P026</t>
-  </si>
-  <si>
-    <t>P027</t>
-  </si>
-  <si>
-    <t>Corey Taylor</t>
-  </si>
-  <si>
-    <t>James Bryan</t>
-  </si>
-  <si>
-    <t>Josh Furnell</t>
-  </si>
-  <si>
-    <t>Josh Hickman</t>
-  </si>
-  <si>
-    <t>Ryan Wonfor</t>
-  </si>
-  <si>
-    <t>Charles Coney</t>
+    <t>Losses</t>
   </si>
 </sst>
 </file>
@@ -912,7 +915,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -921,9 +924,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -934,6 +934,10 @@
     <xf numFmtId="165" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1158,14 +1162,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="3" spans="1:6" ht="30">
       <c r="A3" s="1" t="s">
@@ -1266,403 +1270,403 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="6"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="14"/>
     </row>
     <row r="3" spans="1:8" ht="15">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="H4" s="8" t="s">
+      <c r="G4" s="7" t="s">
         <v>35</v>
       </c>
+      <c r="H4" s="7" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="B6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8" t="s">
-        <v>35</v>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8" t="s">
-        <v>35</v>
+      <c r="E7" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8" t="s">
-        <v>35</v>
+      <c r="A8" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8" t="s">
-        <v>35</v>
+      <c r="A9" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8" t="s">
-        <v>35</v>
+      <c r="A10" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8" t="s">
-        <v>35</v>
+      <c r="A11" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8" t="s">
-        <v>35</v>
+      <c r="A12" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8" t="s">
-        <v>35</v>
+      <c r="A13" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8" t="s">
-        <v>35</v>
+      <c r="A14" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8" t="s">
-        <v>35</v>
+      <c r="A15" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8" t="s">
-        <v>35</v>
+      <c r="A16" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8" t="s">
-        <v>35</v>
+      <c r="A17" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8" t="s">
-        <v>35</v>
+      <c r="A18" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -3516,573 +3520,573 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="3" spans="1:7" ht="30">
-      <c r="A3" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="7" t="s">
+      <c r="A3" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>56</v>
+      <c r="F3" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="8">
+      <c r="A4" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="7">
         <v>9</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="G4" s="8"/>
+      <c r="D4" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="8">
+      <c r="A5" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C5" s="7">
         <v>97</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="G5" s="8"/>
+      <c r="D5" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="8">
+      <c r="A6" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" s="7">
         <v>74</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7" s="7">
+        <v>29</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G7" s="7"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C8" s="7">
+        <v>12</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G8" s="7"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C9" s="7">
+        <v>13</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="G9" s="7"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10" s="7">
+        <v>5</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="G10" s="7"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C11" s="7">
+        <v>10</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="G11" s="7"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C12" s="7">
+        <v>2</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G12" s="7"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C13" s="7">
+        <v>86</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C14" s="7">
+        <v>14</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C15" s="7">
+        <v>18</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="C16" s="7">
+        <v>22</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C17" s="7">
+        <v>24</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C18" s="7">
+        <v>33</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C19" s="7">
+        <v>37</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C20" s="7">
+        <v>45</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="C21" s="7">
         <v>64</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="G6" s="8" t="s">
+      <c r="D21" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="C22" s="7">
         <v>65</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="8">
-        <v>29</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="D22" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="C23" s="7">
         <v>68</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="G7" s="8"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="C8" s="8">
-        <v>12</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="G8" s="8"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="C9" s="8">
-        <v>13</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="G9" s="8"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="C10" s="8">
-        <v>5</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="G10" s="8"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="C11" s="8">
-        <v>10</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="G11" s="8"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="C12" s="8">
-        <v>2</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="G12" s="8"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="C13" s="8">
-        <v>86</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="G13" s="8"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="C14" s="8">
-        <v>14</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="C15" s="8">
-        <v>18</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="C16" s="8">
-        <v>22</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="C17" s="8">
-        <v>24</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="C18" s="8">
+      <c r="D23" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C24" s="7">
+        <v>89</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="C25" s="7">
+        <v>16</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="C26" s="7">
+        <v>23</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C27" s="7">
         <v>33</v>
       </c>
-      <c r="D18" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="C19" s="8">
-        <v>37</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="C20" s="8">
-        <v>45</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="C21" s="8">
-        <v>64</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="C22" s="8">
-        <v>65</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="C23" s="8">
-        <v>68</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="C24" s="8">
-        <v>89</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="C25" s="8">
-        <v>16</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="C26" s="8">
-        <v>23</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="C27" s="8">
-        <v>33</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
+      <c r="D27" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="C28" s="8">
+      <c r="A28" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C28" s="7">
         <v>40</v>
       </c>
-      <c r="D28" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
+      <c r="D28" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="C29" s="8">
+      <c r="A29" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C29" s="7">
         <v>77</v>
       </c>
-      <c r="D29" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
+      <c r="D29" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="C30" s="8">
+      <c r="A30" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="C30" s="7">
         <v>88</v>
       </c>
-      <c r="D30" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
+      <c r="D30" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2"/>
@@ -5651,944 +5655,944 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
     </row>
     <row r="2" spans="1:13"/>
     <row r="3" spans="1:13" ht="30">
-      <c r="A3" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D3" s="7" t="s">
+      <c r="A3" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="B4" s="8">
+        <v>46264</v>
+      </c>
+      <c r="C4" s="9">
+        <v>0.71875</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="10" t="str">
+        <f t="shared" ref="I4:I35" si="0">IF(OR(G4="",H4=""),"",IF(G4&gt;H4,"W",IF(G4&lt;H4,"L","T")))</f>
+        <v/>
+      </c>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="M4" s="7"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="B5" s="8">
+        <v>46270</v>
+      </c>
+      <c r="C5" s="9">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="M5" s="7"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B6" s="8">
+        <v>46278</v>
+      </c>
+      <c r="C6" s="9">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="M6" s="7"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="B7" s="8">
+        <v>46284</v>
+      </c>
+      <c r="C7" s="9">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="M7" s="7"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B8" s="8">
+        <v>46285</v>
+      </c>
+      <c r="C8" s="9">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="M8" s="7"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="B9" s="8">
+        <v>46291</v>
+      </c>
+      <c r="C9" s="9">
+        <v>0.78125</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="M9" s="7"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="B10" s="8">
+        <v>46298</v>
+      </c>
+      <c r="C10" s="9">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="M10" s="7"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="B11" s="8">
+        <v>46306</v>
+      </c>
+      <c r="C11" s="9">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="M11" s="7"/>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="B12" s="8">
+        <v>46312</v>
+      </c>
+      <c r="C12" s="9">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="M12" s="7"/>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="B13" s="8">
+        <v>46320</v>
+      </c>
+      <c r="C13" s="9">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="M13" s="7"/>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B14" s="8">
+        <v>46327</v>
+      </c>
+      <c r="C14" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="M14" s="7"/>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B15" s="8">
+        <v>46334</v>
+      </c>
+      <c r="C15" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="M15" s="7"/>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B16" s="8">
+        <v>46340</v>
+      </c>
+      <c r="C16" s="9">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="M16" s="7"/>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="B17" s="8">
+        <v>46341</v>
+      </c>
+      <c r="C17" s="9">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="M17" s="7"/>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="B18" s="8">
+        <v>46354</v>
+      </c>
+      <c r="C18" s="9">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="M18" s="7"/>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="B19" s="8">
+        <v>46355</v>
+      </c>
+      <c r="C19" s="9">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="M19" s="7"/>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B20" s="8">
+        <v>46368</v>
+      </c>
+      <c r="C20" s="9">
+        <v>0.8125</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="M20" s="7"/>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="B21" s="8">
+        <v>46369</v>
+      </c>
+      <c r="C21" s="9">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="M21" s="7"/>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B22" s="8">
+        <v>46376</v>
+      </c>
+      <c r="C22" s="9">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="M22" s="7"/>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="B23" s="8">
+        <v>46397</v>
+      </c>
+      <c r="C23" s="9">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="M23" s="7"/>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="B24" s="8">
+        <v>46417</v>
+      </c>
+      <c r="C24" s="9">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="M24" s="7"/>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B25" s="8">
+        <v>46425</v>
+      </c>
+      <c r="C25" s="9">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="M25" s="7"/>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="B26" s="8">
+        <v>46446</v>
+      </c>
+      <c r="C26" s="9">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="M26" s="7"/>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B27" s="8">
+        <v>46452</v>
+      </c>
+      <c r="C27" s="9">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="B4" s="9">
-        <v>46264</v>
-      </c>
-      <c r="C4" s="10">
-        <v>0.71875</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="11" t="str">
-        <f t="shared" ref="I4:I35" si="0">IF(OR(G4="",H4=""),"",IF(G4&gt;H4,"W",IF(G4&lt;H4,"L","T")))</f>
-        <v/>
-      </c>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M4" s="8"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B5" s="9">
-        <v>46270</v>
-      </c>
-      <c r="C5" s="10">
-        <v>0.76041666666666663</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="11" t="str">
+      <c r="L27" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="M27" s="7"/>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="B28" s="8">
+        <v>46459</v>
+      </c>
+      <c r="C28" s="9">
+        <v>0.78125</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M5" s="8"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B6" s="9">
-        <v>46278</v>
-      </c>
-      <c r="C6" s="10">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F6" s="8" t="s">
+      <c r="J28" s="7"/>
+      <c r="K28" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="M28" s="7"/>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46467</v>
+      </c>
+      <c r="C29" s="9">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F29" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="11" t="str">
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M6" s="8"/>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="B7" s="9">
-        <v>46284</v>
-      </c>
-      <c r="C7" s="10">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M7" s="8"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="B8" s="9">
-        <v>46285</v>
-      </c>
-      <c r="C8" s="10">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M8" s="8"/>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="B9" s="9">
-        <v>46291</v>
-      </c>
-      <c r="C9" s="10">
-        <v>0.78125</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M9" s="8"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="B10" s="9">
-        <v>46298</v>
-      </c>
-      <c r="C10" s="10">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M10" s="8"/>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="B11" s="9">
-        <v>46306</v>
-      </c>
-      <c r="C11" s="10">
-        <v>0.83333333333333304</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M11" s="8"/>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="B12" s="9">
-        <v>46312</v>
-      </c>
-      <c r="C12" s="10">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M12" s="8"/>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="B13" s="9">
-        <v>46320</v>
-      </c>
-      <c r="C13" s="10">
-        <v>0.77083333333333304</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M13" s="8"/>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="B14" s="9">
-        <v>46327</v>
-      </c>
-      <c r="C14" s="10">
-        <v>0.75</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M14" s="8"/>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="B15" s="9">
-        <v>46334</v>
-      </c>
-      <c r="C15" s="10">
-        <v>0.75</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M15" s="8"/>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="B16" s="9">
-        <v>46340</v>
-      </c>
-      <c r="C16" s="10">
-        <v>0.79166666666666696</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M16" s="8"/>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="B17" s="9">
-        <v>46341</v>
-      </c>
-      <c r="C17" s="10">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M17" s="8"/>
-    </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="B18" s="9">
-        <v>46354</v>
-      </c>
-      <c r="C18" s="10">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M18" s="8"/>
-    </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="B19" s="9">
-        <v>46355</v>
-      </c>
-      <c r="C19" s="10">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M19" s="8"/>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="B20" s="9">
-        <v>46368</v>
-      </c>
-      <c r="C20" s="10">
-        <v>0.8125</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M20" s="8"/>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="B21" s="9">
-        <v>46369</v>
-      </c>
-      <c r="C21" s="10">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M21" s="8"/>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="B22" s="9">
-        <v>46376</v>
-      </c>
-      <c r="C22" s="10">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M22" s="8"/>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="B23" s="9">
-        <v>46397</v>
-      </c>
-      <c r="C23" s="10">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M23" s="8"/>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="A24" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="B24" s="9">
-        <v>46417</v>
-      </c>
-      <c r="C24" s="10">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M24" s="8"/>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="B25" s="9">
-        <v>46425</v>
-      </c>
-      <c r="C25" s="10">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M25" s="8"/>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="B26" s="9">
-        <v>46446</v>
-      </c>
-      <c r="C26" s="10">
-        <v>0.76041666666666663</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M26" s="8"/>
-    </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="8" t="s">
+      <c r="J29" s="7"/>
+      <c r="K29" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="L29" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="B27" s="9">
-        <v>46452</v>
-      </c>
-      <c r="C27" s="10">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="L27" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M27" s="8"/>
-    </row>
-    <row r="28" spans="1:13">
-      <c r="A28" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="B28" s="9">
-        <v>46459</v>
-      </c>
-      <c r="C28" s="10">
-        <v>0.78125</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="L28" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M28" s="8"/>
-    </row>
-    <row r="29" spans="1:13">
-      <c r="A29" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="B29" s="9">
-        <v>46467</v>
-      </c>
-      <c r="C29" s="10">
-        <v>0.73958333333333337</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="L29" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M29" s="8"/>
+      <c r="M29" s="7"/>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="2"/>
@@ -9702,458 +9706,458 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
-      <c r="A1" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
+      <c r="A1" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
     </row>
     <row r="3" spans="1:10" ht="30">
-      <c r="A3" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>56</v>
+      <c r="A3" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="11" t="str">
+      <c r="A4" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="10" t="str">
         <f>IF(B4="","",IFERROR(VLOOKUP(B4,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v>Sam Peters</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="8">
+      <c r="D4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="7">
         <v>1</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="7">
         <v>1</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="10">
         <f t="shared" ref="G4:G67" si="0">IF(AND(E4="",F4=""),"",SUM(E4:F4))</f>
         <v>2</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="7">
         <v>2</v>
       </c>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="11" t="str">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="10" t="str">
         <f>IF(B5="","",IFERROR(VLOOKUP(B5,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="11" t="str">
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="11" t="str">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="10" t="str">
         <f>IF(B6="","",IFERROR(VLOOKUP(B6,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="11" t="str">
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="11" t="str">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="10" t="str">
         <f>IF(B7="","",IFERROR(VLOOKUP(B7,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="11" t="str">
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="11" t="str">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="10" t="str">
         <f>IF(B8="","",IFERROR(VLOOKUP(B8,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="11" t="str">
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="11" t="str">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="10" t="str">
         <f>IF(B9="","",IFERROR(VLOOKUP(B9,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="11" t="str">
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="11" t="str">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="10" t="str">
         <f>IF(B10="","",IFERROR(VLOOKUP(B10,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="11" t="str">
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="11" t="str">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="10" t="str">
         <f>IF(B11="","",IFERROR(VLOOKUP(B11,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="11" t="str">
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="11" t="str">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="10" t="str">
         <f>IF(B12="","",IFERROR(VLOOKUP(B12,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="11" t="str">
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="11" t="str">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="10" t="str">
         <f>IF(B13="","",IFERROR(VLOOKUP(B13,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="11" t="str">
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="11" t="str">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="10" t="str">
         <f>IF(B14="","",IFERROR(VLOOKUP(B14,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="11" t="str">
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="11" t="str">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="10" t="str">
         <f>IF(B15="","",IFERROR(VLOOKUP(B15,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="11" t="str">
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="11" t="str">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="10" t="str">
         <f>IF(B16="","",IFERROR(VLOOKUP(B16,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="11" t="str">
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="11" t="str">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="10" t="str">
         <f>IF(B17="","",IFERROR(VLOOKUP(B17,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="11" t="str">
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="11" t="str">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="10" t="str">
         <f>IF(B18="","",IFERROR(VLOOKUP(B18,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="11" t="str">
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="11" t="str">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="10" t="str">
         <f>IF(B19="","",IFERROR(VLOOKUP(B19,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="11" t="str">
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="11" t="str">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="10" t="str">
         <f>IF(B20="","",IFERROR(VLOOKUP(B20,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="11" t="str">
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="11" t="str">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="10" t="str">
         <f>IF(B21="","",IFERROR(VLOOKUP(B21,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="11" t="str">
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="11" t="str">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="10" t="str">
         <f>IF(B22="","",IFERROR(VLOOKUP(B22,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="11" t="str">
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="11" t="str">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="10" t="str">
         <f>IF(B23="","",IFERROR(VLOOKUP(B23,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="11" t="str">
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="11" t="str">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="10" t="str">
         <f>IF(B24="","",IFERROR(VLOOKUP(B24,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="11" t="str">
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="11" t="str">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="10" t="str">
         <f>IF(B25="","",IFERROR(VLOOKUP(B25,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="11" t="str">
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2"/>
@@ -18742,463 +18746,472 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="25.75" customWidth="1"/>
-    <col min="2" max="2" width="7.375" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="6.875" customWidth="1"/>
+    <col min="4" max="4" width="8.625" customWidth="1"/>
     <col min="5" max="5" width="10.75" customWidth="1"/>
     <col min="6" max="6" width="10.875" customWidth="1"/>
-    <col min="7" max="7" width="4.75" customWidth="1"/>
-    <col min="8" max="8" width="5.875" customWidth="1"/>
-    <col min="9" max="9" width="7.5" customWidth="1"/>
-    <col min="10" max="10" width="7" customWidth="1"/>
+    <col min="7" max="7" width="6.875" customWidth="1"/>
+    <col min="8" max="8" width="8.625" customWidth="1"/>
+    <col min="9" max="9" width="10.625" customWidth="1"/>
+    <col min="10" max="10" width="9.75" customWidth="1"/>
     <col min="11" max="11" width="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20.25">
-      <c r="A1" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
+      <c r="A1" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
     </row>
     <row r="3" spans="1:11" ht="30">
-      <c r="A3" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>56</v>
+      <c r="A3" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="11" t="str">
-        <f>IF(B4="","",IFERROR(VLOOKUP(B4,Players!$A$4:$B$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="11" t="str">
+      <c r="A4" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="D4" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="E4" s="7">
+        <v>20</v>
+      </c>
+      <c r="F4" s="7">
+        <v>1</v>
+      </c>
+      <c r="G4" s="10">
         <f t="shared" ref="G4:G35" si="0">IF(E4="","",E4-F4)</f>
-        <v/>
-      </c>
-      <c r="H4" s="12" t="str">
+        <v>19</v>
+      </c>
+      <c r="H4" s="11">
         <f t="shared" ref="H4:H35" si="1">IF(OR(E4="",E4=0),"",G4/E4)</f>
-        <v/>
-      </c>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
+        <v>0.95</v>
+      </c>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="11" t="str">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="10" t="str">
         <f>IF(B5="","",IFERROR(VLOOKUP(B5,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="11" t="str">
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H5" s="12" t="str">
+      <c r="H5" s="11" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="11" t="str">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="10" t="str">
         <f>IF(B6="","",IFERROR(VLOOKUP(B6,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="11" t="str">
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H6" s="12" t="str">
+      <c r="H6" s="11" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="11" t="str">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="10" t="str">
         <f>IF(B7="","",IFERROR(VLOOKUP(B7,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="11" t="str">
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H7" s="12" t="str">
+      <c r="H7" s="11" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="11" t="str">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="10" t="str">
         <f>IF(B8="","",IFERROR(VLOOKUP(B8,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="11" t="str">
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H8" s="12" t="str">
+      <c r="H8" s="11" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="11" t="str">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="10" t="str">
         <f>IF(B9="","",IFERROR(VLOOKUP(B9,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="11" t="str">
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H9" s="12" t="str">
+      <c r="H9" s="11" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="11" t="str">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="10" t="str">
         <f>IF(B10="","",IFERROR(VLOOKUP(B10,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="11" t="str">
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H10" s="12" t="str">
+      <c r="H10" s="11" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="11" t="str">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="10" t="str">
         <f>IF(B11="","",IFERROR(VLOOKUP(B11,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="11" t="str">
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H11" s="12" t="str">
+      <c r="H11" s="11" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="11" t="str">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="10" t="str">
         <f>IF(B12="","",IFERROR(VLOOKUP(B12,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="11" t="str">
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H12" s="12" t="str">
+      <c r="H12" s="11" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="11" t="str">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="10" t="str">
         <f>IF(B13="","",IFERROR(VLOOKUP(B13,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="11" t="str">
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H13" s="12" t="str">
+      <c r="H13" s="11" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="11" t="str">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="10" t="str">
         <f>IF(B14="","",IFERROR(VLOOKUP(B14,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="11" t="str">
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H14" s="12" t="str">
+      <c r="H14" s="11" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="11" t="str">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="10" t="str">
         <f>IF(B15="","",IFERROR(VLOOKUP(B15,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="11" t="str">
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H15" s="12" t="str">
+      <c r="H15" s="11" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="11" t="str">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="10" t="str">
         <f>IF(B16="","",IFERROR(VLOOKUP(B16,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="11" t="str">
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H16" s="12" t="str">
+      <c r="H16" s="11" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="11" t="str">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="10" t="str">
         <f>IF(B17="","",IFERROR(VLOOKUP(B17,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="11" t="str">
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H17" s="12" t="str">
+      <c r="H17" s="11" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="11" t="str">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="10" t="str">
         <f>IF(B18="","",IFERROR(VLOOKUP(B18,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="11" t="str">
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H18" s="12" t="str">
+      <c r="H18" s="11" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="11" t="str">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="10" t="str">
         <f>IF(B19="","",IFERROR(VLOOKUP(B19,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="11" t="str">
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H19" s="12" t="str">
+      <c r="H19" s="11" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="11" t="str">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="10" t="str">
         <f>IF(B20="","",IFERROR(VLOOKUP(B20,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="11" t="str">
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H20" s="12" t="str">
+      <c r="H20" s="11" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="11" t="str">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="10" t="str">
         <f>IF(B21="","",IFERROR(VLOOKUP(B21,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="11" t="str">
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H21" s="12" t="str">
+      <c r="H21" s="11" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="2"/>
@@ -23192,355 +23205,355 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
-      <c r="A1" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
+      <c r="A1" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
     </row>
     <row r="2" spans="1:13" ht="15">
-      <c r="L2" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>107</v>
+      <c r="L2" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="30">
       <c r="A3" s="1" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>108</v>
+        <v>250</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>109</v>
+        <v>251</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>111</v>
+        <v>253</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>112</v>
+        <v>254</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>113</v>
+        <v>255</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>95</v>
+        <v>236</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="K3" s="14"/>
-      <c r="L3" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="M3" s="13">
+        <v>237</v>
+      </c>
+      <c r="K3" s="13"/>
+      <c r="L3" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="M3" s="12">
         <f>COUNT(Games!$A$4:$A$200)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="13" t="str">
+      <c r="A4" s="12" t="str">
         <f>IF(Players!A4="","",Players!A4)</f>
         <v>P001</v>
       </c>
-      <c r="B4" s="13" t="str">
+      <c r="B4" s="12" t="str">
         <f>IF(A4="","",IFERROR(VLOOKUP(A4,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Sam Peters</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="12">
         <f>IF(A4="","",IFERROR(VLOOKUP(A4,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>9</v>
       </c>
-      <c r="D4" s="13" t="str">
+      <c r="D4" s="12" t="str">
         <f>IF(A4="","",IFERROR(VLOOKUP(A4,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <f>IF(A4="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A4,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>1</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <f>IF(A4="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A4))</f>
         <v>1</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="12">
         <f>IF(A4="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A4))</f>
         <v>1</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="12">
         <f t="shared" ref="H4:H35" si="0">IF(A4="","",F4+G4)</f>
         <v>2</v>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="12">
         <f>IF(A4="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A4))</f>
         <v>2</v>
       </c>
-      <c r="J4" s="13">
+      <c r="J4" s="12">
         <f>IF(A4="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A4))</f>
         <v>0</v>
       </c>
-      <c r="K4" s="14"/>
-      <c r="L4" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="M4" s="13">
+      <c r="K4" s="13"/>
+      <c r="L4" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="M4" s="12">
         <f>SUM(Games!$G$4:$G$200)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="13" t="str">
+      <c r="A5" s="12" t="str">
         <f>IF(Players!A5="","",Players!A5)</f>
         <v>P002</v>
       </c>
-      <c r="B5" s="13" t="str">
+      <c r="B5" s="12" t="str">
         <f>IF(A5="","",IFERROR(VLOOKUP(A5,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Marks Kanins</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="12">
         <f>IF(A5="","",IFERROR(VLOOKUP(A5,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>97</v>
       </c>
-      <c r="D5" s="13" t="str">
+      <c r="D5" s="12" t="str">
         <f>IF(A5="","",IFERROR(VLOOKUP(A5,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <f>IF(A5="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A5,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <f>IF(A5="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A5))</f>
         <v>0</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="12">
         <f>IF(A5="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A5))</f>
         <v>0</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="12">
         <f>IF(A5="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A5))</f>
         <v>0</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="12">
         <f>IF(A5="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A5))</f>
         <v>0</v>
       </c>
-      <c r="K5" s="14"/>
-      <c r="L5" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="M5" s="13">
+      <c r="K5" s="13"/>
+      <c r="L5" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="M5" s="12">
         <f>SUM(Games!$H$4:$H$200)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="13" t="str">
+      <c r="A6" s="12" t="str">
         <f>IF(Players!A6="","",Players!A6)</f>
         <v>P003</v>
       </c>
-      <c r="B6" s="13" t="str">
+      <c r="B6" s="12" t="str">
         <f>IF(A6="","",IFERROR(VLOOKUP(A6,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Dominic Wealthall</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="12">
         <f>IF(A6="","",IFERROR(VLOOKUP(A6,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>74</v>
       </c>
-      <c r="D6" s="13" t="str">
+      <c r="D6" s="12" t="str">
         <f>IF(A6="","",IFERROR(VLOOKUP(A6,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="12">
         <f>IF(A6="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A6,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <f>IF(A6="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A6))</f>
         <v>0</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="12">
         <f>IF(A6="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A6))</f>
         <v>0</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="12">
         <f>IF(A6="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A6))</f>
         <v>0</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="12">
         <f>IF(A6="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A6))</f>
         <v>0</v>
       </c>
-      <c r="K6" s="14"/>
-      <c r="L6" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="M6" s="13">
+      <c r="K6" s="13"/>
+      <c r="L6" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="M6" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"W")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="13" t="str">
+      <c r="A7" s="12" t="str">
         <f>IF(Players!A7="","",Players!A7)</f>
         <v>P004</v>
       </c>
-      <c r="B7" s="13" t="str">
+      <c r="B7" s="12" t="str">
         <f>IF(A7="","",IFERROR(VLOOKUP(A7,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Aaron Burton</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="12">
         <f>IF(A7="","",IFERROR(VLOOKUP(A7,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>29</v>
       </c>
-      <c r="D7" s="13" t="str">
+      <c r="D7" s="12" t="str">
         <f>IF(A7="","",IFERROR(VLOOKUP(A7,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Netminder</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="12">
         <f>IF(A7="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A7,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="12">
         <f>IF(A7="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A7))</f>
         <v>0</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="12">
         <f>IF(A7="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A7))</f>
         <v>0</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="12">
         <f>IF(A7="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A7))</f>
         <v>0</v>
       </c>
-      <c r="J7" s="13">
+      <c r="J7" s="12">
         <f>IF(A7="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A7))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="14"/>
-      <c r="L7" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="M7" s="13">
+      <c r="K7" s="13"/>
+      <c r="L7" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="M7" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"L")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="13" t="str">
+      <c r="A8" s="12" t="str">
         <f>IF(Players!A8="","",Players!A8)</f>
         <v>P005</v>
       </c>
-      <c r="B8" s="13" t="str">
+      <c r="B8" s="12" t="str">
         <f>IF(A8="","",IFERROR(VLOOKUP(A8,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Charlie Russell</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="12">
         <f>IF(A8="","",IFERROR(VLOOKUP(A8,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>12</v>
       </c>
-      <c r="D8" s="13" t="str">
+      <c r="D8" s="12" t="str">
         <f>IF(A8="","",IFERROR(VLOOKUP(A8,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="12">
         <f>IF(A8="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A8,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="12">
         <f>IF(A8="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A8))</f>
         <v>0</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="12">
         <f>IF(A8="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A8))</f>
         <v>0</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="12">
         <f>IF(A8="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A8))</f>
         <v>0</v>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="12">
         <f>IF(A8="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A8))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="14"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="13" t="str">
+      <c r="A9" s="12" t="str">
         <f>IF(Players!A9="","",Players!A9)</f>
         <v>P006</v>
       </c>
-      <c r="B9" s="13" t="str">
+      <c r="B9" s="12" t="str">
         <f>IF(A9="","",IFERROR(VLOOKUP(A9,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Lewis Smith</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="12">
         <f>IF(A9="","",IFERROR(VLOOKUP(A9,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>13</v>
       </c>
-      <c r="D9" s="13" t="str">
+      <c r="D9" s="12" t="str">
         <f>IF(A9="","",IFERROR(VLOOKUP(A9,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <f>IF(A9="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A9,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="12">
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
         <v>0</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="12">
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
         <v>0</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="12">
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
         <v>0</v>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="12">
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="str">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94DD3027-AC4A-4501-886E-F93BFC0C04B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3583A987-5E18-4354-B032-6322B4CF425B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -937,10 +937,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="46" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1162,14 +1162,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="3" spans="1:6" ht="30">
       <c r="A3" s="1" t="s">
@@ -1270,15 +1270,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
       <c r="H1" s="14"/>
     </row>
     <row r="3" spans="1:8" ht="15">
@@ -3520,15 +3520,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="3" spans="1:7" ht="30">
       <c r="A3" s="6" t="s">
@@ -5655,21 +5655,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
     </row>
     <row r="2" spans="1:13"/>
     <row r="3" spans="1:13" ht="30">
@@ -9706,18 +9706,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>230</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
     </row>
     <row r="3" spans="1:10" ht="30">
       <c r="A3" s="6" t="s">
@@ -18748,7 +18748,7 @@
     <col min="1" max="1" width="25.75" customWidth="1"/>
     <col min="2" max="2" width="9.25" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="8.625" customWidth="1"/>
+    <col min="4" max="4" width="14.5" customWidth="1"/>
     <col min="5" max="5" width="10.75" customWidth="1"/>
     <col min="6" max="6" width="10.875" customWidth="1"/>
     <col min="7" max="7" width="6.875" customWidth="1"/>
@@ -18759,19 +18759,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
     </row>
     <row r="3" spans="1:11" ht="30">
       <c r="A3" s="6" t="s">
@@ -18818,8 +18818,8 @@
       <c r="C4" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="D4" s="15">
-        <v>2.5</v>
+      <c r="D4" s="16">
+        <v>60</v>
       </c>
       <c r="E4" s="7">
         <v>20</v>
@@ -18846,7 +18846,7 @@
         <f>IF(B5="","",IFERROR(VLOOKUP(B5,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D5" s="7"/>
+      <c r="D5" s="16"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="10" t="str">
@@ -18868,7 +18868,7 @@
         <f>IF(B6="","",IFERROR(VLOOKUP(B6,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D6" s="7"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="10" t="str">
@@ -18890,7 +18890,7 @@
         <f>IF(B7="","",IFERROR(VLOOKUP(B7,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D7" s="7"/>
+      <c r="D7" s="16"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="10" t="str">
@@ -18912,7 +18912,7 @@
         <f>IF(B8="","",IFERROR(VLOOKUP(B8,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D8" s="7"/>
+      <c r="D8" s="16"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="10" t="str">
@@ -18934,7 +18934,7 @@
         <f>IF(B9="","",IFERROR(VLOOKUP(B9,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D9" s="7"/>
+      <c r="D9" s="16"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="10" t="str">
@@ -18956,7 +18956,7 @@
         <f>IF(B10="","",IFERROR(VLOOKUP(B10,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D10" s="7"/>
+      <c r="D10" s="16"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="10" t="str">
@@ -18978,7 +18978,7 @@
         <f>IF(B11="","",IFERROR(VLOOKUP(B11,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D11" s="7"/>
+      <c r="D11" s="16"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="10" t="str">
@@ -19000,7 +19000,7 @@
         <f>IF(B12="","",IFERROR(VLOOKUP(B12,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D12" s="7"/>
+      <c r="D12" s="16"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="10" t="str">
@@ -19022,7 +19022,7 @@
         <f>IF(B13="","",IFERROR(VLOOKUP(B13,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D13" s="7"/>
+      <c r="D13" s="16"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="10" t="str">
@@ -19044,7 +19044,7 @@
         <f>IF(B14="","",IFERROR(VLOOKUP(B14,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D14" s="7"/>
+      <c r="D14" s="16"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="10" t="str">
@@ -19066,7 +19066,7 @@
         <f>IF(B15="","",IFERROR(VLOOKUP(B15,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D15" s="7"/>
+      <c r="D15" s="16"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="10" t="str">
@@ -19088,7 +19088,7 @@
         <f>IF(B16="","",IFERROR(VLOOKUP(B16,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D16" s="7"/>
+      <c r="D16" s="16"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
       <c r="G16" s="10" t="str">
@@ -23205,18 +23205,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
     </row>
     <row r="2" spans="1:13" ht="15">
       <c r="L2" s="6" t="s">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3583A987-5E18-4354-B032-6322B4CF425B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E55B7CF-0DA4-4185-9072-B228EC57664E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,9 @@
     <sheet name="Games" sheetId="3" r:id="rId4"/>
     <sheet name="Player Game Stats" sheetId="4" r:id="rId5"/>
     <sheet name="Netminder Stats" sheetId="5" r:id="rId6"/>
-    <sheet name="Dashboard" sheetId="6" r:id="rId7"/>
+    <sheet name="League Table" sheetId="8" r:id="rId7"/>
+    <sheet name="Cup Table" sheetId="10" r:id="rId8"/>
+    <sheet name="Dashboard" sheetId="6" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="271">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -785,6 +787,42 @@
     <t>Aaron burton</t>
   </si>
   <si>
+    <t>League Table</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>GP</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>OTW</t>
+  </si>
+  <si>
+    <t>OTL</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>GF</t>
+  </si>
+  <si>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>GD</t>
+  </si>
+  <si>
+    <t>PTS</t>
+  </si>
+  <si>
+    <t>Cup Table</t>
+  </si>
+  <si>
     <t>MK Thunder Season Player Totals</t>
   </si>
   <si>
@@ -803,13 +841,7 @@
     <t>Pos</t>
   </si>
   <si>
-    <t>GP</t>
-  </si>
-  <si>
     <t>G</t>
-  </si>
-  <si>
-    <t>PTS</t>
   </si>
   <si>
     <t>Games entered</t>
@@ -23186,6 +23218,738 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94FF06D7-21FB-428F-802C-72F9E7BDE1D7}">
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="20.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="20.25">
+      <c r="A1" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+    </row>
+    <row r="3" spans="1:10" ht="16.5">
+      <c r="A3" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:J1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6831908-464E-4F9B-8316-B9A7357174A7}">
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="20.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="20.25">
+      <c r="A1" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+    </row>
+    <row r="3" spans="1:10" ht="16.5">
+      <c r="A3" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:J1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:M103"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -23206,7 +23970,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
       <c r="A1" s="15" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -23220,10 +23984,10 @@
     </row>
     <row r="2" spans="1:13" ht="15">
       <c r="L2" s="6" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="30">
@@ -23231,25 +23995,25 @@
         <v>111</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>198</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>236</v>
@@ -23259,7 +24023,7 @@
       </c>
       <c r="K3" s="13"/>
       <c r="L3" s="12" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="M3" s="12">
         <f>COUNT(Games!$A$4:$A$200)</f>
@@ -23309,7 +24073,7 @@
       </c>
       <c r="K4" s="13"/>
       <c r="L4" s="12" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="M4" s="12">
         <f>SUM(Games!$G$4:$G$200)</f>
@@ -23359,7 +24123,7 @@
       </c>
       <c r="K5" s="13"/>
       <c r="L5" s="12" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="M5" s="12">
         <f>SUM(Games!$H$4:$H$200)</f>
@@ -23409,7 +24173,7 @@
       </c>
       <c r="K6" s="13"/>
       <c r="L6" s="12" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="M6" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"W")</f>
@@ -23459,7 +24223,7 @@
       </c>
       <c r="K7" s="13"/>
       <c r="L7" s="12" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="M7" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"L")</f>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E55B7CF-0DA4-4185-9072-B228EC57664E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1306DB6B-B53B-4723-98EC-6C8A069F2A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -23532,10 +23532,10 @@
         <v>31</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -23547,16 +23547,16 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -23564,7 +23564,7 @@
         <v>81</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -23576,16 +23576,16 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -23596,7 +23596,7 @@
         <v>64</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -23608,16 +23608,16 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="J14">
         <v>0</v>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1306DB6B-B53B-4723-98EC-6C8A069F2A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{46605674-C112-4805-B8B2-24A76CCC4A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23532,31 +23532,31 @@
         <v>31</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>6</v>
       </c>
       <c r="J12">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:10">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46605674-C112-4805-B8B2-24A76CCC4A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C239D517-225F-4125-8F83-6CAE2CD06D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="270">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -784,9 +784,6 @@
     <t>Decision</t>
   </si>
   <si>
-    <t>Aaron burton</t>
-  </si>
-  <si>
     <t>League Table</t>
   </si>
   <si>
@@ -913,7 +910,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -943,11 +940,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -973,6 +998,8 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9784,32 +9811,14 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C4" s="10" t="str">
-        <f>IF(B4="","",IFERROR(VLOOKUP(B4,Players!$A$4:$B$200,2,FALSE),""))</f>
-        <v>Sam Peters</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="7">
-        <v>1</v>
-      </c>
-      <c r="F4" s="7">
-        <v>1</v>
-      </c>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G67" si="0">IF(AND(E4="",F4=""),"",SUM(E4:F4))</f>
-        <v>2</v>
-      </c>
-      <c r="H4" s="7">
-        <v>2</v>
-      </c>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
     </row>
@@ -9824,7 +9833,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="G4:G67" si="0">IF(AND(E5="",F5=""),"",SUM(E5:F5))</f>
         <v/>
       </c>
       <c r="H5" s="7"/>
@@ -18841,31 +18850,19 @@
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="D4" s="16">
-        <v>60</v>
-      </c>
-      <c r="E4" s="7">
-        <v>20</v>
-      </c>
-      <c r="F4" s="7">
-        <v>1</v>
-      </c>
-      <c r="G4" s="10">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="10" t="str">
         <f t="shared" ref="G4:G35" si="0">IF(E4="","",E4-F4)</f>
-        <v>19</v>
-      </c>
-      <c r="H4" s="11">
+        <v/>
+      </c>
+      <c r="H4" s="11" t="str">
         <f t="shared" ref="H4:H35" si="1">IF(OR(E4="",E4=0),"",G4/E4)</f>
-        <v>0.95</v>
+        <v/>
       </c>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
@@ -23227,7 +23224,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
       <c r="A1" s="15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -23241,34 +23238,34 @@
     </row>
     <row r="3" spans="1:10" ht="16.5">
       <c r="A3" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -23532,31 +23529,31 @@
         <v>31</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -23564,7 +23561,7 @@
         <v>81</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -23576,16 +23573,16 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -23596,7 +23593,7 @@
         <v>64</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -23608,16 +23605,16 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -23705,7 +23702,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
       <c r="A1" s="15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -23719,34 +23716,34 @@
     </row>
     <row r="3" spans="1:10" ht="16.5">
       <c r="A3" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -23970,7 +23967,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
       <c r="A1" s="15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -23984,10 +23981,10 @@
     </row>
     <row r="2" spans="1:13" ht="15">
       <c r="L2" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="M2" s="6" t="s">
         <v>260</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="30">
@@ -23995,25 +23992,25 @@
         <v>111</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>264</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>265</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>198</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>236</v>
@@ -24023,7 +24020,7 @@
       </c>
       <c r="K3" s="13"/>
       <c r="L3" s="12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="M3" s="12">
         <f>COUNT(Games!$A$4:$A$200)</f>
@@ -24049,23 +24046,23 @@
       </c>
       <c r="E4" s="12">
         <f>IF(A4="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A4,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="12">
         <f>IF(A4="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A4))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="12">
         <f>IF(A4="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A4))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="12">
         <f t="shared" ref="H4:H35" si="0">IF(A4="","",F4+G4)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" s="12">
         <f>IF(A4="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A4))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" s="12">
         <f>IF(A4="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A4))</f>
@@ -24073,7 +24070,7 @@
       </c>
       <c r="K4" s="13"/>
       <c r="L4" s="12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="M4" s="12">
         <f>SUM(Games!$G$4:$G$200)</f>
@@ -24123,7 +24120,7 @@
       </c>
       <c r="K5" s="13"/>
       <c r="L5" s="12" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="M5" s="12">
         <f>SUM(Games!$H$4:$H$200)</f>
@@ -24173,7 +24170,7 @@
       </c>
       <c r="K6" s="13"/>
       <c r="L6" s="12" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="M6" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"W")</f>
@@ -24223,7 +24220,7 @@
       </c>
       <c r="K7" s="13"/>
       <c r="L7" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="M7" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"L")</f>
@@ -24276,43 +24273,43 @@
       <c r="M8" s="12"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="12" t="str">
+      <c r="A9" s="18" t="str">
         <f>IF(Players!A9="","",Players!A9)</f>
         <v>P006</v>
       </c>
-      <c r="B9" s="12" t="str">
+      <c r="B9" s="18" t="str">
         <f>IF(A9="","",IFERROR(VLOOKUP(A9,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Lewis Smith</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="18">
         <f>IF(A9="","",IFERROR(VLOOKUP(A9,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>13</v>
       </c>
-      <c r="D9" s="12" t="str">
+      <c r="D9" s="18" t="str">
         <f>IF(A9="","",IFERROR(VLOOKUP(A9,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="18">
         <f>IF(A9="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A9,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="18">
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
         <v>0</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="18">
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
         <v>0</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="18">
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
         <v>0</v>
       </c>
-      <c r="J9" s="12">
+      <c r="J9" s="18">
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
         <v>0</v>
       </c>
@@ -24320,930 +24317,951 @@
       <c r="L9" s="13"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" t="str">
+      <c r="A10" s="17" t="str">
         <f>IF(Players!A10="","",Players!A10)</f>
         <v>P007</v>
       </c>
-      <c r="B10" t="str">
+      <c r="B10" s="17" t="str">
         <f>IF(A10="","",IFERROR(VLOOKUP(A10,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Robert Oxley</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="17">
         <f>IF(A10="","",IFERROR(VLOOKUP(A10,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>5</v>
       </c>
-      <c r="D10" t="str">
+      <c r="D10" s="17" t="str">
         <f>IF(A10="","",IFERROR(VLOOKUP(A10,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="17">
         <f>IF(A10="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A10,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="17">
         <f>IF(A10="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A10))</f>
         <v>0</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="17">
         <f>IF(A10="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A10))</f>
         <v>0</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="17">
         <f>IF(A10="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A10))</f>
         <v>0</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="17">
         <f>IF(A10="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A10))</f>
         <v>0</v>
       </c>
+      <c r="K10" s="13"/>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" t="str">
+      <c r="A11" s="17" t="str">
         <f>IF(Players!A11="","",Players!A11)</f>
         <v>P008</v>
       </c>
-      <c r="B11" t="str">
+      <c r="B11" s="17" t="str">
         <f>IF(A11="","",IFERROR(VLOOKUP(A11,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Madi Wright</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="17">
         <f>IF(A11="","",IFERROR(VLOOKUP(A11,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>10</v>
       </c>
-      <c r="D11" t="str">
+      <c r="D11" s="17" t="str">
         <f>IF(A11="","",IFERROR(VLOOKUP(A11,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="17">
         <f>IF(A11="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A11,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="17">
         <f>IF(A11="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A11))</f>
         <v>0</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="17">
         <f>IF(A11="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A11))</f>
         <v>0</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="17">
         <f>IF(A11="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A11))</f>
         <v>0</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="17">
         <f>IF(A11="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A11))</f>
         <v>0</v>
       </c>
+      <c r="K11" s="13"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" t="str">
+      <c r="A12" s="17" t="str">
         <f>IF(Players!A12="","",Players!A12)</f>
         <v>P009</v>
       </c>
-      <c r="B12" t="str">
+      <c r="B12" s="17" t="str">
         <f>IF(A12="","",IFERROR(VLOOKUP(A12,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Lizzie Nowik</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="17">
         <f>IF(A12="","",IFERROR(VLOOKUP(A12,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>2</v>
       </c>
-      <c r="D12" t="str">
+      <c r="D12" s="17" t="str">
         <f>IF(A12="","",IFERROR(VLOOKUP(A12,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Netminder</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="17">
         <f>IF(A12="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A12,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="17">
         <f>IF(A12="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A12))</f>
         <v>0</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="17">
         <f>IF(A12="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A12))</f>
         <v>0</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="17">
         <f>IF(A12="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A12))</f>
         <v>0</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="17">
         <f>IF(A12="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A12))</f>
         <v>0</v>
       </c>
+      <c r="K12" s="13"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" t="str">
+      <c r="A13" s="17" t="str">
         <f>IF(Players!A13="","",Players!A13)</f>
         <v>P010</v>
       </c>
-      <c r="B13" t="str">
+      <c r="B13" s="17" t="str">
         <f>IF(A13="","",IFERROR(VLOOKUP(A13,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Nicole Jackson</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="17">
         <f>IF(A13="","",IFERROR(VLOOKUP(A13,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>86</v>
       </c>
-      <c r="D13" t="str">
+      <c r="D13" s="17" t="str">
         <f>IF(A13="","",IFERROR(VLOOKUP(A13,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Netminder</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="17">
         <f>IF(A13="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A13,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="17">
         <f>IF(A13="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A13))</f>
         <v>0</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="17">
         <f>IF(A13="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A13))</f>
         <v>0</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="17">
         <f>IF(A13="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A13))</f>
         <v>0</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="17">
         <f>IF(A13="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A13))</f>
         <v>0</v>
       </c>
+      <c r="K13" s="13"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" t="str">
+      <c r="A14" s="17" t="str">
         <f>IF(Players!A14="","",Players!A14)</f>
         <v>P011</v>
       </c>
-      <c r="B14" t="str">
+      <c r="B14" s="17" t="str">
         <f>IF(A14="","",IFERROR(VLOOKUP(A14,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Xander Robinson</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="17">
         <f>IF(A14="","",IFERROR(VLOOKUP(A14,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>14</v>
       </c>
-      <c r="D14" t="str">
+      <c r="D14" s="17" t="str">
         <f>IF(A14="","",IFERROR(VLOOKUP(A14,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="17">
         <f>IF(A14="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A14,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="17">
         <f>IF(A14="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A14))</f>
         <v>0</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="17">
         <f>IF(A14="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A14))</f>
         <v>0</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="17">
         <f>IF(A14="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A14))</f>
         <v>0</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="17">
         <f>IF(A14="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A14))</f>
         <v>0</v>
       </c>
+      <c r="K14" s="13"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" t="str">
+      <c r="A15" s="17" t="str">
         <f>IF(Players!A15="","",Players!A15)</f>
         <v>P012</v>
       </c>
-      <c r="B15" t="str">
+      <c r="B15" s="17" t="str">
         <f>IF(A15="","",IFERROR(VLOOKUP(A15,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Joshua Blackwood</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="17">
         <f>IF(A15="","",IFERROR(VLOOKUP(A15,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>18</v>
       </c>
-      <c r="D15" t="str">
+      <c r="D15" s="17" t="str">
         <f>IF(A15="","",IFERROR(VLOOKUP(A15,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="17">
         <f>IF(A15="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A15,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="17">
         <f>IF(A15="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A15))</f>
         <v>0</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="17">
         <f>IF(A15="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A15))</f>
         <v>0</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="17">
         <f>IF(A15="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A15))</f>
         <v>0</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="17">
         <f>IF(A15="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A15))</f>
         <v>0</v>
       </c>
+      <c r="K15" s="13"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" t="str">
+      <c r="A16" s="17" t="str">
         <f>IF(Players!A16="","",Players!A16)</f>
         <v>P013</v>
       </c>
-      <c r="B16" t="str">
+      <c r="B16" s="17" t="str">
         <f>IF(A16="","",IFERROR(VLOOKUP(A16,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Harry MacGarvery</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="17">
         <f>IF(A16="","",IFERROR(VLOOKUP(A16,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>22</v>
       </c>
-      <c r="D16" t="str">
+      <c r="D16" s="17" t="str">
         <f>IF(A16="","",IFERROR(VLOOKUP(A16,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="17">
         <f>IF(A16="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A16,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="17">
         <f>IF(A16="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A16))</f>
         <v>0</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="17">
         <f>IF(A16="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A16))</f>
         <v>0</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="17">
         <f>IF(A16="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A16))</f>
         <v>0</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="17">
         <f>IF(A16="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A16))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" t="str">
+      <c r="K16" s="13"/>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="17" t="str">
         <f>IF(Players!A17="","",Players!A17)</f>
         <v>P014</v>
       </c>
-      <c r="B17" t="str">
+      <c r="B17" s="17" t="str">
         <f>IF(A17="","",IFERROR(VLOOKUP(A17,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Chalie Conroy</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="17">
         <f>IF(A17="","",IFERROR(VLOOKUP(A17,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>24</v>
       </c>
-      <c r="D17" t="str">
+      <c r="D17" s="17" t="str">
         <f>IF(A17="","",IFERROR(VLOOKUP(A17,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="17">
         <f>IF(A17="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A17,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="17">
         <f>IF(A17="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A17))</f>
         <v>0</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="17">
         <f>IF(A17="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A17))</f>
         <v>0</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="17">
         <f>IF(A17="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A17))</f>
         <v>0</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="17">
         <f>IF(A17="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A17))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" t="str">
+      <c r="K17" s="13"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="17" t="str">
         <f>IF(Players!A18="","",Players!A18)</f>
         <v>P015</v>
       </c>
-      <c r="B18" t="str">
+      <c r="B18" s="17" t="str">
         <f>IF(A18="","",IFERROR(VLOOKUP(A18,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Oliver Broyd</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="17">
         <f>IF(A18="","",IFERROR(VLOOKUP(A18,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>33</v>
       </c>
-      <c r="D18" t="str">
+      <c r="D18" s="17" t="str">
         <f>IF(A18="","",IFERROR(VLOOKUP(A18,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="17">
         <f>IF(A18="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A18,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="17">
         <f>IF(A18="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A18))</f>
         <v>0</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="17">
         <f>IF(A18="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A18))</f>
         <v>0</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="17">
         <f>IF(A18="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A18))</f>
         <v>0</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="17">
         <f>IF(A18="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A18))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" t="str">
+      <c r="K18" s="13"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="17" t="str">
         <f>IF(Players!A19="","",Players!A19)</f>
         <v>P016</v>
       </c>
-      <c r="B19" t="str">
+      <c r="B19" s="17" t="str">
         <f>IF(A19="","",IFERROR(VLOOKUP(A19,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Connor Mellett</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="17">
         <f>IF(A19="","",IFERROR(VLOOKUP(A19,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>37</v>
       </c>
-      <c r="D19" t="str">
+      <c r="D19" s="17" t="str">
         <f>IF(A19="","",IFERROR(VLOOKUP(A19,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="17">
         <f>IF(A19="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A19,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="17">
         <f>IF(A19="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A19))</f>
         <v>0</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="17">
         <f>IF(A19="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A19))</f>
         <v>0</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="17">
         <f>IF(A19="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A19))</f>
         <v>0</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="17">
         <f>IF(A19="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A19))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" t="str">
+      <c r="K19" s="13"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="17" t="str">
         <f>IF(Players!A20="","",Players!A20)</f>
         <v>P017</v>
       </c>
-      <c r="B20" t="str">
+      <c r="B20" s="17" t="str">
         <f>IF(A20="","",IFERROR(VLOOKUP(A20,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Hayden Hagger</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="17">
         <f>IF(A20="","",IFERROR(VLOOKUP(A20,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>45</v>
       </c>
-      <c r="D20" t="str">
+      <c r="D20" s="17" t="str">
         <f>IF(A20="","",IFERROR(VLOOKUP(A20,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="17">
         <f>IF(A20="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A20,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="17">
         <f>IF(A20="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A20))</f>
         <v>0</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="17">
         <f>IF(A20="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A20))</f>
         <v>0</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="17">
         <f>IF(A20="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A20))</f>
         <v>0</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="17">
         <f>IF(A20="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A20))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" t="str">
+      <c r="K20" s="13"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="17" t="str">
         <f>IF(Players!A21="","",Players!A21)</f>
         <v>P018</v>
       </c>
-      <c r="B21" t="str">
+      <c r="B21" s="17" t="str">
         <f>IF(A21="","",IFERROR(VLOOKUP(A21,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Sam Purcell</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="17">
         <f>IF(A21="","",IFERROR(VLOOKUP(A21,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>64</v>
       </c>
-      <c r="D21" t="str">
+      <c r="D21" s="17" t="str">
         <f>IF(A21="","",IFERROR(VLOOKUP(A21,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="17">
         <f>IF(A21="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A21,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="17">
         <f>IF(A21="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A21))</f>
         <v>0</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="17">
         <f>IF(A21="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A21))</f>
         <v>0</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="17">
         <f>IF(A21="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A21))</f>
         <v>0</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="17">
         <f>IF(A21="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A21))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" t="str">
+      <c r="K21" s="13"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="17" t="str">
         <f>IF(Players!A22="","",Players!A22)</f>
         <v>P019</v>
       </c>
-      <c r="B22" t="str">
+      <c r="B22" s="17" t="str">
         <f>IF(A22="","",IFERROR(VLOOKUP(A22,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Samuel Rickard</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="17">
         <f>IF(A22="","",IFERROR(VLOOKUP(A22,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>65</v>
       </c>
-      <c r="D22" t="str">
+      <c r="D22" s="17" t="str">
         <f>IF(A22="","",IFERROR(VLOOKUP(A22,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="17">
         <f>IF(A22="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A22,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="17">
         <f>IF(A22="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A22))</f>
         <v>0</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="17">
         <f>IF(A22="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A22))</f>
         <v>0</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="17">
         <f>IF(A22="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A22))</f>
         <v>0</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="17">
         <f>IF(A22="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A22))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" t="str">
+      <c r="K22" s="13"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="17" t="str">
         <f>IF(Players!A23="","",Players!A23)</f>
         <v>P020</v>
       </c>
-      <c r="B23" t="str">
+      <c r="B23" s="17" t="str">
         <f>IF(A23="","",IFERROR(VLOOKUP(A23,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Oscar Lee</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="17">
         <f>IF(A23="","",IFERROR(VLOOKUP(A23,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>68</v>
       </c>
-      <c r="D23" t="str">
+      <c r="D23" s="17" t="str">
         <f>IF(A23="","",IFERROR(VLOOKUP(A23,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="17">
         <f>IF(A23="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A23,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="17">
         <f>IF(A23="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A23))</f>
         <v>0</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="17">
         <f>IF(A23="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A23))</f>
         <v>0</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="17">
         <f>IF(A23="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A23))</f>
         <v>0</v>
       </c>
-      <c r="J23">
+      <c r="J23" s="17">
         <f>IF(A23="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A23))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" t="str">
+      <c r="K23" s="13"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="17" t="str">
         <f>IF(Players!A24="","",Players!A24)</f>
         <v>P021</v>
       </c>
-      <c r="B24" t="str">
+      <c r="B24" s="17" t="str">
         <f>IF(A24="","",IFERROR(VLOOKUP(A24,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Jacob Maidment</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="17">
         <f>IF(A24="","",IFERROR(VLOOKUP(A24,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>89</v>
       </c>
-      <c r="D24" t="str">
+      <c r="D24" s="17" t="str">
         <f>IF(A24="","",IFERROR(VLOOKUP(A24,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="17">
         <f>IF(A24="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A24,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="17">
         <f>IF(A24="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A24))</f>
         <v>0</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="17">
         <f>IF(A24="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A24))</f>
         <v>0</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="17">
         <f>IF(A24="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A24))</f>
         <v>0</v>
       </c>
-      <c r="J24">
+      <c r="J24" s="17">
         <f>IF(A24="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A24))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" t="str">
+      <c r="K24" s="13"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="17" t="str">
         <f>IF(Players!A25="","",Players!A25)</f>
         <v>P022</v>
       </c>
-      <c r="B25" t="str">
+      <c r="B25" s="17" t="str">
         <f>IF(A25="","",IFERROR(VLOOKUP(A25,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Corey Taylor</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="17">
         <f>IF(A25="","",IFERROR(VLOOKUP(A25,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>16</v>
       </c>
-      <c r="D25" t="str">
+      <c r="D25" s="17" t="str">
         <f>IF(A25="","",IFERROR(VLOOKUP(A25,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="17">
         <f>IF(A25="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A25,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="17">
         <f>IF(A25="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A25))</f>
         <v>0</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="17">
         <f>IF(A25="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A25))</f>
         <v>0</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="17">
         <f>IF(A25="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A25))</f>
         <v>0</v>
       </c>
-      <c r="J25">
+      <c r="J25" s="17">
         <f>IF(A25="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A25))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" t="str">
+      <c r="K25" s="13"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="17" t="str">
         <f>IF(Players!A26="","",Players!A26)</f>
         <v>P023</v>
       </c>
-      <c r="B26" t="str">
+      <c r="B26" s="17" t="str">
         <f>IF(A26="","",IFERROR(VLOOKUP(A26,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>James Bryan</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="17">
         <f>IF(A26="","",IFERROR(VLOOKUP(A26,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>23</v>
       </c>
-      <c r="D26" t="str">
+      <c r="D26" s="17" t="str">
         <f>IF(A26="","",IFERROR(VLOOKUP(A26,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="17">
         <f>IF(A26="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A26,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="17">
         <f>IF(A26="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A26))</f>
         <v>0</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="17">
         <f>IF(A26="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A26))</f>
         <v>0</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="17">
         <f>IF(A26="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A26))</f>
         <v>0</v>
       </c>
-      <c r="J26">
+      <c r="J26" s="17">
         <f>IF(A26="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A26))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" t="str">
+      <c r="K26" s="13"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="17" t="str">
         <f>IF(Players!A27="","",Players!A27)</f>
         <v>P024</v>
       </c>
-      <c r="B27" t="str">
+      <c r="B27" s="17" t="str">
         <f>IF(A27="","",IFERROR(VLOOKUP(A27,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Josh Furnell</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="17">
         <f>IF(A27="","",IFERROR(VLOOKUP(A27,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>33</v>
       </c>
-      <c r="D27" t="str">
+      <c r="D27" s="17" t="str">
         <f>IF(A27="","",IFERROR(VLOOKUP(A27,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="17">
         <f>IF(A27="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A27,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="17">
         <f>IF(A27="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A27))</f>
         <v>0</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="17">
         <f>IF(A27="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A27))</f>
         <v>0</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="17">
         <f>IF(A27="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A27))</f>
         <v>0</v>
       </c>
-      <c r="J27">
+      <c r="J27" s="17">
         <f>IF(A27="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A27))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" t="str">
+      <c r="K27" s="13"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="17" t="str">
         <f>IF(Players!A28="","",Players!A28)</f>
         <v>P025</v>
       </c>
-      <c r="B28" t="str">
+      <c r="B28" s="17" t="str">
         <f>IF(A28="","",IFERROR(VLOOKUP(A28,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Josh Hickman</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="17">
         <f>IF(A28="","",IFERROR(VLOOKUP(A28,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>40</v>
       </c>
-      <c r="D28" t="str">
+      <c r="D28" s="17" t="str">
         <f>IF(A28="","",IFERROR(VLOOKUP(A28,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="17">
         <f>IF(A28="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A28,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="17">
         <f>IF(A28="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A28))</f>
         <v>0</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="17">
         <f>IF(A28="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A28))</f>
         <v>0</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="17">
         <f>IF(A28="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A28))</f>
         <v>0</v>
       </c>
-      <c r="J28">
+      <c r="J28" s="17">
         <f>IF(A28="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A28))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" t="str">
+      <c r="K28" s="13"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="17" t="str">
         <f>IF(Players!A29="","",Players!A29)</f>
         <v>P026</v>
       </c>
-      <c r="B29" t="str">
+      <c r="B29" s="17" t="str">
         <f>IF(A29="","",IFERROR(VLOOKUP(A29,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Ryan Wonfor</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="17">
         <f>IF(A29="","",IFERROR(VLOOKUP(A29,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>77</v>
       </c>
-      <c r="D29" t="str">
+      <c r="D29" s="17" t="str">
         <f>IF(A29="","",IFERROR(VLOOKUP(A29,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="17">
         <f>IF(A29="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A29,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="17">
         <f>IF(A29="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A29))</f>
         <v>0</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="17">
         <f>IF(A29="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A29))</f>
         <v>0</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="17">
         <f>IF(A29="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A29))</f>
         <v>0</v>
       </c>
-      <c r="J29">
+      <c r="J29" s="17">
         <f>IF(A29="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A29))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" t="str">
+      <c r="K29" s="13"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="17" t="str">
         <f>IF(Players!A30="","",Players!A30)</f>
         <v>P027</v>
       </c>
-      <c r="B30" t="str">
+      <c r="B30" s="17" t="str">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Charles Coney</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="17">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>88</v>
       </c>
-      <c r="D30" t="str">
+      <c r="D30" s="17" t="str">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="17">
         <f>IF(A30="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A30,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="17">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="17">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="17">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
-      <c r="J30">
+      <c r="J30" s="17">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" t="str">
+      <c r="K30" s="13"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="13" t="str">
         <f>IF(Players!A31="","",Players!A31)</f>
         <v/>
       </c>
-      <c r="B31" t="str">
+      <c r="B31" s="13" t="str">
         <f>IF(A31="","",IFERROR(VLOOKUP(A31,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="C31" t="str">
+      <c r="C31" s="13" t="str">
         <f>IF(A31="","",IFERROR(VLOOKUP(A31,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D31" t="str">
+      <c r="D31" s="13" t="str">
         <f>IF(A31="","",IFERROR(VLOOKUP(A31,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E31" t="str">
+      <c r="E31" s="13" t="str">
         <f>IF(A31="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A31,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v/>
       </c>
-      <c r="F31" t="str">
+      <c r="F31" s="13" t="str">
         <f>IF(A31="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A31))</f>
         <v/>
       </c>
-      <c r="G31" t="str">
+      <c r="G31" s="13" t="str">
         <f>IF(A31="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A31))</f>
         <v/>
       </c>
-      <c r="H31" t="str">
+      <c r="H31" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I31" t="str">
+      <c r="I31" s="13" t="str">
         <f>IF(A31="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A31))</f>
         <v/>
       </c>
-      <c r="J31" t="str">
+      <c r="J31" s="13" t="str">
         <f>IF(A31="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A31))</f>
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:11">
       <c r="A32" t="str">
         <f>IF(Players!A32="","",Players!A32)</f>
         <v/>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C239D517-225F-4125-8F83-6CAE2CD06D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57891FBA-42DF-49DA-A51E-4965F9285BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="275">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -855,6 +855,21 @@
   <si>
     <t>Losses</t>
   </si>
+  <si>
+    <t>robinson.png</t>
+  </si>
+  <si>
+    <t>conroy.png</t>
+  </si>
+  <si>
+    <t>mellett.png</t>
+  </si>
+  <si>
+    <t>Josh.png</t>
+  </si>
+  <si>
+    <t>macGarvey.png</t>
+  </si>
 </sst>
 </file>
 
@@ -972,7 +987,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -994,12 +1009,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1221,14 +1235,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.25">
-      <c r="A1" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="3" spans="1:6" ht="30">
       <c r="A3" s="1" t="s">
@@ -1329,15 +1343,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
       <c r="H1" s="14"/>
     </row>
     <row r="3" spans="1:8" ht="15">
@@ -3574,20 +3588,20 @@
     <col min="3" max="3" width="8.875" customWidth="1"/>
     <col min="4" max="4" width="10.625" customWidth="1"/>
     <col min="5" max="5" width="6.125" customWidth="1"/>
-    <col min="6" max="6" width="11.625" customWidth="1"/>
+    <col min="6" max="6" width="14.625" customWidth="1"/>
     <col min="7" max="7" width="9.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="3" spans="1:7" ht="30">
       <c r="A3" s="6" t="s">
@@ -3840,7 +3854,9 @@
       <c r="E14" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="7"/>
+      <c r="F14" s="7" t="s">
+        <v>270</v>
+      </c>
       <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7">
@@ -3859,7 +3875,9 @@
       <c r="E15" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="7"/>
+      <c r="F15" s="7" t="s">
+        <v>273</v>
+      </c>
       <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7">
@@ -3878,7 +3896,9 @@
       <c r="E16" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="7"/>
+      <c r="F16" s="7" t="s">
+        <v>274</v>
+      </c>
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7">
@@ -3897,7 +3917,9 @@
       <c r="E17" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F17" s="7"/>
+      <c r="F17" s="7" t="s">
+        <v>271</v>
+      </c>
       <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7">
@@ -3935,7 +3957,9 @@
       <c r="E19" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F19" s="7"/>
+      <c r="F19" s="7" t="s">
+        <v>272</v>
+      </c>
       <c r="G19" s="7"/>
     </row>
     <row r="20" spans="1:7">
@@ -5714,21 +5738,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
     </row>
     <row r="2" spans="1:13"/>
     <row r="3" spans="1:13" ht="30">
@@ -9765,18 +9789,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
     </row>
     <row r="3" spans="1:10" ht="30">
       <c r="A3" s="6" t="s">
@@ -9833,7 +9857,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="10" t="str">
-        <f t="shared" ref="G4:G67" si="0">IF(AND(E5="",F5=""),"",SUM(E5:F5))</f>
+        <f t="shared" ref="G5:G67" si="0">IF(AND(E5="",F5=""),"",SUM(E5:F5))</f>
         <v/>
       </c>
       <c r="H5" s="7"/>
@@ -18800,19 +18824,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
     </row>
     <row r="3" spans="1:11" ht="30">
       <c r="A3" s="6" t="s">
@@ -18853,7 +18877,7 @@
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="10"/>
-      <c r="D4" s="16"/>
+      <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="10" t="str">
@@ -18875,7 +18899,7 @@
         <f>IF(B5="","",IFERROR(VLOOKUP(B5,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D5" s="16"/>
+      <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="10" t="str">
@@ -18897,7 +18921,7 @@
         <f>IF(B6="","",IFERROR(VLOOKUP(B6,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D6" s="16"/>
+      <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="10" t="str">
@@ -18919,7 +18943,7 @@
         <f>IF(B7="","",IFERROR(VLOOKUP(B7,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D7" s="16"/>
+      <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="10" t="str">
@@ -18941,7 +18965,7 @@
         <f>IF(B8="","",IFERROR(VLOOKUP(B8,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D8" s="16"/>
+      <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="10" t="str">
@@ -18963,7 +18987,7 @@
         <f>IF(B9="","",IFERROR(VLOOKUP(B9,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D9" s="16"/>
+      <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="10" t="str">
@@ -18985,7 +19009,7 @@
         <f>IF(B10="","",IFERROR(VLOOKUP(B10,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D10" s="16"/>
+      <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="10" t="str">
@@ -19007,7 +19031,7 @@
         <f>IF(B11="","",IFERROR(VLOOKUP(B11,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D11" s="16"/>
+      <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="10" t="str">
@@ -19029,7 +19053,7 @@
         <f>IF(B12="","",IFERROR(VLOOKUP(B12,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D12" s="16"/>
+      <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="10" t="str">
@@ -19051,7 +19075,7 @@
         <f>IF(B13="","",IFERROR(VLOOKUP(B13,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D13" s="16"/>
+      <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="10" t="str">
@@ -19073,7 +19097,7 @@
         <f>IF(B14="","",IFERROR(VLOOKUP(B14,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D14" s="16"/>
+      <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="10" t="str">
@@ -19095,7 +19119,7 @@
         <f>IF(B15="","",IFERROR(VLOOKUP(B15,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D15" s="16"/>
+      <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="10" t="str">
@@ -19117,7 +19141,7 @@
         <f>IF(B16="","",IFERROR(VLOOKUP(B16,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D16" s="16"/>
+      <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
       <c r="G16" s="10" t="str">
@@ -23223,20 +23247,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-    </row>
-    <row r="3" spans="1:10" ht="16.5">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+    </row>
+    <row r="3" spans="1:10" ht="15">
       <c r="A3" s="6" t="s">
         <v>247</v>
       </c>
@@ -23701,20 +23725,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-    </row>
-    <row r="3" spans="1:10" ht="16.5">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+    </row>
+    <row r="3" spans="1:10" ht="15">
       <c r="A3" s="6" t="s">
         <v>247</v>
       </c>
@@ -23966,18 +23990,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
     </row>
     <row r="2" spans="1:13" ht="15">
       <c r="L2" s="6" t="s">
@@ -24273,43 +24297,43 @@
       <c r="M8" s="12"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="18" t="str">
+      <c r="A9" s="16" t="str">
         <f>IF(Players!A9="","",Players!A9)</f>
         <v>P006</v>
       </c>
-      <c r="B9" s="18" t="str">
+      <c r="B9" s="16" t="str">
         <f>IF(A9="","",IFERROR(VLOOKUP(A9,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Lewis Smith</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="16">
         <f>IF(A9="","",IFERROR(VLOOKUP(A9,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>13</v>
       </c>
-      <c r="D9" s="18" t="str">
+      <c r="D9" s="16" t="str">
         <f>IF(A9="","",IFERROR(VLOOKUP(A9,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="16">
         <f>IF(A9="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A9,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="16">
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
         <v>0</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="16">
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
         <v>0</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="16">
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
         <v>0</v>
       </c>
-      <c r="J9" s="18">
+      <c r="J9" s="16">
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
         <v>0</v>
       </c>
@@ -24317,903 +24341,903 @@
       <c r="L9" s="13"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="17" t="str">
+      <c r="A10" s="15" t="str">
         <f>IF(Players!A10="","",Players!A10)</f>
         <v>P007</v>
       </c>
-      <c r="B10" s="17" t="str">
+      <c r="B10" s="15" t="str">
         <f>IF(A10="","",IFERROR(VLOOKUP(A10,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Robert Oxley</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="15">
         <f>IF(A10="","",IFERROR(VLOOKUP(A10,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>5</v>
       </c>
-      <c r="D10" s="17" t="str">
+      <c r="D10" s="15" t="str">
         <f>IF(A10="","",IFERROR(VLOOKUP(A10,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="15">
         <f>IF(A10="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A10,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="15">
         <f>IF(A10="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A10))</f>
         <v>0</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="15">
         <f>IF(A10="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A10))</f>
         <v>0</v>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I10" s="17">
+      <c r="I10" s="15">
         <f>IF(A10="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A10))</f>
         <v>0</v>
       </c>
-      <c r="J10" s="17">
+      <c r="J10" s="15">
         <f>IF(A10="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A10))</f>
         <v>0</v>
       </c>
       <c r="K10" s="13"/>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="17" t="str">
+      <c r="A11" s="15" t="str">
         <f>IF(Players!A11="","",Players!A11)</f>
         <v>P008</v>
       </c>
-      <c r="B11" s="17" t="str">
+      <c r="B11" s="15" t="str">
         <f>IF(A11="","",IFERROR(VLOOKUP(A11,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Madi Wright</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="15">
         <f>IF(A11="","",IFERROR(VLOOKUP(A11,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>10</v>
       </c>
-      <c r="D11" s="17" t="str">
+      <c r="D11" s="15" t="str">
         <f>IF(A11="","",IFERROR(VLOOKUP(A11,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="15">
         <f>IF(A11="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A11,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="15">
         <f>IF(A11="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A11))</f>
         <v>0</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="15">
         <f>IF(A11="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A11))</f>
         <v>0</v>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="15">
         <f>IF(A11="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A11))</f>
         <v>0</v>
       </c>
-      <c r="J11" s="17">
+      <c r="J11" s="15">
         <f>IF(A11="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A11))</f>
         <v>0</v>
       </c>
       <c r="K11" s="13"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="17" t="str">
+      <c r="A12" s="15" t="str">
         <f>IF(Players!A12="","",Players!A12)</f>
         <v>P009</v>
       </c>
-      <c r="B12" s="17" t="str">
+      <c r="B12" s="15" t="str">
         <f>IF(A12="","",IFERROR(VLOOKUP(A12,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Lizzie Nowik</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="15">
         <f>IF(A12="","",IFERROR(VLOOKUP(A12,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>2</v>
       </c>
-      <c r="D12" s="17" t="str">
+      <c r="D12" s="15" t="str">
         <f>IF(A12="","",IFERROR(VLOOKUP(A12,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Netminder</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="15">
         <f>IF(A12="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A12,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="15">
         <f>IF(A12="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A12))</f>
         <v>0</v>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="15">
         <f>IF(A12="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A12))</f>
         <v>0</v>
       </c>
-      <c r="H12" s="17">
+      <c r="H12" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I12" s="17">
+      <c r="I12" s="15">
         <f>IF(A12="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A12))</f>
         <v>0</v>
       </c>
-      <c r="J12" s="17">
+      <c r="J12" s="15">
         <f>IF(A12="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A12))</f>
         <v>0</v>
       </c>
       <c r="K12" s="13"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="17" t="str">
+      <c r="A13" s="15" t="str">
         <f>IF(Players!A13="","",Players!A13)</f>
         <v>P010</v>
       </c>
-      <c r="B13" s="17" t="str">
+      <c r="B13" s="15" t="str">
         <f>IF(A13="","",IFERROR(VLOOKUP(A13,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Nicole Jackson</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="15">
         <f>IF(A13="","",IFERROR(VLOOKUP(A13,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>86</v>
       </c>
-      <c r="D13" s="17" t="str">
+      <c r="D13" s="15" t="str">
         <f>IF(A13="","",IFERROR(VLOOKUP(A13,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Netminder</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="15">
         <f>IF(A13="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A13,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="15">
         <f>IF(A13="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A13))</f>
         <v>0</v>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="15">
         <f>IF(A13="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A13))</f>
         <v>0</v>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="15">
         <f>IF(A13="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A13))</f>
         <v>0</v>
       </c>
-      <c r="J13" s="17">
+      <c r="J13" s="15">
         <f>IF(A13="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A13))</f>
         <v>0</v>
       </c>
       <c r="K13" s="13"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="17" t="str">
+      <c r="A14" s="15" t="str">
         <f>IF(Players!A14="","",Players!A14)</f>
         <v>P011</v>
       </c>
-      <c r="B14" s="17" t="str">
+      <c r="B14" s="15" t="str">
         <f>IF(A14="","",IFERROR(VLOOKUP(A14,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Xander Robinson</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="15">
         <f>IF(A14="","",IFERROR(VLOOKUP(A14,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>14</v>
       </c>
-      <c r="D14" s="17" t="str">
+      <c r="D14" s="15" t="str">
         <f>IF(A14="","",IFERROR(VLOOKUP(A14,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="15">
         <f>IF(A14="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A14,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="15">
         <f>IF(A14="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A14))</f>
         <v>0</v>
       </c>
-      <c r="G14" s="17">
+      <c r="G14" s="15">
         <f>IF(A14="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A14))</f>
         <v>0</v>
       </c>
-      <c r="H14" s="17">
+      <c r="H14" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I14" s="17">
+      <c r="I14" s="15">
         <f>IF(A14="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A14))</f>
         <v>0</v>
       </c>
-      <c r="J14" s="17">
+      <c r="J14" s="15">
         <f>IF(A14="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A14))</f>
         <v>0</v>
       </c>
       <c r="K14" s="13"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="17" t="str">
+      <c r="A15" s="15" t="str">
         <f>IF(Players!A15="","",Players!A15)</f>
         <v>P012</v>
       </c>
-      <c r="B15" s="17" t="str">
+      <c r="B15" s="15" t="str">
         <f>IF(A15="","",IFERROR(VLOOKUP(A15,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Joshua Blackwood</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="15">
         <f>IF(A15="","",IFERROR(VLOOKUP(A15,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>18</v>
       </c>
-      <c r="D15" s="17" t="str">
+      <c r="D15" s="15" t="str">
         <f>IF(A15="","",IFERROR(VLOOKUP(A15,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="15">
         <f>IF(A15="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A15,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="15">
         <f>IF(A15="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A15))</f>
         <v>0</v>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="15">
         <f>IF(A15="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A15))</f>
         <v>0</v>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="15">
         <f>IF(A15="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A15))</f>
         <v>0</v>
       </c>
-      <c r="J15" s="17">
+      <c r="J15" s="15">
         <f>IF(A15="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A15))</f>
         <v>0</v>
       </c>
       <c r="K15" s="13"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="17" t="str">
+      <c r="A16" s="15" t="str">
         <f>IF(Players!A16="","",Players!A16)</f>
         <v>P013</v>
       </c>
-      <c r="B16" s="17" t="str">
+      <c r="B16" s="15" t="str">
         <f>IF(A16="","",IFERROR(VLOOKUP(A16,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Harry MacGarvery</v>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="15">
         <f>IF(A16="","",IFERROR(VLOOKUP(A16,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>22</v>
       </c>
-      <c r="D16" s="17" t="str">
+      <c r="D16" s="15" t="str">
         <f>IF(A16="","",IFERROR(VLOOKUP(A16,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="15">
         <f>IF(A16="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A16,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F16" s="17">
+      <c r="F16" s="15">
         <f>IF(A16="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A16))</f>
         <v>0</v>
       </c>
-      <c r="G16" s="17">
+      <c r="G16" s="15">
         <f>IF(A16="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A16))</f>
         <v>0</v>
       </c>
-      <c r="H16" s="17">
+      <c r="H16" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I16" s="17">
+      <c r="I16" s="15">
         <f>IF(A16="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A16))</f>
         <v>0</v>
       </c>
-      <c r="J16" s="17">
+      <c r="J16" s="15">
         <f>IF(A16="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A16))</f>
         <v>0</v>
       </c>
       <c r="K16" s="13"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="17" t="str">
+      <c r="A17" s="15" t="str">
         <f>IF(Players!A17="","",Players!A17)</f>
         <v>P014</v>
       </c>
-      <c r="B17" s="17" t="str">
+      <c r="B17" s="15" t="str">
         <f>IF(A17="","",IFERROR(VLOOKUP(A17,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Chalie Conroy</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="15">
         <f>IF(A17="","",IFERROR(VLOOKUP(A17,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>24</v>
       </c>
-      <c r="D17" s="17" t="str">
+      <c r="D17" s="15" t="str">
         <f>IF(A17="","",IFERROR(VLOOKUP(A17,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="15">
         <f>IF(A17="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A17,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="15">
         <f>IF(A17="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A17))</f>
         <v>0</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="15">
         <f>IF(A17="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A17))</f>
         <v>0</v>
       </c>
-      <c r="H17" s="17">
+      <c r="H17" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I17" s="17">
+      <c r="I17" s="15">
         <f>IF(A17="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A17))</f>
         <v>0</v>
       </c>
-      <c r="J17" s="17">
+      <c r="J17" s="15">
         <f>IF(A17="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A17))</f>
         <v>0</v>
       </c>
       <c r="K17" s="13"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="17" t="str">
+      <c r="A18" s="15" t="str">
         <f>IF(Players!A18="","",Players!A18)</f>
         <v>P015</v>
       </c>
-      <c r="B18" s="17" t="str">
+      <c r="B18" s="15" t="str">
         <f>IF(A18="","",IFERROR(VLOOKUP(A18,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Oliver Broyd</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="15">
         <f>IF(A18="","",IFERROR(VLOOKUP(A18,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>33</v>
       </c>
-      <c r="D18" s="17" t="str">
+      <c r="D18" s="15" t="str">
         <f>IF(A18="","",IFERROR(VLOOKUP(A18,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="15">
         <f>IF(A18="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A18,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F18" s="17">
+      <c r="F18" s="15">
         <f>IF(A18="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A18))</f>
         <v>0</v>
       </c>
-      <c r="G18" s="17">
+      <c r="G18" s="15">
         <f>IF(A18="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A18))</f>
         <v>0</v>
       </c>
-      <c r="H18" s="17">
+      <c r="H18" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I18" s="17">
+      <c r="I18" s="15">
         <f>IF(A18="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A18))</f>
         <v>0</v>
       </c>
-      <c r="J18" s="17">
+      <c r="J18" s="15">
         <f>IF(A18="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A18))</f>
         <v>0</v>
       </c>
       <c r="K18" s="13"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="17" t="str">
+      <c r="A19" s="15" t="str">
         <f>IF(Players!A19="","",Players!A19)</f>
         <v>P016</v>
       </c>
-      <c r="B19" s="17" t="str">
+      <c r="B19" s="15" t="str">
         <f>IF(A19="","",IFERROR(VLOOKUP(A19,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Connor Mellett</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="15">
         <f>IF(A19="","",IFERROR(VLOOKUP(A19,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>37</v>
       </c>
-      <c r="D19" s="17" t="str">
+      <c r="D19" s="15" t="str">
         <f>IF(A19="","",IFERROR(VLOOKUP(A19,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="15">
         <f>IF(A19="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A19,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="15">
         <f>IF(A19="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A19))</f>
         <v>0</v>
       </c>
-      <c r="G19" s="17">
+      <c r="G19" s="15">
         <f>IF(A19="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A19))</f>
         <v>0</v>
       </c>
-      <c r="H19" s="17">
+      <c r="H19" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I19" s="17">
+      <c r="I19" s="15">
         <f>IF(A19="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A19))</f>
         <v>0</v>
       </c>
-      <c r="J19" s="17">
+      <c r="J19" s="15">
         <f>IF(A19="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A19))</f>
         <v>0</v>
       </c>
       <c r="K19" s="13"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="17" t="str">
+      <c r="A20" s="15" t="str">
         <f>IF(Players!A20="","",Players!A20)</f>
         <v>P017</v>
       </c>
-      <c r="B20" s="17" t="str">
+      <c r="B20" s="15" t="str">
         <f>IF(A20="","",IFERROR(VLOOKUP(A20,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Hayden Hagger</v>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="15">
         <f>IF(A20="","",IFERROR(VLOOKUP(A20,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>45</v>
       </c>
-      <c r="D20" s="17" t="str">
+      <c r="D20" s="15" t="str">
         <f>IF(A20="","",IFERROR(VLOOKUP(A20,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="15">
         <f>IF(A20="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A20,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F20" s="17">
+      <c r="F20" s="15">
         <f>IF(A20="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A20))</f>
         <v>0</v>
       </c>
-      <c r="G20" s="17">
+      <c r="G20" s="15">
         <f>IF(A20="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A20))</f>
         <v>0</v>
       </c>
-      <c r="H20" s="17">
+      <c r="H20" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I20" s="17">
+      <c r="I20" s="15">
         <f>IF(A20="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A20))</f>
         <v>0</v>
       </c>
-      <c r="J20" s="17">
+      <c r="J20" s="15">
         <f>IF(A20="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A20))</f>
         <v>0</v>
       </c>
       <c r="K20" s="13"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="17" t="str">
+      <c r="A21" s="15" t="str">
         <f>IF(Players!A21="","",Players!A21)</f>
         <v>P018</v>
       </c>
-      <c r="B21" s="17" t="str">
+      <c r="B21" s="15" t="str">
         <f>IF(A21="","",IFERROR(VLOOKUP(A21,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Sam Purcell</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="15">
         <f>IF(A21="","",IFERROR(VLOOKUP(A21,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>64</v>
       </c>
-      <c r="D21" s="17" t="str">
+      <c r="D21" s="15" t="str">
         <f>IF(A21="","",IFERROR(VLOOKUP(A21,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="15">
         <f>IF(A21="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A21,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="15">
         <f>IF(A21="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A21))</f>
         <v>0</v>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="15">
         <f>IF(A21="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A21))</f>
         <v>0</v>
       </c>
-      <c r="H21" s="17">
+      <c r="H21" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I21" s="17">
+      <c r="I21" s="15">
         <f>IF(A21="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A21))</f>
         <v>0</v>
       </c>
-      <c r="J21" s="17">
+      <c r="J21" s="15">
         <f>IF(A21="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A21))</f>
         <v>0</v>
       </c>
       <c r="K21" s="13"/>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="17" t="str">
+      <c r="A22" s="15" t="str">
         <f>IF(Players!A22="","",Players!A22)</f>
         <v>P019</v>
       </c>
-      <c r="B22" s="17" t="str">
+      <c r="B22" s="15" t="str">
         <f>IF(A22="","",IFERROR(VLOOKUP(A22,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Samuel Rickard</v>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="15">
         <f>IF(A22="","",IFERROR(VLOOKUP(A22,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>65</v>
       </c>
-      <c r="D22" s="17" t="str">
+      <c r="D22" s="15" t="str">
         <f>IF(A22="","",IFERROR(VLOOKUP(A22,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E22" s="17">
+      <c r="E22" s="15">
         <f>IF(A22="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A22,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F22" s="17">
+      <c r="F22" s="15">
         <f>IF(A22="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A22))</f>
         <v>0</v>
       </c>
-      <c r="G22" s="17">
+      <c r="G22" s="15">
         <f>IF(A22="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A22))</f>
         <v>0</v>
       </c>
-      <c r="H22" s="17">
+      <c r="H22" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I22" s="17">
+      <c r="I22" s="15">
         <f>IF(A22="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A22))</f>
         <v>0</v>
       </c>
-      <c r="J22" s="17">
+      <c r="J22" s="15">
         <f>IF(A22="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A22))</f>
         <v>0</v>
       </c>
       <c r="K22" s="13"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="17" t="str">
+      <c r="A23" s="15" t="str">
         <f>IF(Players!A23="","",Players!A23)</f>
         <v>P020</v>
       </c>
-      <c r="B23" s="17" t="str">
+      <c r="B23" s="15" t="str">
         <f>IF(A23="","",IFERROR(VLOOKUP(A23,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Oscar Lee</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="15">
         <f>IF(A23="","",IFERROR(VLOOKUP(A23,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>68</v>
       </c>
-      <c r="D23" s="17" t="str">
+      <c r="D23" s="15" t="str">
         <f>IF(A23="","",IFERROR(VLOOKUP(A23,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="15">
         <f>IF(A23="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A23,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F23" s="17">
+      <c r="F23" s="15">
         <f>IF(A23="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A23))</f>
         <v>0</v>
       </c>
-      <c r="G23" s="17">
+      <c r="G23" s="15">
         <f>IF(A23="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A23))</f>
         <v>0</v>
       </c>
-      <c r="H23" s="17">
+      <c r="H23" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I23" s="17">
+      <c r="I23" s="15">
         <f>IF(A23="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A23))</f>
         <v>0</v>
       </c>
-      <c r="J23" s="17">
+      <c r="J23" s="15">
         <f>IF(A23="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A23))</f>
         <v>0</v>
       </c>
       <c r="K23" s="13"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="17" t="str">
+      <c r="A24" s="15" t="str">
         <f>IF(Players!A24="","",Players!A24)</f>
         <v>P021</v>
       </c>
-      <c r="B24" s="17" t="str">
+      <c r="B24" s="15" t="str">
         <f>IF(A24="","",IFERROR(VLOOKUP(A24,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Jacob Maidment</v>
       </c>
-      <c r="C24" s="17">
+      <c r="C24" s="15">
         <f>IF(A24="","",IFERROR(VLOOKUP(A24,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>89</v>
       </c>
-      <c r="D24" s="17" t="str">
+      <c r="D24" s="15" t="str">
         <f>IF(A24="","",IFERROR(VLOOKUP(A24,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="15">
         <f>IF(A24="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A24,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="15">
         <f>IF(A24="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A24))</f>
         <v>0</v>
       </c>
-      <c r="G24" s="17">
+      <c r="G24" s="15">
         <f>IF(A24="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A24))</f>
         <v>0</v>
       </c>
-      <c r="H24" s="17">
+      <c r="H24" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I24" s="17">
+      <c r="I24" s="15">
         <f>IF(A24="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A24))</f>
         <v>0</v>
       </c>
-      <c r="J24" s="17">
+      <c r="J24" s="15">
         <f>IF(A24="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A24))</f>
         <v>0</v>
       </c>
       <c r="K24" s="13"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="17" t="str">
+      <c r="A25" s="15" t="str">
         <f>IF(Players!A25="","",Players!A25)</f>
         <v>P022</v>
       </c>
-      <c r="B25" s="17" t="str">
+      <c r="B25" s="15" t="str">
         <f>IF(A25="","",IFERROR(VLOOKUP(A25,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Corey Taylor</v>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="15">
         <f>IF(A25="","",IFERROR(VLOOKUP(A25,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>16</v>
       </c>
-      <c r="D25" s="17" t="str">
+      <c r="D25" s="15" t="str">
         <f>IF(A25="","",IFERROR(VLOOKUP(A25,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E25" s="17">
+      <c r="E25" s="15">
         <f>IF(A25="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A25,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F25" s="17">
+      <c r="F25" s="15">
         <f>IF(A25="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A25))</f>
         <v>0</v>
       </c>
-      <c r="G25" s="17">
+      <c r="G25" s="15">
         <f>IF(A25="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A25))</f>
         <v>0</v>
       </c>
-      <c r="H25" s="17">
+      <c r="H25" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I25" s="17">
+      <c r="I25" s="15">
         <f>IF(A25="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A25))</f>
         <v>0</v>
       </c>
-      <c r="J25" s="17">
+      <c r="J25" s="15">
         <f>IF(A25="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A25))</f>
         <v>0</v>
       </c>
       <c r="K25" s="13"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="17" t="str">
+      <c r="A26" s="15" t="str">
         <f>IF(Players!A26="","",Players!A26)</f>
         <v>P023</v>
       </c>
-      <c r="B26" s="17" t="str">
+      <c r="B26" s="15" t="str">
         <f>IF(A26="","",IFERROR(VLOOKUP(A26,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>James Bryan</v>
       </c>
-      <c r="C26" s="17">
+      <c r="C26" s="15">
         <f>IF(A26="","",IFERROR(VLOOKUP(A26,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>23</v>
       </c>
-      <c r="D26" s="17" t="str">
+      <c r="D26" s="15" t="str">
         <f>IF(A26="","",IFERROR(VLOOKUP(A26,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E26" s="17">
+      <c r="E26" s="15">
         <f>IF(A26="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A26,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F26" s="17">
+      <c r="F26" s="15">
         <f>IF(A26="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A26))</f>
         <v>0</v>
       </c>
-      <c r="G26" s="17">
+      <c r="G26" s="15">
         <f>IF(A26="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A26))</f>
         <v>0</v>
       </c>
-      <c r="H26" s="17">
+      <c r="H26" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I26" s="17">
+      <c r="I26" s="15">
         <f>IF(A26="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A26))</f>
         <v>0</v>
       </c>
-      <c r="J26" s="17">
+      <c r="J26" s="15">
         <f>IF(A26="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A26))</f>
         <v>0</v>
       </c>
       <c r="K26" s="13"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="17" t="str">
+      <c r="A27" s="15" t="str">
         <f>IF(Players!A27="","",Players!A27)</f>
         <v>P024</v>
       </c>
-      <c r="B27" s="17" t="str">
+      <c r="B27" s="15" t="str">
         <f>IF(A27="","",IFERROR(VLOOKUP(A27,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Josh Furnell</v>
       </c>
-      <c r="C27" s="17">
+      <c r="C27" s="15">
         <f>IF(A27="","",IFERROR(VLOOKUP(A27,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>33</v>
       </c>
-      <c r="D27" s="17" t="str">
+      <c r="D27" s="15" t="str">
         <f>IF(A27="","",IFERROR(VLOOKUP(A27,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E27" s="17">
+      <c r="E27" s="15">
         <f>IF(A27="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A27,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F27" s="17">
+      <c r="F27" s="15">
         <f>IF(A27="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A27))</f>
         <v>0</v>
       </c>
-      <c r="G27" s="17">
+      <c r="G27" s="15">
         <f>IF(A27="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A27))</f>
         <v>0</v>
       </c>
-      <c r="H27" s="17">
+      <c r="H27" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I27" s="17">
+      <c r="I27" s="15">
         <f>IF(A27="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A27))</f>
         <v>0</v>
       </c>
-      <c r="J27" s="17">
+      <c r="J27" s="15">
         <f>IF(A27="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A27))</f>
         <v>0</v>
       </c>
       <c r="K27" s="13"/>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="17" t="str">
+      <c r="A28" s="15" t="str">
         <f>IF(Players!A28="","",Players!A28)</f>
         <v>P025</v>
       </c>
-      <c r="B28" s="17" t="str">
+      <c r="B28" s="15" t="str">
         <f>IF(A28="","",IFERROR(VLOOKUP(A28,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Josh Hickman</v>
       </c>
-      <c r="C28" s="17">
+      <c r="C28" s="15">
         <f>IF(A28="","",IFERROR(VLOOKUP(A28,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>40</v>
       </c>
-      <c r="D28" s="17" t="str">
+      <c r="D28" s="15" t="str">
         <f>IF(A28="","",IFERROR(VLOOKUP(A28,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E28" s="17">
+      <c r="E28" s="15">
         <f>IF(A28="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A28,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F28" s="17">
+      <c r="F28" s="15">
         <f>IF(A28="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A28))</f>
         <v>0</v>
       </c>
-      <c r="G28" s="17">
+      <c r="G28" s="15">
         <f>IF(A28="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A28))</f>
         <v>0</v>
       </c>
-      <c r="H28" s="17">
+      <c r="H28" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I28" s="17">
+      <c r="I28" s="15">
         <f>IF(A28="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A28))</f>
         <v>0</v>
       </c>
-      <c r="J28" s="17">
+      <c r="J28" s="15">
         <f>IF(A28="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A28))</f>
         <v>0</v>
       </c>
       <c r="K28" s="13"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="17" t="str">
+      <c r="A29" s="15" t="str">
         <f>IF(Players!A29="","",Players!A29)</f>
         <v>P026</v>
       </c>
-      <c r="B29" s="17" t="str">
+      <c r="B29" s="15" t="str">
         <f>IF(A29="","",IFERROR(VLOOKUP(A29,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Ryan Wonfor</v>
       </c>
-      <c r="C29" s="17">
+      <c r="C29" s="15">
         <f>IF(A29="","",IFERROR(VLOOKUP(A29,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>77</v>
       </c>
-      <c r="D29" s="17" t="str">
+      <c r="D29" s="15" t="str">
         <f>IF(A29="","",IFERROR(VLOOKUP(A29,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E29" s="17">
+      <c r="E29" s="15">
         <f>IF(A29="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A29,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F29" s="17">
+      <c r="F29" s="15">
         <f>IF(A29="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A29))</f>
         <v>0</v>
       </c>
-      <c r="G29" s="17">
+      <c r="G29" s="15">
         <f>IF(A29="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A29))</f>
         <v>0</v>
       </c>
-      <c r="H29" s="17">
+      <c r="H29" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I29" s="17">
+      <c r="I29" s="15">
         <f>IF(A29="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A29))</f>
         <v>0</v>
       </c>
-      <c r="J29" s="17">
+      <c r="J29" s="15">
         <f>IF(A29="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A29))</f>
         <v>0</v>
       </c>
       <c r="K29" s="13"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="17" t="str">
+      <c r="A30" s="15" t="str">
         <f>IF(Players!A30="","",Players!A30)</f>
         <v>P027</v>
       </c>
-      <c r="B30" s="17" t="str">
+      <c r="B30" s="15" t="str">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Charles Coney</v>
       </c>
-      <c r="C30" s="17">
+      <c r="C30" s="15">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>88</v>
       </c>
-      <c r="D30" s="17" t="str">
+      <c r="D30" s="15" t="str">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E30" s="17">
+      <c r="E30" s="15">
         <f>IF(A30="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A30,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F30" s="17">
+      <c r="F30" s="15">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
-      <c r="G30" s="17">
+      <c r="G30" s="15">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
-      <c r="H30" s="17">
+      <c r="H30" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I30" s="17">
+      <c r="I30" s="15">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
-      <c r="J30" s="17">
+      <c r="J30" s="15">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57891FBA-42DF-49DA-A51E-4965F9285BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32236E73-9F31-44DB-915F-3AE0FE5E054A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -5815,11 +5815,15 @@
       <c r="F4" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
+      <c r="G4" s="7">
+        <v>4</v>
+      </c>
+      <c r="H4" s="7">
+        <v>3</v>
+      </c>
       <c r="I4" s="10" t="str">
         <f t="shared" ref="I4:I35" si="0">IF(OR(G4="",H4=""),"",IF(G4&gt;H4,"W",IF(G4&lt;H4,"L","T")))</f>
-        <v/>
+        <v>W</v>
       </c>
       <c r="J4" s="7"/>
       <c r="K4" s="7" t="s">
@@ -24098,7 +24102,7 @@
       </c>
       <c r="M4" s="12">
         <f>SUM(Games!$G$4:$G$200)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -24148,7 +24152,7 @@
       </c>
       <c r="M5" s="12">
         <f>SUM(Games!$H$4:$H$200)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -24198,7 +24202,7 @@
       </c>
       <c r="M6" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"W")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32236E73-9F31-44DB-915F-3AE0FE5E054A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E59B82-7F53-447F-9EA1-DC0B9B5B098C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="286">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -869,6 +869,39 @@
   </si>
   <si>
     <t>macGarvey.png</t>
+  </si>
+  <si>
+    <t>hagger.png</t>
+  </si>
+  <si>
+    <t>purcell.png</t>
+  </si>
+  <si>
+    <t>rickard.png</t>
+  </si>
+  <si>
+    <t>maidment.png</t>
+  </si>
+  <si>
+    <t>taylor.png</t>
+  </si>
+  <si>
+    <t>bryan.png</t>
+  </si>
+  <si>
+    <t>furnell.png</t>
+  </si>
+  <si>
+    <t>hickman.png</t>
+  </si>
+  <si>
+    <t>wonfor.png</t>
+  </si>
+  <si>
+    <t>coney.png</t>
+  </si>
+  <si>
+    <t>oscar.png</t>
   </si>
 </sst>
 </file>
@@ -3978,7 +4011,9 @@
       <c r="E20" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="7"/>
+      <c r="F20" s="7" t="s">
+        <v>275</v>
+      </c>
       <c r="G20" s="7"/>
     </row>
     <row r="21" spans="1:7">
@@ -3997,7 +4032,9 @@
       <c r="E21" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F21" s="7"/>
+      <c r="F21" s="7" t="s">
+        <v>276</v>
+      </c>
       <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:7">
@@ -4016,7 +4053,9 @@
       <c r="E22" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="7"/>
+      <c r="F22" s="7" t="s">
+        <v>277</v>
+      </c>
       <c r="G22" s="7"/>
     </row>
     <row r="23" spans="1:7">
@@ -4035,7 +4074,9 @@
       <c r="E23" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F23" s="7"/>
+      <c r="F23" s="7" t="s">
+        <v>285</v>
+      </c>
       <c r="G23" s="7"/>
     </row>
     <row r="24" spans="1:7">
@@ -4054,7 +4095,9 @@
       <c r="E24" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F24" s="7"/>
+      <c r="F24" s="7" t="s">
+        <v>278</v>
+      </c>
       <c r="G24" s="7"/>
     </row>
     <row r="25" spans="1:7">
@@ -4073,7 +4116,9 @@
       <c r="E25" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="7"/>
+      <c r="F25" s="7" t="s">
+        <v>279</v>
+      </c>
       <c r="G25" s="7"/>
     </row>
     <row r="26" spans="1:7">
@@ -4092,7 +4137,9 @@
       <c r="E26" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F26" s="7"/>
+      <c r="F26" s="7" t="s">
+        <v>280</v>
+      </c>
       <c r="G26" s="7"/>
     </row>
     <row r="27" spans="1:7">
@@ -4111,7 +4158,9 @@
       <c r="E27" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F27" s="7"/>
+      <c r="F27" s="7" t="s">
+        <v>281</v>
+      </c>
       <c r="G27" s="7"/>
     </row>
     <row r="28" spans="1:7">
@@ -4130,7 +4179,9 @@
       <c r="E28" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F28" s="7"/>
+      <c r="F28" s="7" t="s">
+        <v>282</v>
+      </c>
       <c r="G28" s="7"/>
     </row>
     <row r="29" spans="1:7">
@@ -4149,7 +4200,9 @@
       <c r="E29" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F29" s="7"/>
+      <c r="F29" s="7" t="s">
+        <v>283</v>
+      </c>
       <c r="G29" s="7"/>
     </row>
     <row r="30" spans="1:7">
@@ -4168,17 +4221,19 @@
       <c r="E30" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F30" s="7"/>
+      <c r="F30" s="7" t="s">
+        <v>284</v>
+      </c>
       <c r="G30" s="7"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2"/>
@@ -5815,15 +5870,11 @@
       <c r="F4" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="G4" s="7">
-        <v>4</v>
-      </c>
-      <c r="H4" s="7">
-        <v>3</v>
-      </c>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
       <c r="I4" s="10" t="str">
         <f t="shared" ref="I4:I35" si="0">IF(OR(G4="",H4=""),"",IF(G4&gt;H4,"W",IF(G4&lt;H4,"L","T")))</f>
-        <v>W</v>
+        <v/>
       </c>
       <c r="J4" s="7"/>
       <c r="K4" s="7" t="s">
@@ -24102,7 +24153,7 @@
       </c>
       <c r="M4" s="12">
         <f>SUM(Games!$G$4:$G$200)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -24152,7 +24203,7 @@
       </c>
       <c r="M5" s="12">
         <f>SUM(Games!$H$4:$H$200)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -24202,7 +24253,7 @@
       </c>
       <c r="M6" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"W")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:13">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E59B82-7F53-447F-9EA1-DC0B9B5B098C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9ECC8503-CA9E-41BF-9B61-3F0FCDBC0171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="8" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="292">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -505,24 +505,36 @@
     <t>Xander Robinson</t>
   </si>
   <si>
+    <t>robinson.png</t>
+  </si>
+  <si>
     <t>P012</t>
   </si>
   <si>
     <t>Joshua Blackwood</t>
   </si>
   <si>
+    <t>Josh.png</t>
+  </si>
+  <si>
     <t>P013</t>
   </si>
   <si>
     <t>Harry MacGarvery</t>
   </si>
   <si>
+    <t>macGarvey.png</t>
+  </si>
+  <si>
     <t>P014</t>
   </si>
   <si>
     <t>Chalie Conroy</t>
   </si>
   <si>
+    <t>conroy.png</t>
+  </si>
+  <si>
     <t>P015</t>
   </si>
   <si>
@@ -535,72 +547,126 @@
     <t>Connor Mellett</t>
   </si>
   <si>
+    <t>mellett.png</t>
+  </si>
+  <si>
     <t>P017</t>
   </si>
   <si>
     <t>Hayden Hagger</t>
   </si>
   <si>
+    <t>hagger.png</t>
+  </si>
+  <si>
     <t>P018</t>
   </si>
   <si>
     <t>Sam Purcell</t>
   </si>
   <si>
+    <t>purcell.png</t>
+  </si>
+  <si>
     <t>P019</t>
   </si>
   <si>
     <t>Samuel Rickard</t>
   </si>
   <si>
+    <t>rickard.png</t>
+  </si>
+  <si>
     <t>P020</t>
   </si>
   <si>
     <t>Oscar Lee</t>
   </si>
   <si>
+    <t>oscar.png</t>
+  </si>
+  <si>
     <t>P021</t>
   </si>
   <si>
     <t>Jacob Maidment</t>
   </si>
   <si>
+    <t>maidment.png</t>
+  </si>
+  <si>
     <t>P022</t>
   </si>
   <si>
     <t>Corey Taylor</t>
   </si>
   <si>
+    <t>taylor.png</t>
+  </si>
+  <si>
     <t>P023</t>
   </si>
   <si>
     <t>James Bryan</t>
   </si>
   <si>
+    <t>bryan.png</t>
+  </si>
+  <si>
     <t>P024</t>
   </si>
   <si>
     <t>Josh Furnell</t>
   </si>
   <si>
+    <t>furnell.png</t>
+  </si>
+  <si>
     <t>P025</t>
   </si>
   <si>
     <t>Josh Hickman</t>
   </si>
   <si>
+    <t>hickman.png</t>
+  </si>
+  <si>
     <t>P026</t>
   </si>
   <si>
     <t>Ryan Wonfor</t>
   </si>
   <si>
+    <t>wonfor.png</t>
+  </si>
+  <si>
     <t>P027</t>
   </si>
   <si>
     <t>Charles Coney</t>
   </si>
   <si>
+    <t>coney.png</t>
+  </si>
+  <si>
+    <t>P028</t>
+  </si>
+  <si>
+    <t>Will Nowik</t>
+  </si>
+  <si>
+    <t>nowik.png</t>
+  </si>
+  <si>
+    <t>P029</t>
+  </si>
+  <si>
+    <t>James Moeller</t>
+  </si>
+  <si>
+    <t>moeller.png</t>
+  </si>
+  <si>
     <t>Game ID</t>
   </si>
   <si>
@@ -854,54 +920,6 @@
   </si>
   <si>
     <t>Losses</t>
-  </si>
-  <si>
-    <t>robinson.png</t>
-  </si>
-  <si>
-    <t>conroy.png</t>
-  </si>
-  <si>
-    <t>mellett.png</t>
-  </si>
-  <si>
-    <t>Josh.png</t>
-  </si>
-  <si>
-    <t>macGarvey.png</t>
-  </si>
-  <si>
-    <t>hagger.png</t>
-  </si>
-  <si>
-    <t>purcell.png</t>
-  </si>
-  <si>
-    <t>rickard.png</t>
-  </si>
-  <si>
-    <t>maidment.png</t>
-  </si>
-  <si>
-    <t>taylor.png</t>
-  </si>
-  <si>
-    <t>bryan.png</t>
-  </si>
-  <si>
-    <t>furnell.png</t>
-  </si>
-  <si>
-    <t>hickman.png</t>
-  </si>
-  <si>
-    <t>wonfor.png</t>
-  </si>
-  <si>
-    <t>coney.png</t>
-  </si>
-  <si>
-    <t>oscar.png</t>
   </si>
 </sst>
 </file>
@@ -1020,7 +1038,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1039,14 +1057,16 @@
     <xf numFmtId="165" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1385,7 +1405,7 @@
       <c r="E1" s="17"/>
       <c r="F1" s="17"/>
       <c r="G1" s="17"/>
-      <c r="H1" s="14"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="3" spans="1:8" ht="15">
       <c r="A3" s="6" t="s">
@@ -3613,7 +3633,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G200"/>
+  <dimension ref="A1:H200"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="8.5" customWidth="1"/>
@@ -3888,16 +3908,16 @@
         <v>36</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>270</v>
+        <v>153</v>
       </c>
       <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C15" s="7">
         <v>18</v>
@@ -3909,16 +3929,16 @@
         <v>36</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>273</v>
+        <v>156</v>
       </c>
       <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="7" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C16" s="7">
         <v>22</v>
@@ -3930,16 +3950,16 @@
         <v>36</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>274</v>
+        <v>159</v>
       </c>
       <c r="G16" s="7"/>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:8">
       <c r="A17" s="7" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C17" s="7">
         <v>24</v>
@@ -3951,16 +3971,16 @@
         <v>36</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>271</v>
+        <v>162</v>
       </c>
       <c r="G17" s="7"/>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:8">
       <c r="A18" s="7" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C18" s="7">
         <v>33</v>
@@ -3974,12 +3994,12 @@
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:8">
       <c r="A19" s="7" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C19" s="7">
         <v>37</v>
@@ -3991,16 +4011,16 @@
         <v>36</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>272</v>
+        <v>167</v>
       </c>
       <c r="G19" s="7"/>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:8">
       <c r="A20" s="7" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C20" s="7">
         <v>45</v>
@@ -4012,16 +4032,16 @@
         <v>36</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>275</v>
+        <v>170</v>
       </c>
       <c r="G20" s="7"/>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:8">
       <c r="A21" s="7" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C21" s="7">
         <v>64</v>
@@ -4033,16 +4053,16 @@
         <v>36</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>276</v>
+        <v>173</v>
       </c>
       <c r="G21" s="7"/>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:8">
       <c r="A22" s="7" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C22" s="7">
         <v>65</v>
@@ -4054,16 +4074,16 @@
         <v>36</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>277</v>
+        <v>176</v>
       </c>
       <c r="G22" s="7"/>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:8">
       <c r="A23" s="7" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C23" s="7">
         <v>68</v>
@@ -4075,16 +4095,16 @@
         <v>36</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>285</v>
+        <v>179</v>
       </c>
       <c r="G23" s="7"/>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:8">
       <c r="A24" s="7" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="C24" s="7">
         <v>89</v>
@@ -4096,16 +4116,16 @@
         <v>36</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>278</v>
+        <v>182</v>
       </c>
       <c r="G24" s="7"/>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:8">
       <c r="A25" s="7" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="C25" s="7">
         <v>16</v>
@@ -4117,16 +4137,16 @@
         <v>36</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>279</v>
+        <v>185</v>
       </c>
       <c r="G25" s="7"/>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:8">
       <c r="A26" s="7" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="C26" s="7">
         <v>23</v>
@@ -4138,16 +4158,16 @@
         <v>36</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>280</v>
+        <v>188</v>
       </c>
       <c r="G26" s="7"/>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:8">
       <c r="A27" s="7" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="C27" s="7">
         <v>33</v>
@@ -4159,16 +4179,16 @@
         <v>36</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>281</v>
+        <v>191</v>
       </c>
       <c r="G27" s="7"/>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:8">
       <c r="A28" s="7" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="C28" s="7">
         <v>40</v>
@@ -4180,16 +4200,16 @@
         <v>36</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>282</v>
+        <v>194</v>
       </c>
       <c r="G28" s="7"/>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:8">
       <c r="A29" s="7" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="C29" s="7">
         <v>77</v>
@@ -4201,16 +4221,16 @@
         <v>36</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>283</v>
+        <v>197</v>
       </c>
       <c r="G29" s="7"/>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:8">
       <c r="A30" s="7" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="C30" s="7">
         <v>88</v>
@@ -4222,27 +4242,52 @@
         <v>36</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>284</v>
+        <v>200</v>
       </c>
       <c r="G30" s="7"/>
     </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
+    <row r="31" spans="1:8">
+      <c r="A31" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="C31" s="19">
+        <v>98</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="G31" s="19"/>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="C32" s="18">
+        <v>81</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="F32" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="G32" s="18"/>
+      <c r="H32" s="13"/>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2"/>
@@ -5812,40 +5857,40 @@
     <row r="2" spans="1:13"/>
     <row r="3" spans="1:13" ht="30">
       <c r="A3" s="6" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="M3" s="6" t="s">
         <v>116</v>
@@ -5853,7 +5898,7 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="7" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="B4" s="8">
         <v>46264</v>
@@ -5865,10 +5910,10 @@
         <v>37</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
@@ -5881,13 +5926,13 @@
         <v>41</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="M4" s="7"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="7" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="B5" s="8">
         <v>46270</v>
@@ -5899,10 +5944,10 @@
         <v>42</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
@@ -5915,13 +5960,13 @@
         <v>46</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="M5" s="7"/>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="7" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="B6" s="8">
         <v>46278</v>
@@ -5933,10 +5978,10 @@
         <v>47</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
@@ -5946,16 +5991,16 @@
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="M6" s="7"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="7" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="B7" s="8">
         <v>46284</v>
@@ -5967,10 +6012,10 @@
         <v>52</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
@@ -5980,13 +6025,13 @@
         <v>56</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="M7" s="7"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="7" t="s">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="B8" s="8">
         <v>46285</v>
@@ -5998,10 +6043,10 @@
         <v>58</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
@@ -6011,16 +6056,16 @@
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="M8" s="7"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="7" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="B9" s="8">
         <v>46291</v>
@@ -6032,10 +6077,10 @@
         <v>74</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
@@ -6048,13 +6093,13 @@
         <v>78</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="M9" s="7"/>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="7" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B10" s="8">
         <v>46298</v>
@@ -6066,10 +6111,10 @@
         <v>101</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
@@ -6079,16 +6124,16 @@
       </c>
       <c r="J10" s="7"/>
       <c r="K10" s="7" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="M10" s="7"/>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="7" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="B11" s="8">
         <v>46306</v>
@@ -6100,10 +6145,10 @@
         <v>106</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
@@ -6113,16 +6158,16 @@
       </c>
       <c r="J11" s="7"/>
       <c r="K11" s="7" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="M11" s="7"/>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="7" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="B12" s="8">
         <v>46312</v>
@@ -6134,10 +6179,10 @@
         <v>101</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
@@ -6150,13 +6195,13 @@
         <v>105</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="M12" s="7"/>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="7" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="B13" s="8">
         <v>46320</v>
@@ -6168,10 +6213,10 @@
         <v>95</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
@@ -6181,16 +6226,16 @@
       </c>
       <c r="J13" s="7"/>
       <c r="K13" s="7" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="M13" s="7"/>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="7" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="B14" s="8">
         <v>46327</v>
@@ -6202,10 +6247,10 @@
         <v>47</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
@@ -6218,13 +6263,13 @@
         <v>51</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="M14" s="7"/>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="7" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="B15" s="8">
         <v>46334</v>
@@ -6236,10 +6281,10 @@
         <v>52</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
@@ -6249,16 +6294,16 @@
       </c>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="M15" s="7"/>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="7" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="B16" s="8">
         <v>46340</v>
@@ -6270,10 +6315,10 @@
         <v>74</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
@@ -6283,16 +6328,16 @@
       </c>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="M16" s="7"/>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="7" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="B17" s="8">
         <v>46341</v>
@@ -6304,10 +6349,10 @@
         <v>95</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -6320,13 +6365,13 @@
         <v>99</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="M17" s="7"/>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="7" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="B18" s="8">
         <v>46354</v>
@@ -6338,10 +6383,10 @@
         <v>85</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
@@ -6354,13 +6399,13 @@
         <v>89</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="M18" s="7"/>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="7" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="B19" s="8">
         <v>46355</v>
@@ -6372,10 +6417,10 @@
         <v>58</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
@@ -6388,13 +6433,13 @@
         <v>62</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="M19" s="7"/>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="7" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="B20" s="8">
         <v>46368</v>
@@ -6406,10 +6451,10 @@
         <v>63</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
@@ -6422,13 +6467,13 @@
         <v>67</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="M20" s="7"/>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="7" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="B21" s="8">
         <v>46369</v>
@@ -6440,10 +6485,10 @@
         <v>68</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
@@ -6453,16 +6498,16 @@
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="M21" s="7"/>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="7" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="B22" s="8">
         <v>46376</v>
@@ -6474,10 +6519,10 @@
         <v>85</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
@@ -6487,16 +6532,16 @@
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="M22" s="7"/>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="7" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="B23" s="8">
         <v>46397</v>
@@ -6508,10 +6553,10 @@
         <v>80</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
@@ -6521,16 +6566,16 @@
       </c>
       <c r="J23" s="7"/>
       <c r="K23" s="7" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="M23" s="7"/>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="7" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="B24" s="8">
         <v>46417</v>
@@ -6542,10 +6587,10 @@
         <v>90</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
@@ -6555,16 +6600,16 @@
       </c>
       <c r="J24" s="7"/>
       <c r="K24" s="7" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="M24" s="7"/>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="7" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="B25" s="8">
         <v>46425</v>
@@ -6576,10 +6621,10 @@
         <v>63</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
@@ -6589,16 +6634,16 @@
       </c>
       <c r="J25" s="7"/>
       <c r="K25" s="7" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="M25" s="7"/>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="7" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="B26" s="8">
         <v>46446</v>
@@ -6610,10 +6655,10 @@
         <v>80</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
@@ -6626,13 +6671,13 @@
         <v>84</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="M26" s="7"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="7" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="B27" s="8">
         <v>46452</v>
@@ -6644,10 +6689,10 @@
         <v>68</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="G27" s="7"/>
       <c r="H27" s="7"/>
@@ -6660,13 +6705,13 @@
         <v>72</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="M27" s="7"/>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="7" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="B28" s="8">
         <v>46459</v>
@@ -6678,10 +6723,10 @@
         <v>106</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
@@ -6694,13 +6739,13 @@
         <v>110</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="M28" s="7"/>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="7" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="B29" s="8">
         <v>46467</v>
@@ -6712,10 +6757,10 @@
         <v>90</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
@@ -6728,7 +6773,7 @@
         <v>94</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="M29" s="7"/>
     </row>
@@ -9845,7 +9890,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
       <c r="A1" s="17" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -9859,31 +9904,31 @@
     </row>
     <row r="3" spans="1:10" ht="30">
       <c r="A3" s="6" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>111</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="J3" s="6" t="s">
         <v>116</v>
@@ -18880,7 +18925,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20.25">
       <c r="A1" s="17" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -18895,7 +18940,7 @@
     </row>
     <row r="3" spans="1:11" ht="30">
       <c r="A3" s="6" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>111</v>
@@ -18904,25 +18949,25 @@
         <v>131</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>116</v>
@@ -23303,7 +23348,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
       <c r="A1" s="17" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -23317,34 +23362,34 @@
     </row>
     <row r="3" spans="1:10" ht="15">
       <c r="A3" s="6" t="s">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -23781,7 +23826,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
       <c r="A1" s="17" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -23795,34 +23840,34 @@
     </row>
     <row r="3" spans="1:10" ht="15">
       <c r="A3" s="6" t="s">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -24046,7 +24091,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
       <c r="A1" s="17" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -24060,10 +24105,10 @@
     </row>
     <row r="2" spans="1:13" ht="15">
       <c r="L2" s="6" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="30">
@@ -24071,35 +24116,35 @@
         <v>111</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="K3" s="13"/>
       <c r="L3" s="12" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="M3" s="12">
         <f>COUNT(Games!$A$4:$A$200)</f>
@@ -24149,7 +24194,7 @@
       </c>
       <c r="K4" s="13"/>
       <c r="L4" s="12" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="M4" s="12">
         <f>SUM(Games!$G$4:$G$200)</f>
@@ -24199,7 +24244,7 @@
       </c>
       <c r="K5" s="13"/>
       <c r="L5" s="12" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="M5" s="12">
         <f>SUM(Games!$H$4:$H$200)</f>
@@ -24249,7 +24294,7 @@
       </c>
       <c r="K6" s="13"/>
       <c r="L6" s="12" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="M6" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"W")</f>
@@ -24299,7 +24344,7 @@
       </c>
       <c r="K7" s="13"/>
       <c r="L7" s="12" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="M7" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"L")</f>
@@ -24352,43 +24397,43 @@
       <c r="M8" s="12"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="16" t="str">
+      <c r="A9" s="15" t="str">
         <f>IF(Players!A9="","",Players!A9)</f>
         <v>P006</v>
       </c>
-      <c r="B9" s="16" t="str">
+      <c r="B9" s="15" t="str">
         <f>IF(A9="","",IFERROR(VLOOKUP(A9,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Lewis Smith</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="15">
         <f>IF(A9="","",IFERROR(VLOOKUP(A9,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>13</v>
       </c>
-      <c r="D9" s="16" t="str">
+      <c r="D9" s="15" t="str">
         <f>IF(A9="","",IFERROR(VLOOKUP(A9,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="15">
         <f>IF(A9="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A9,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="15">
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
         <v>0</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="15">
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
         <v>0</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="15">
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
         <v>0</v>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="15">
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
         <v>0</v>
       </c>
@@ -24396,903 +24441,903 @@
       <c r="L9" s="13"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="15" t="str">
+      <c r="A10" s="14" t="str">
         <f>IF(Players!A10="","",Players!A10)</f>
         <v>P007</v>
       </c>
-      <c r="B10" s="15" t="str">
+      <c r="B10" s="14" t="str">
         <f>IF(A10="","",IFERROR(VLOOKUP(A10,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Robert Oxley</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="14">
         <f>IF(A10="","",IFERROR(VLOOKUP(A10,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>5</v>
       </c>
-      <c r="D10" s="15" t="str">
+      <c r="D10" s="14" t="str">
         <f>IF(A10="","",IFERROR(VLOOKUP(A10,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="14">
         <f>IF(A10="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A10,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="14">
         <f>IF(A10="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A10))</f>
         <v>0</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="14">
         <f>IF(A10="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A10))</f>
         <v>0</v>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I10" s="15">
+      <c r="I10" s="14">
         <f>IF(A10="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A10))</f>
         <v>0</v>
       </c>
-      <c r="J10" s="15">
+      <c r="J10" s="14">
         <f>IF(A10="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A10))</f>
         <v>0</v>
       </c>
       <c r="K10" s="13"/>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="15" t="str">
+      <c r="A11" s="14" t="str">
         <f>IF(Players!A11="","",Players!A11)</f>
         <v>P008</v>
       </c>
-      <c r="B11" s="15" t="str">
+      <c r="B11" s="14" t="str">
         <f>IF(A11="","",IFERROR(VLOOKUP(A11,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Madi Wright</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="14">
         <f>IF(A11="","",IFERROR(VLOOKUP(A11,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>10</v>
       </c>
-      <c r="D11" s="15" t="str">
+      <c r="D11" s="14" t="str">
         <f>IF(A11="","",IFERROR(VLOOKUP(A11,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="14">
         <f>IF(A11="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A11,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="14">
         <f>IF(A11="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A11))</f>
         <v>0</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="14">
         <f>IF(A11="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A11))</f>
         <v>0</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I11" s="15">
+      <c r="I11" s="14">
         <f>IF(A11="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A11))</f>
         <v>0</v>
       </c>
-      <c r="J11" s="15">
+      <c r="J11" s="14">
         <f>IF(A11="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A11))</f>
         <v>0</v>
       </c>
       <c r="K11" s="13"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="15" t="str">
+      <c r="A12" s="14" t="str">
         <f>IF(Players!A12="","",Players!A12)</f>
         <v>P009</v>
       </c>
-      <c r="B12" s="15" t="str">
+      <c r="B12" s="14" t="str">
         <f>IF(A12="","",IFERROR(VLOOKUP(A12,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Lizzie Nowik</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="14">
         <f>IF(A12="","",IFERROR(VLOOKUP(A12,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>2</v>
       </c>
-      <c r="D12" s="15" t="str">
+      <c r="D12" s="14" t="str">
         <f>IF(A12="","",IFERROR(VLOOKUP(A12,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Netminder</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="14">
         <f>IF(A12="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A12,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F12" s="15">
+      <c r="F12" s="14">
         <f>IF(A12="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A12))</f>
         <v>0</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="14">
         <f>IF(A12="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A12))</f>
         <v>0</v>
       </c>
-      <c r="H12" s="15">
+      <c r="H12" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I12" s="15">
+      <c r="I12" s="14">
         <f>IF(A12="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A12))</f>
         <v>0</v>
       </c>
-      <c r="J12" s="15">
+      <c r="J12" s="14">
         <f>IF(A12="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A12))</f>
         <v>0</v>
       </c>
       <c r="K12" s="13"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="15" t="str">
+      <c r="A13" s="14" t="str">
         <f>IF(Players!A13="","",Players!A13)</f>
         <v>P010</v>
       </c>
-      <c r="B13" s="15" t="str">
+      <c r="B13" s="14" t="str">
         <f>IF(A13="","",IFERROR(VLOOKUP(A13,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Nicole Jackson</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="14">
         <f>IF(A13="","",IFERROR(VLOOKUP(A13,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>86</v>
       </c>
-      <c r="D13" s="15" t="str">
+      <c r="D13" s="14" t="str">
         <f>IF(A13="","",IFERROR(VLOOKUP(A13,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Netminder</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="14">
         <f>IF(A13="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A13,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="14">
         <f>IF(A13="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A13))</f>
         <v>0</v>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="14">
         <f>IF(A13="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A13))</f>
         <v>0</v>
       </c>
-      <c r="H13" s="15">
+      <c r="H13" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I13" s="15">
+      <c r="I13" s="14">
         <f>IF(A13="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A13))</f>
         <v>0</v>
       </c>
-      <c r="J13" s="15">
+      <c r="J13" s="14">
         <f>IF(A13="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A13))</f>
         <v>0</v>
       </c>
       <c r="K13" s="13"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="15" t="str">
+      <c r="A14" s="14" t="str">
         <f>IF(Players!A14="","",Players!A14)</f>
         <v>P011</v>
       </c>
-      <c r="B14" s="15" t="str">
+      <c r="B14" s="14" t="str">
         <f>IF(A14="","",IFERROR(VLOOKUP(A14,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Xander Robinson</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="14">
         <f>IF(A14="","",IFERROR(VLOOKUP(A14,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>14</v>
       </c>
-      <c r="D14" s="15" t="str">
+      <c r="D14" s="14" t="str">
         <f>IF(A14="","",IFERROR(VLOOKUP(A14,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="14">
         <f>IF(A14="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A14,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="14">
         <f>IF(A14="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A14))</f>
         <v>0</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="14">
         <f>IF(A14="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A14))</f>
         <v>0</v>
       </c>
-      <c r="H14" s="15">
+      <c r="H14" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I14" s="15">
+      <c r="I14" s="14">
         <f>IF(A14="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A14))</f>
         <v>0</v>
       </c>
-      <c r="J14" s="15">
+      <c r="J14" s="14">
         <f>IF(A14="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A14))</f>
         <v>0</v>
       </c>
       <c r="K14" s="13"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="15" t="str">
+      <c r="A15" s="14" t="str">
         <f>IF(Players!A15="","",Players!A15)</f>
         <v>P012</v>
       </c>
-      <c r="B15" s="15" t="str">
+      <c r="B15" s="14" t="str">
         <f>IF(A15="","",IFERROR(VLOOKUP(A15,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Joshua Blackwood</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="14">
         <f>IF(A15="","",IFERROR(VLOOKUP(A15,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>18</v>
       </c>
-      <c r="D15" s="15" t="str">
+      <c r="D15" s="14" t="str">
         <f>IF(A15="","",IFERROR(VLOOKUP(A15,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="14">
         <f>IF(A15="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A15,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="14">
         <f>IF(A15="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A15))</f>
         <v>0</v>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="14">
         <f>IF(A15="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A15))</f>
         <v>0</v>
       </c>
-      <c r="H15" s="15">
+      <c r="H15" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I15" s="15">
+      <c r="I15" s="14">
         <f>IF(A15="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A15))</f>
         <v>0</v>
       </c>
-      <c r="J15" s="15">
+      <c r="J15" s="14">
         <f>IF(A15="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A15))</f>
         <v>0</v>
       </c>
       <c r="K15" s="13"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="15" t="str">
+      <c r="A16" s="14" t="str">
         <f>IF(Players!A16="","",Players!A16)</f>
         <v>P013</v>
       </c>
-      <c r="B16" s="15" t="str">
+      <c r="B16" s="14" t="str">
         <f>IF(A16="","",IFERROR(VLOOKUP(A16,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Harry MacGarvery</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="14">
         <f>IF(A16="","",IFERROR(VLOOKUP(A16,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>22</v>
       </c>
-      <c r="D16" s="15" t="str">
+      <c r="D16" s="14" t="str">
         <f>IF(A16="","",IFERROR(VLOOKUP(A16,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="14">
         <f>IF(A16="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A16,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="14">
         <f>IF(A16="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A16))</f>
         <v>0</v>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="14">
         <f>IF(A16="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A16))</f>
         <v>0</v>
       </c>
-      <c r="H16" s="15">
+      <c r="H16" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I16" s="15">
+      <c r="I16" s="14">
         <f>IF(A16="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A16))</f>
         <v>0</v>
       </c>
-      <c r="J16" s="15">
+      <c r="J16" s="14">
         <f>IF(A16="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A16))</f>
         <v>0</v>
       </c>
       <c r="K16" s="13"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="15" t="str">
+      <c r="A17" s="14" t="str">
         <f>IF(Players!A17="","",Players!A17)</f>
         <v>P014</v>
       </c>
-      <c r="B17" s="15" t="str">
+      <c r="B17" s="14" t="str">
         <f>IF(A17="","",IFERROR(VLOOKUP(A17,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Chalie Conroy</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="14">
         <f>IF(A17="","",IFERROR(VLOOKUP(A17,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>24</v>
       </c>
-      <c r="D17" s="15" t="str">
+      <c r="D17" s="14" t="str">
         <f>IF(A17="","",IFERROR(VLOOKUP(A17,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="14">
         <f>IF(A17="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A17,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="14">
         <f>IF(A17="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A17))</f>
         <v>0</v>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="14">
         <f>IF(A17="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A17))</f>
         <v>0</v>
       </c>
-      <c r="H17" s="15">
+      <c r="H17" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I17" s="15">
+      <c r="I17" s="14">
         <f>IF(A17="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A17))</f>
         <v>0</v>
       </c>
-      <c r="J17" s="15">
+      <c r="J17" s="14">
         <f>IF(A17="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A17))</f>
         <v>0</v>
       </c>
       <c r="K17" s="13"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="15" t="str">
+      <c r="A18" s="14" t="str">
         <f>IF(Players!A18="","",Players!A18)</f>
         <v>P015</v>
       </c>
-      <c r="B18" s="15" t="str">
+      <c r="B18" s="14" t="str">
         <f>IF(A18="","",IFERROR(VLOOKUP(A18,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Oliver Broyd</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="14">
         <f>IF(A18="","",IFERROR(VLOOKUP(A18,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>33</v>
       </c>
-      <c r="D18" s="15" t="str">
+      <c r="D18" s="14" t="str">
         <f>IF(A18="","",IFERROR(VLOOKUP(A18,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="14">
         <f>IF(A18="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A18,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="14">
         <f>IF(A18="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A18))</f>
         <v>0</v>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="14">
         <f>IF(A18="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A18))</f>
         <v>0</v>
       </c>
-      <c r="H18" s="15">
+      <c r="H18" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I18" s="15">
+      <c r="I18" s="14">
         <f>IF(A18="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A18))</f>
         <v>0</v>
       </c>
-      <c r="J18" s="15">
+      <c r="J18" s="14">
         <f>IF(A18="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A18))</f>
         <v>0</v>
       </c>
       <c r="K18" s="13"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="15" t="str">
+      <c r="A19" s="14" t="str">
         <f>IF(Players!A19="","",Players!A19)</f>
         <v>P016</v>
       </c>
-      <c r="B19" s="15" t="str">
+      <c r="B19" s="14" t="str">
         <f>IF(A19="","",IFERROR(VLOOKUP(A19,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Connor Mellett</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="14">
         <f>IF(A19="","",IFERROR(VLOOKUP(A19,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>37</v>
       </c>
-      <c r="D19" s="15" t="str">
+      <c r="D19" s="14" t="str">
         <f>IF(A19="","",IFERROR(VLOOKUP(A19,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="14">
         <f>IF(A19="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A19,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="14">
         <f>IF(A19="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A19))</f>
         <v>0</v>
       </c>
-      <c r="G19" s="15">
+      <c r="G19" s="14">
         <f>IF(A19="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A19))</f>
         <v>0</v>
       </c>
-      <c r="H19" s="15">
+      <c r="H19" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I19" s="15">
+      <c r="I19" s="14">
         <f>IF(A19="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A19))</f>
         <v>0</v>
       </c>
-      <c r="J19" s="15">
+      <c r="J19" s="14">
         <f>IF(A19="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A19))</f>
         <v>0</v>
       </c>
       <c r="K19" s="13"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="15" t="str">
+      <c r="A20" s="14" t="str">
         <f>IF(Players!A20="","",Players!A20)</f>
         <v>P017</v>
       </c>
-      <c r="B20" s="15" t="str">
+      <c r="B20" s="14" t="str">
         <f>IF(A20="","",IFERROR(VLOOKUP(A20,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Hayden Hagger</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="14">
         <f>IF(A20="","",IFERROR(VLOOKUP(A20,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>45</v>
       </c>
-      <c r="D20" s="15" t="str">
+      <c r="D20" s="14" t="str">
         <f>IF(A20="","",IFERROR(VLOOKUP(A20,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="14">
         <f>IF(A20="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A20,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F20" s="15">
+      <c r="F20" s="14">
         <f>IF(A20="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A20))</f>
         <v>0</v>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="14">
         <f>IF(A20="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A20))</f>
         <v>0</v>
       </c>
-      <c r="H20" s="15">
+      <c r="H20" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I20" s="15">
+      <c r="I20" s="14">
         <f>IF(A20="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A20))</f>
         <v>0</v>
       </c>
-      <c r="J20" s="15">
+      <c r="J20" s="14">
         <f>IF(A20="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A20))</f>
         <v>0</v>
       </c>
       <c r="K20" s="13"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="15" t="str">
+      <c r="A21" s="14" t="str">
         <f>IF(Players!A21="","",Players!A21)</f>
         <v>P018</v>
       </c>
-      <c r="B21" s="15" t="str">
+      <c r="B21" s="14" t="str">
         <f>IF(A21="","",IFERROR(VLOOKUP(A21,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Sam Purcell</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="14">
         <f>IF(A21="","",IFERROR(VLOOKUP(A21,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>64</v>
       </c>
-      <c r="D21" s="15" t="str">
+      <c r="D21" s="14" t="str">
         <f>IF(A21="","",IFERROR(VLOOKUP(A21,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="14">
         <f>IF(A21="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A21,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="14">
         <f>IF(A21="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A21))</f>
         <v>0</v>
       </c>
-      <c r="G21" s="15">
+      <c r="G21" s="14">
         <f>IF(A21="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A21))</f>
         <v>0</v>
       </c>
-      <c r="H21" s="15">
+      <c r="H21" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I21" s="15">
+      <c r="I21" s="14">
         <f>IF(A21="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A21))</f>
         <v>0</v>
       </c>
-      <c r="J21" s="15">
+      <c r="J21" s="14">
         <f>IF(A21="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A21))</f>
         <v>0</v>
       </c>
       <c r="K21" s="13"/>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="15" t="str">
+      <c r="A22" s="14" t="str">
         <f>IF(Players!A22="","",Players!A22)</f>
         <v>P019</v>
       </c>
-      <c r="B22" s="15" t="str">
+      <c r="B22" s="14" t="str">
         <f>IF(A22="","",IFERROR(VLOOKUP(A22,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Samuel Rickard</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="14">
         <f>IF(A22="","",IFERROR(VLOOKUP(A22,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>65</v>
       </c>
-      <c r="D22" s="15" t="str">
+      <c r="D22" s="14" t="str">
         <f>IF(A22="","",IFERROR(VLOOKUP(A22,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="14">
         <f>IF(A22="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A22,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="14">
         <f>IF(A22="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A22))</f>
         <v>0</v>
       </c>
-      <c r="G22" s="15">
+      <c r="G22" s="14">
         <f>IF(A22="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A22))</f>
         <v>0</v>
       </c>
-      <c r="H22" s="15">
+      <c r="H22" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I22" s="15">
+      <c r="I22" s="14">
         <f>IF(A22="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A22))</f>
         <v>0</v>
       </c>
-      <c r="J22" s="15">
+      <c r="J22" s="14">
         <f>IF(A22="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A22))</f>
         <v>0</v>
       </c>
       <c r="K22" s="13"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="15" t="str">
+      <c r="A23" s="14" t="str">
         <f>IF(Players!A23="","",Players!A23)</f>
         <v>P020</v>
       </c>
-      <c r="B23" s="15" t="str">
+      <c r="B23" s="14" t="str">
         <f>IF(A23="","",IFERROR(VLOOKUP(A23,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Oscar Lee</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="14">
         <f>IF(A23="","",IFERROR(VLOOKUP(A23,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>68</v>
       </c>
-      <c r="D23" s="15" t="str">
+      <c r="D23" s="14" t="str">
         <f>IF(A23="","",IFERROR(VLOOKUP(A23,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="14">
         <f>IF(A23="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A23,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F23" s="15">
+      <c r="F23" s="14">
         <f>IF(A23="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A23))</f>
         <v>0</v>
       </c>
-      <c r="G23" s="15">
+      <c r="G23" s="14">
         <f>IF(A23="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A23))</f>
         <v>0</v>
       </c>
-      <c r="H23" s="15">
+      <c r="H23" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I23" s="15">
+      <c r="I23" s="14">
         <f>IF(A23="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A23))</f>
         <v>0</v>
       </c>
-      <c r="J23" s="15">
+      <c r="J23" s="14">
         <f>IF(A23="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A23))</f>
         <v>0</v>
       </c>
       <c r="K23" s="13"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="15" t="str">
+      <c r="A24" s="14" t="str">
         <f>IF(Players!A24="","",Players!A24)</f>
         <v>P021</v>
       </c>
-      <c r="B24" s="15" t="str">
+      <c r="B24" s="14" t="str">
         <f>IF(A24="","",IFERROR(VLOOKUP(A24,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Jacob Maidment</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="14">
         <f>IF(A24="","",IFERROR(VLOOKUP(A24,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>89</v>
       </c>
-      <c r="D24" s="15" t="str">
+      <c r="D24" s="14" t="str">
         <f>IF(A24="","",IFERROR(VLOOKUP(A24,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="14">
         <f>IF(A24="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A24,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F24" s="15">
+      <c r="F24" s="14">
         <f>IF(A24="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A24))</f>
         <v>0</v>
       </c>
-      <c r="G24" s="15">
+      <c r="G24" s="14">
         <f>IF(A24="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A24))</f>
         <v>0</v>
       </c>
-      <c r="H24" s="15">
+      <c r="H24" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I24" s="15">
+      <c r="I24" s="14">
         <f>IF(A24="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A24))</f>
         <v>0</v>
       </c>
-      <c r="J24" s="15">
+      <c r="J24" s="14">
         <f>IF(A24="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A24))</f>
         <v>0</v>
       </c>
       <c r="K24" s="13"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="15" t="str">
+      <c r="A25" s="14" t="str">
         <f>IF(Players!A25="","",Players!A25)</f>
         <v>P022</v>
       </c>
-      <c r="B25" s="15" t="str">
+      <c r="B25" s="14" t="str">
         <f>IF(A25="","",IFERROR(VLOOKUP(A25,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Corey Taylor</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="14">
         <f>IF(A25="","",IFERROR(VLOOKUP(A25,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>16</v>
       </c>
-      <c r="D25" s="15" t="str">
+      <c r="D25" s="14" t="str">
         <f>IF(A25="","",IFERROR(VLOOKUP(A25,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E25" s="15">
+      <c r="E25" s="14">
         <f>IF(A25="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A25,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F25" s="15">
+      <c r="F25" s="14">
         <f>IF(A25="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A25))</f>
         <v>0</v>
       </c>
-      <c r="G25" s="15">
+      <c r="G25" s="14">
         <f>IF(A25="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A25))</f>
         <v>0</v>
       </c>
-      <c r="H25" s="15">
+      <c r="H25" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I25" s="15">
+      <c r="I25" s="14">
         <f>IF(A25="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A25))</f>
         <v>0</v>
       </c>
-      <c r="J25" s="15">
+      <c r="J25" s="14">
         <f>IF(A25="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A25))</f>
         <v>0</v>
       </c>
       <c r="K25" s="13"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="15" t="str">
+      <c r="A26" s="14" t="str">
         <f>IF(Players!A26="","",Players!A26)</f>
         <v>P023</v>
       </c>
-      <c r="B26" s="15" t="str">
+      <c r="B26" s="14" t="str">
         <f>IF(A26="","",IFERROR(VLOOKUP(A26,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>James Bryan</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="14">
         <f>IF(A26="","",IFERROR(VLOOKUP(A26,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>23</v>
       </c>
-      <c r="D26" s="15" t="str">
+      <c r="D26" s="14" t="str">
         <f>IF(A26="","",IFERROR(VLOOKUP(A26,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E26" s="15">
+      <c r="E26" s="14">
         <f>IF(A26="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A26,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F26" s="15">
+      <c r="F26" s="14">
         <f>IF(A26="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A26))</f>
         <v>0</v>
       </c>
-      <c r="G26" s="15">
+      <c r="G26" s="14">
         <f>IF(A26="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A26))</f>
         <v>0</v>
       </c>
-      <c r="H26" s="15">
+      <c r="H26" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I26" s="15">
+      <c r="I26" s="14">
         <f>IF(A26="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A26))</f>
         <v>0</v>
       </c>
-      <c r="J26" s="15">
+      <c r="J26" s="14">
         <f>IF(A26="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A26))</f>
         <v>0</v>
       </c>
       <c r="K26" s="13"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="15" t="str">
+      <c r="A27" s="14" t="str">
         <f>IF(Players!A27="","",Players!A27)</f>
         <v>P024</v>
       </c>
-      <c r="B27" s="15" t="str">
+      <c r="B27" s="14" t="str">
         <f>IF(A27="","",IFERROR(VLOOKUP(A27,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Josh Furnell</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="14">
         <f>IF(A27="","",IFERROR(VLOOKUP(A27,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>33</v>
       </c>
-      <c r="D27" s="15" t="str">
+      <c r="D27" s="14" t="str">
         <f>IF(A27="","",IFERROR(VLOOKUP(A27,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="14">
         <f>IF(A27="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A27,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F27" s="15">
+      <c r="F27" s="14">
         <f>IF(A27="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A27))</f>
         <v>0</v>
       </c>
-      <c r="G27" s="15">
+      <c r="G27" s="14">
         <f>IF(A27="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A27))</f>
         <v>0</v>
       </c>
-      <c r="H27" s="15">
+      <c r="H27" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="14">
         <f>IF(A27="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A27))</f>
         <v>0</v>
       </c>
-      <c r="J27" s="15">
+      <c r="J27" s="14">
         <f>IF(A27="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A27))</f>
         <v>0</v>
       </c>
       <c r="K27" s="13"/>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="15" t="str">
+      <c r="A28" s="14" t="str">
         <f>IF(Players!A28="","",Players!A28)</f>
         <v>P025</v>
       </c>
-      <c r="B28" s="15" t="str">
+      <c r="B28" s="14" t="str">
         <f>IF(A28="","",IFERROR(VLOOKUP(A28,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Josh Hickman</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="14">
         <f>IF(A28="","",IFERROR(VLOOKUP(A28,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>40</v>
       </c>
-      <c r="D28" s="15" t="str">
+      <c r="D28" s="14" t="str">
         <f>IF(A28="","",IFERROR(VLOOKUP(A28,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E28" s="15">
+      <c r="E28" s="14">
         <f>IF(A28="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A28,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F28" s="15">
+      <c r="F28" s="14">
         <f>IF(A28="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A28))</f>
         <v>0</v>
       </c>
-      <c r="G28" s="15">
+      <c r="G28" s="14">
         <f>IF(A28="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A28))</f>
         <v>0</v>
       </c>
-      <c r="H28" s="15">
+      <c r="H28" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I28" s="15">
+      <c r="I28" s="14">
         <f>IF(A28="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A28))</f>
         <v>0</v>
       </c>
-      <c r="J28" s="15">
+      <c r="J28" s="14">
         <f>IF(A28="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A28))</f>
         <v>0</v>
       </c>
       <c r="K28" s="13"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="15" t="str">
+      <c r="A29" s="14" t="str">
         <f>IF(Players!A29="","",Players!A29)</f>
         <v>P026</v>
       </c>
-      <c r="B29" s="15" t="str">
+      <c r="B29" s="14" t="str">
         <f>IF(A29="","",IFERROR(VLOOKUP(A29,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Ryan Wonfor</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="14">
         <f>IF(A29="","",IFERROR(VLOOKUP(A29,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>77</v>
       </c>
-      <c r="D29" s="15" t="str">
+      <c r="D29" s="14" t="str">
         <f>IF(A29="","",IFERROR(VLOOKUP(A29,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E29" s="15">
+      <c r="E29" s="14">
         <f>IF(A29="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A29,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F29" s="15">
+      <c r="F29" s="14">
         <f>IF(A29="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A29))</f>
         <v>0</v>
       </c>
-      <c r="G29" s="15">
+      <c r="G29" s="14">
         <f>IF(A29="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A29))</f>
         <v>0</v>
       </c>
-      <c r="H29" s="15">
+      <c r="H29" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I29" s="15">
+      <c r="I29" s="14">
         <f>IF(A29="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A29))</f>
         <v>0</v>
       </c>
-      <c r="J29" s="15">
+      <c r="J29" s="14">
         <f>IF(A29="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A29))</f>
         <v>0</v>
       </c>
       <c r="K29" s="13"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="15" t="str">
+      <c r="A30" s="14" t="str">
         <f>IF(Players!A30="","",Players!A30)</f>
         <v>P027</v>
       </c>
-      <c r="B30" s="15" t="str">
+      <c r="B30" s="14" t="str">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Charles Coney</v>
       </c>
-      <c r="C30" s="15">
+      <c r="C30" s="14">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>88</v>
       </c>
-      <c r="D30" s="15" t="str">
+      <c r="D30" s="14" t="str">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E30" s="15">
+      <c r="E30" s="14">
         <f>IF(A30="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A30,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F30" s="15">
+      <c r="F30" s="14">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
-      <c r="G30" s="15">
+      <c r="G30" s="14">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
-      <c r="H30" s="15">
+      <c r="H30" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I30" s="15">
+      <c r="I30" s="14">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
-      <c r="J30" s="15">
+      <c r="J30" s="14">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
@@ -25301,85 +25346,85 @@
     <row r="31" spans="1:11">
       <c r="A31" s="13" t="str">
         <f>IF(Players!A31="","",Players!A31)</f>
-        <v/>
+        <v>P028</v>
       </c>
       <c r="B31" s="13" t="str">
         <f>IF(A31="","",IFERROR(VLOOKUP(A31,Players!$A$4:$D$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="C31" s="13" t="str">
+        <v>Will Nowik</v>
+      </c>
+      <c r="C31" s="13">
         <f>IF(A31="","",IFERROR(VLOOKUP(A31,Players!$A$4:$D$200,3,FALSE),""))</f>
-        <v/>
+        <v>98</v>
       </c>
       <c r="D31" s="13" t="str">
         <f>IF(A31="","",IFERROR(VLOOKUP(A31,Players!$A$4:$D$200,4,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="E31" s="13" t="str">
+        <v>Forward</v>
+      </c>
+      <c r="E31" s="13">
         <f>IF(A31="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A31,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v/>
-      </c>
-      <c r="F31" s="13" t="str">
+        <v>0</v>
+      </c>
+      <c r="F31" s="13">
         <f>IF(A31="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A31))</f>
-        <v/>
-      </c>
-      <c r="G31" s="13" t="str">
+        <v>0</v>
+      </c>
+      <c r="G31" s="13">
         <f>IF(A31="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A31))</f>
-        <v/>
-      </c>
-      <c r="H31" s="13" t="str">
+        <v>0</v>
+      </c>
+      <c r="H31" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I31" s="13" t="str">
+        <v>0</v>
+      </c>
+      <c r="I31" s="13">
         <f>IF(A31="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A31))</f>
-        <v/>
-      </c>
-      <c r="J31" s="13" t="str">
+        <v>0</v>
+      </c>
+      <c r="J31" s="13">
         <f>IF(A31="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A31))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="str">
         <f>IF(Players!A32="","",Players!A32)</f>
-        <v/>
+        <v>P029</v>
       </c>
       <c r="B32" t="str">
         <f>IF(A32="","",IFERROR(VLOOKUP(A32,Players!$A$4:$D$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="C32" t="str">
+        <v>James Moeller</v>
+      </c>
+      <c r="C32">
         <f>IF(A32="","",IFERROR(VLOOKUP(A32,Players!$A$4:$D$200,3,FALSE),""))</f>
-        <v/>
+        <v>81</v>
       </c>
       <c r="D32" t="str">
         <f>IF(A32="","",IFERROR(VLOOKUP(A32,Players!$A$4:$D$200,4,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="E32" t="str">
+        <v>Defence</v>
+      </c>
+      <c r="E32">
         <f>IF(A32="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A32,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v/>
-      </c>
-      <c r="F32" t="str">
+        <v>0</v>
+      </c>
+      <c r="F32">
         <f>IF(A32="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A32))</f>
-        <v/>
-      </c>
-      <c r="G32" t="str">
+        <v>0</v>
+      </c>
+      <c r="G32">
         <f>IF(A32="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A32))</f>
-        <v/>
-      </c>
-      <c r="H32" t="str">
+        <v>0</v>
+      </c>
+      <c r="H32">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I32" t="str">
+        <v>0</v>
+      </c>
+      <c r="I32">
         <f>IF(A32="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A32))</f>
-        <v/>
-      </c>
-      <c r="J32" t="str">
+        <v>0</v>
+      </c>
+      <c r="J32">
         <f>IF(A32="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A32))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9ECC8503-CA9E-41BF-9B61-3F0FCDBC0171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{382BA49A-7D28-4A59-9A25-906A775C1DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="8" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="296">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -667,6 +667,15 @@
     <t>moeller.png</t>
   </si>
   <si>
+    <t>P030</t>
+  </si>
+  <si>
+    <t>Cass  McCormack</t>
+  </si>
+  <si>
+    <t>McCormack</t>
+  </si>
+  <si>
     <t>Game ID</t>
   </si>
   <si>
@@ -824,6 +833,9 @@
   </si>
   <si>
     <t>+/-</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
   <si>
     <t>Netminder Game Stats</t>
@@ -976,7 +988,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1034,11 +1046,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1062,11 +1087,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="46" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1288,14 +1316,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.25">
-      <c r="A1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
+      <c r="A1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
     </row>
     <row r="3" spans="1:6" ht="30">
       <c r="A3" s="1" t="s">
@@ -1396,15 +1424,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
       <c r="H1" s="16"/>
     </row>
     <row r="3" spans="1:8" ht="15">
@@ -3646,15 +3674,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="3" spans="1:7" ht="30">
       <c r="A3" s="6" t="s">
@@ -4247,67 +4275,80 @@
       <c r="G30" s="7"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="19" t="s">
+      <c r="A31" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="B31" s="19" t="s">
+      <c r="B31" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="C31" s="19">
+      <c r="C31" s="18">
         <v>98</v>
       </c>
-      <c r="D31" s="19" t="s">
+      <c r="D31" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="E31" s="19" t="s">
+      <c r="E31" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="F31" s="19" t="s">
+      <c r="F31" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="G31" s="19"/>
+      <c r="G31" s="18"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="18" t="s">
+      <c r="A32" s="20" t="s">
         <v>204</v>
       </c>
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="C32" s="18">
+      <c r="C32" s="20">
         <v>81</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="D32" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="E32" s="18" t="s">
+      <c r="E32" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="F32" s="18" t="s">
+      <c r="F32" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="G32" s="18"/>
+      <c r="G32" s="20"/>
       <c r="H32" s="13"/>
     </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-    </row>
-    <row r="34" spans="1:7">
+    <row r="33" spans="1:8">
+      <c r="A33" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="C33" s="17">
+        <v>0</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="13"/>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
+      <c r="B34" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:8">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -4316,7 +4357,7 @@
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:8">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -4325,7 +4366,7 @@
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:8">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -4334,7 +4375,7 @@
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:8">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -4343,7 +4384,7 @@
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:8">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -4352,7 +4393,7 @@
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:8">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -4361,7 +4402,7 @@
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:8">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -4370,7 +4411,7 @@
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:8">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -4379,7 +4420,7 @@
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:8">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -4388,7 +4429,7 @@
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:8">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -4397,7 +4438,7 @@
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:8">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -4406,7 +4447,7 @@
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:8">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -4415,7 +4456,7 @@
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:8">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -4424,7 +4465,7 @@
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:8">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -5838,59 +5879,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13"/>
     <row r="3" spans="1:13" ht="30">
       <c r="A3" s="6" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="M3" s="6" t="s">
         <v>116</v>
@@ -5898,7 +5939,7 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="7" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B4" s="8">
         <v>46264</v>
@@ -5910,29 +5951,33 @@
         <v>37</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
+        <v>224</v>
+      </c>
+      <c r="G4" s="7">
+        <v>12</v>
+      </c>
+      <c r="H4" s="7">
+        <v>2</v>
+      </c>
       <c r="I4" s="10" t="str">
         <f t="shared" ref="I4:I35" si="0">IF(OR(G4="",H4=""),"",IF(G4&gt;H4,"W",IF(G4&lt;H4,"L","T")))</f>
-        <v/>
+        <v>W</v>
       </c>
       <c r="J4" s="7"/>
       <c r="K4" s="7" t="s">
         <v>41</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M4" s="7"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="7" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B5" s="8">
         <v>46270</v>
@@ -5944,10 +5989,10 @@
         <v>42</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
@@ -5960,13 +6005,13 @@
         <v>46</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M5" s="7"/>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="7" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B6" s="8">
         <v>46278</v>
@@ -5978,10 +6023,10 @@
         <v>47</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
@@ -5991,16 +6036,16 @@
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M6" s="7"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="7" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B7" s="8">
         <v>46284</v>
@@ -6012,10 +6057,10 @@
         <v>52</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
@@ -6025,13 +6070,13 @@
         <v>56</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M7" s="7"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="7" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B8" s="8">
         <v>46285</v>
@@ -6043,10 +6088,10 @@
         <v>58</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
@@ -6056,16 +6101,16 @@
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M8" s="7"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="7" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B9" s="8">
         <v>46291</v>
@@ -6077,10 +6122,10 @@
         <v>74</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
@@ -6093,13 +6138,13 @@
         <v>78</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M9" s="7"/>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="7" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B10" s="8">
         <v>46298</v>
@@ -6111,10 +6156,10 @@
         <v>101</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
@@ -6124,16 +6169,16 @@
       </c>
       <c r="J10" s="7"/>
       <c r="K10" s="7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M10" s="7"/>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B11" s="8">
         <v>46306</v>
@@ -6145,10 +6190,10 @@
         <v>106</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
@@ -6158,16 +6203,16 @@
       </c>
       <c r="J11" s="7"/>
       <c r="K11" s="7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M11" s="7"/>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="7" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B12" s="8">
         <v>46312</v>
@@ -6179,10 +6224,10 @@
         <v>101</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
@@ -6195,13 +6240,13 @@
         <v>105</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M12" s="7"/>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="7" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B13" s="8">
         <v>46320</v>
@@ -6213,10 +6258,10 @@
         <v>95</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
@@ -6226,16 +6271,16 @@
       </c>
       <c r="J13" s="7"/>
       <c r="K13" s="7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M13" s="7"/>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="7" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B14" s="8">
         <v>46327</v>
@@ -6247,10 +6292,10 @@
         <v>47</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
@@ -6263,13 +6308,13 @@
         <v>51</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M14" s="7"/>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="7" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B15" s="8">
         <v>46334</v>
@@ -6281,10 +6326,10 @@
         <v>52</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
@@ -6294,16 +6339,16 @@
       </c>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M15" s="7"/>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="7" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B16" s="8">
         <v>46340</v>
@@ -6315,10 +6360,10 @@
         <v>74</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
@@ -6328,16 +6373,16 @@
       </c>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M16" s="7"/>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="7" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B17" s="8">
         <v>46341</v>
@@ -6349,10 +6394,10 @@
         <v>95</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -6365,13 +6410,13 @@
         <v>99</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M17" s="7"/>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="7" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B18" s="8">
         <v>46354</v>
@@ -6383,10 +6428,10 @@
         <v>85</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
@@ -6399,13 +6444,13 @@
         <v>89</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M18" s="7"/>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="7" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B19" s="8">
         <v>46355</v>
@@ -6417,10 +6462,10 @@
         <v>58</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
@@ -6433,13 +6478,13 @@
         <v>62</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M19" s="7"/>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="7" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B20" s="8">
         <v>46368</v>
@@ -6451,10 +6496,10 @@
         <v>63</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
@@ -6467,13 +6512,13 @@
         <v>67</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M20" s="7"/>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="7" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B21" s="8">
         <v>46369</v>
@@ -6485,10 +6530,10 @@
         <v>68</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
@@ -6498,16 +6543,16 @@
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M21" s="7"/>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="7" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B22" s="8">
         <v>46376</v>
@@ -6519,10 +6564,10 @@
         <v>85</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
@@ -6532,16 +6577,16 @@
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M22" s="7"/>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="7" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B23" s="8">
         <v>46397</v>
@@ -6553,10 +6598,10 @@
         <v>80</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
@@ -6566,16 +6611,16 @@
       </c>
       <c r="J23" s="7"/>
       <c r="K23" s="7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M23" s="7"/>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="7" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B24" s="8">
         <v>46417</v>
@@ -6587,10 +6632,10 @@
         <v>90</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
@@ -6600,16 +6645,16 @@
       </c>
       <c r="J24" s="7"/>
       <c r="K24" s="7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M24" s="7"/>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="7" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B25" s="8">
         <v>46425</v>
@@ -6621,10 +6666,10 @@
         <v>63</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
@@ -6634,16 +6679,16 @@
       </c>
       <c r="J25" s="7"/>
       <c r="K25" s="7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M25" s="7"/>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B26" s="8">
         <v>46446</v>
@@ -6655,10 +6700,10 @@
         <v>80</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
@@ -6671,13 +6716,13 @@
         <v>84</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M26" s="7"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B27" s="8">
         <v>46452</v>
@@ -6689,10 +6734,10 @@
         <v>68</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G27" s="7"/>
       <c r="H27" s="7"/>
@@ -6705,13 +6750,13 @@
         <v>72</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M27" s="7"/>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="7" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B28" s="8">
         <v>46459</v>
@@ -6723,10 +6768,10 @@
         <v>106</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
@@ -6739,13 +6784,13 @@
         <v>110</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M28" s="7"/>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="7" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B29" s="8">
         <v>46467</v>
@@ -6757,10 +6802,10 @@
         <v>90</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
@@ -6773,7 +6818,7 @@
         <v>94</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M29" s="7"/>
     </row>
@@ -9889,114 +9934,166 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
-      <c r="A1" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
+      <c r="A1" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
     </row>
     <row r="3" spans="1:10" ht="30">
       <c r="A3" s="6" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>111</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="J3" s="6" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="7"/>
+      <c r="A4" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="E4" s="7">
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <v>0</v>
+      </c>
+      <c r="G4" s="10">
+        <v>0</v>
+      </c>
+      <c r="H4" s="7">
+        <v>0</v>
+      </c>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
+      <c r="A5" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>121</v>
+      </c>
       <c r="C5" s="10" t="str">
         <f>IF(B5="","",IFERROR(VLOOKUP(B5,Players!$A$4:$B$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="10" t="str">
+        <v>Marks Kanins</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="7">
+        <v>1</v>
+      </c>
+      <c r="F5" s="7">
+        <v>3</v>
+      </c>
+      <c r="G5" s="10">
         <f t="shared" ref="G5:G67" si="0">IF(AND(E5="",F5=""),"",SUM(E5:F5))</f>
-        <v/>
-      </c>
-      <c r="H5" s="7"/>
+        <v>4</v>
+      </c>
+      <c r="H5" s="7">
+        <v>0</v>
+      </c>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
+      <c r="A6" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>124</v>
+      </c>
       <c r="C6" s="10" t="str">
         <f>IF(B6="","",IFERROR(VLOOKUP(B6,Players!$A$4:$B$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="10" t="str">
+        <v>Dominic Wealthall</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="7">
+        <v>0</v>
+      </c>
+      <c r="F6" s="7">
+        <v>1</v>
+      </c>
+      <c r="G6" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H6" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="H6" s="7">
+        <v>7</v>
+      </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
+      <c r="A7" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>133</v>
+      </c>
       <c r="C7" s="10" t="str">
         <f>IF(B7="","",IFERROR(VLOOKUP(B7,Players!$A$4:$B$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="10" t="str">
+        <v>Charlie Russell</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="7">
+        <v>2</v>
+      </c>
+      <c r="F7" s="7">
+        <v>2</v>
+      </c>
+      <c r="G7" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H7" s="7"/>
+        <v>4</v>
+      </c>
+      <c r="H7" s="7">
+        <v>0</v>
+      </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
     </row>
@@ -18924,23 +19021,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20.25">
-      <c r="A1" s="17" t="s">
-        <v>260</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
+      <c r="A1" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="3" spans="1:11" ht="30">
       <c r="A3" s="6" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>111</v>
@@ -18949,44 +19046,56 @@
         <v>131</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="10" t="str">
+      <c r="A4" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="D4" s="22">
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="E4" s="7">
+        <v>23</v>
+      </c>
+      <c r="F4" s="7">
+        <v>2</v>
+      </c>
+      <c r="G4" s="10">
         <f t="shared" ref="G4:G35" si="0">IF(E4="","",E4-F4)</f>
-        <v/>
-      </c>
-      <c r="H4" s="11" t="str">
+        <v>21</v>
+      </c>
+      <c r="H4" s="11">
         <f t="shared" ref="H4:H35" si="1">IF(OR(E4="",E4=0),"",G4/E4)</f>
-        <v/>
+        <v>0.91304347826086951</v>
       </c>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
@@ -18994,21 +19103,29 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
+      <c r="B5" s="7" t="s">
+        <v>148</v>
+      </c>
       <c r="C5" s="10" t="str">
         <f>IF(B5="","",IFERROR(VLOOKUP(B5,Players!$A$4:$B$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="10" t="str">
+        <v>Nicole Jackson</v>
+      </c>
+      <c r="D5" s="9">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="E5" s="7">
+        <v>6</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0</v>
+      </c>
+      <c r="G5" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H5" s="11" t="str">
+        <v>6</v>
+      </c>
+      <c r="H5" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
@@ -23347,49 +23464,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
-      <c r="A1" s="17" t="s">
-        <v>268</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
+      <c r="A1" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
     </row>
     <row r="3" spans="1:10" ht="15">
       <c r="A3" s="6" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -23825,49 +23942,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
-      <c r="A1" s="17" t="s">
-        <v>279</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
+      <c r="A1" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
     </row>
     <row r="3" spans="1:10" ht="15">
       <c r="A3" s="6" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -24090,25 +24207,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
-      <c r="A1" s="17" t="s">
-        <v>280</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
+      <c r="A1" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15">
       <c r="L2" s="6" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="30">
@@ -24116,35 +24233,35 @@
         <v>111</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="K3" s="13"/>
       <c r="L3" s="12" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="M3" s="12">
         <f>COUNT(Games!$A$4:$A$200)</f>
@@ -24194,11 +24311,11 @@
       </c>
       <c r="K4" s="13"/>
       <c r="L4" s="12" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="M4" s="12">
         <f>SUM(Games!$G$4:$G$200)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -24220,19 +24337,19 @@
       </c>
       <c r="E5" s="12">
         <f>IF(A5="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A5,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="12">
         <f>IF(A5="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A5))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="12">
         <f>IF(A5="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A5))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I5" s="12">
         <f>IF(A5="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A5))</f>
@@ -24244,11 +24361,11 @@
       </c>
       <c r="K5" s="13"/>
       <c r="L5" s="12" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="M5" s="12">
         <f>SUM(Games!$H$4:$H$200)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -24270,7 +24387,7 @@
       </c>
       <c r="E6" s="12">
         <f>IF(A6="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A6,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="12">
         <f>IF(A6="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A6))</f>
@@ -24278,15 +24395,15 @@
       </c>
       <c r="G6" s="12">
         <f>IF(A6="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A6))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="12">
         <f>IF(A6="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A6))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J6" s="12">
         <f>IF(A6="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A6))</f>
@@ -24294,11 +24411,11 @@
       </c>
       <c r="K6" s="13"/>
       <c r="L6" s="12" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="M6" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"W")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -24344,7 +24461,7 @@
       </c>
       <c r="K7" s="13"/>
       <c r="L7" s="12" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="M7" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"L")</f>
@@ -24370,19 +24487,19 @@
       </c>
       <c r="E8" s="12">
         <f>IF(A8="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A8,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="12">
         <f>IF(A8="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A8))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="12">
         <f>IF(A8="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A8))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I8" s="12">
         <f>IF(A8="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A8))</f>
@@ -25301,217 +25418,220 @@
       <c r="K29" s="13"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="14" t="str">
+      <c r="A30" s="21" t="str">
         <f>IF(Players!A30="","",Players!A30)</f>
         <v>P027</v>
       </c>
-      <c r="B30" s="14" t="str">
+      <c r="B30" s="21" t="str">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Charles Coney</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="21">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>88</v>
       </c>
-      <c r="D30" s="14" t="str">
+      <c r="D30" s="21" t="str">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E30" s="14">
+      <c r="E30" s="21">
         <f>IF(A30="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A30,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="21">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
-      <c r="G30" s="14">
+      <c r="G30" s="21">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
-      <c r="H30" s="14">
+      <c r="H30" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I30" s="14">
+      <c r="I30" s="21">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
-      <c r="J30" s="14">
+      <c r="J30" s="21">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
       <c r="K30" s="13"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="13" t="str">
+      <c r="A31" s="14" t="str">
         <f>IF(Players!A31="","",Players!A31)</f>
         <v>P028</v>
       </c>
-      <c r="B31" s="13" t="str">
+      <c r="B31" s="14" t="str">
         <f>IF(A31="","",IFERROR(VLOOKUP(A31,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Will Nowik</v>
       </c>
-      <c r="C31" s="13">
+      <c r="C31" s="14">
         <f>IF(A31="","",IFERROR(VLOOKUP(A31,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>98</v>
       </c>
-      <c r="D31" s="13" t="str">
+      <c r="D31" s="14" t="str">
         <f>IF(A31="","",IFERROR(VLOOKUP(A31,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Forward</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="14">
         <f>IF(A31="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A31,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F31" s="13">
+      <c r="F31" s="14">
         <f>IF(A31="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A31))</f>
         <v>0</v>
       </c>
-      <c r="G31" s="13">
+      <c r="G31" s="14">
         <f>IF(A31="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A31))</f>
         <v>0</v>
       </c>
-      <c r="H31" s="13">
+      <c r="H31" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I31" s="13">
+      <c r="I31" s="14">
         <f>IF(A31="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A31))</f>
         <v>0</v>
       </c>
-      <c r="J31" s="13">
+      <c r="J31" s="14">
         <f>IF(A31="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A31))</f>
         <v>0</v>
       </c>
+      <c r="K31" s="13"/>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" t="str">
+      <c r="A32" s="14" t="str">
         <f>IF(Players!A32="","",Players!A32)</f>
         <v>P029</v>
       </c>
-      <c r="B32" t="str">
+      <c r="B32" s="14" t="str">
         <f>IF(A32="","",IFERROR(VLOOKUP(A32,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>James Moeller</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="14">
         <f>IF(A32="","",IFERROR(VLOOKUP(A32,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>81</v>
       </c>
-      <c r="D32" t="str">
+      <c r="D32" s="14" t="str">
         <f>IF(A32="","",IFERROR(VLOOKUP(A32,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="14">
         <f>IF(A32="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A32,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="14">
         <f>IF(A32="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A32))</f>
         <v>0</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="14">
         <f>IF(A32="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A32))</f>
         <v>0</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="14">
         <f>IF(A32="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A32))</f>
         <v>0</v>
       </c>
-      <c r="J32">
+      <c r="J32" s="14">
         <f>IF(A32="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A32))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" t="str">
+      <c r="K32" s="13"/>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="14" t="str">
         <f>IF(Players!A33="","",Players!A33)</f>
-        <v/>
-      </c>
-      <c r="B33" t="str">
+        <v>P030</v>
+      </c>
+      <c r="B33" s="14" t="str">
         <f>IF(A33="","",IFERROR(VLOOKUP(A33,Players!$A$4:$D$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="C33" t="str">
+        <v>Cass  McCormack</v>
+      </c>
+      <c r="C33" s="14">
         <f>IF(A33="","",IFERROR(VLOOKUP(A33,Players!$A$4:$D$200,3,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="D33" t="str">
+        <v>0</v>
+      </c>
+      <c r="D33" s="14" t="str">
         <f>IF(A33="","",IFERROR(VLOOKUP(A33,Players!$A$4:$D$200,4,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="E33" t="str">
+        <v>Forward</v>
+      </c>
+      <c r="E33" s="14">
         <f>IF(A33="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A33,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v/>
-      </c>
-      <c r="F33" t="str">
+        <v>0</v>
+      </c>
+      <c r="F33" s="14">
         <f>IF(A33="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A33))</f>
-        <v/>
-      </c>
-      <c r="G33" t="str">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
         <f>IF(A33="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A33))</f>
-        <v/>
-      </c>
-      <c r="H33" t="str">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I33" t="str">
+        <v>0</v>
+      </c>
+      <c r="I33" s="14">
         <f>IF(A33="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A33))</f>
-        <v/>
-      </c>
-      <c r="J33" t="str">
+        <v>0</v>
+      </c>
+      <c r="J33" s="14">
         <f>IF(A33="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A33))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" t="str">
+        <v>0</v>
+      </c>
+      <c r="K33" s="13"/>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="13" t="str">
         <f>IF(Players!A34="","",Players!A34)</f>
         <v/>
       </c>
-      <c r="B34" t="str">
+      <c r="B34" s="13" t="str">
         <f>IF(A34="","",IFERROR(VLOOKUP(A34,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="C34" t="str">
+      <c r="C34" s="13" t="str">
         <f>IF(A34="","",IFERROR(VLOOKUP(A34,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D34" t="str">
+      <c r="D34" s="13" t="str">
         <f>IF(A34="","",IFERROR(VLOOKUP(A34,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E34" t="str">
+      <c r="E34" s="13" t="str">
         <f>IF(A34="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A34,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v/>
       </c>
-      <c r="F34" t="str">
+      <c r="F34" s="13" t="str">
         <f>IF(A34="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A34))</f>
         <v/>
       </c>
-      <c r="G34" t="str">
+      <c r="G34" s="13" t="str">
         <f>IF(A34="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A34))</f>
         <v/>
       </c>
-      <c r="H34" t="str">
+      <c r="H34" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I34" t="str">
+      <c r="I34" s="13" t="str">
         <f>IF(A34="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A34))</f>
         <v/>
       </c>
-      <c r="J34" t="str">
+      <c r="J34" s="13" t="str">
         <f>IF(A34="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A34))</f>
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:11">
       <c r="A35" t="str">
         <f>IF(Players!A35="","",Players!A35)</f>
         <v/>
@@ -25553,7 +25673,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:11">
       <c r="A36" t="str">
         <f>IF(Players!A36="","",Players!A36)</f>
         <v/>
@@ -25595,7 +25715,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:11">
       <c r="A37" t="str">
         <f>IF(Players!A37="","",Players!A37)</f>
         <v/>
@@ -25637,7 +25757,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:11">
       <c r="A38" t="str">
         <f>IF(Players!A38="","",Players!A38)</f>
         <v/>
@@ -25679,7 +25799,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:11">
       <c r="A39" t="str">
         <f>IF(Players!A39="","",Players!A39)</f>
         <v/>
@@ -25721,7 +25841,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:11">
       <c r="A40" t="str">
         <f>IF(Players!A40="","",Players!A40)</f>
         <v/>
@@ -25763,7 +25883,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:11">
       <c r="A41" t="str">
         <f>IF(Players!A41="","",Players!A41)</f>
         <v/>
@@ -25805,7 +25925,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:11">
       <c r="A42" t="str">
         <f>IF(Players!A42="","",Players!A42)</f>
         <v/>
@@ -25847,7 +25967,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:11">
       <c r="A43" t="str">
         <f>IF(Players!A43="","",Players!A43)</f>
         <v/>
@@ -25889,7 +26009,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:11">
       <c r="A44" t="str">
         <f>IF(Players!A44="","",Players!A44)</f>
         <v/>
@@ -25931,7 +26051,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:11">
       <c r="A45" t="str">
         <f>IF(Players!A45="","",Players!A45)</f>
         <v/>
@@ -25973,7 +26093,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:11">
       <c r="A46" t="str">
         <f>IF(Players!A46="","",Players!A46)</f>
         <v/>
@@ -26015,7 +26135,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:11">
       <c r="A47" t="str">
         <f>IF(Players!A47="","",Players!A47)</f>
         <v/>
@@ -26057,7 +26177,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:11">
       <c r="A48" t="str">
         <f>IF(Players!A48="","",Players!A48)</f>
         <v/>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{382BA49A-7D28-4A59-9A25-906A775C1DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{56F4593D-DBCB-42AD-82DD-F78177B6CD08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="296">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -9986,8 +9986,9 @@
       <c r="B4" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>118</v>
+      <c r="C4" s="10" t="str">
+        <f>IF(B5="","",IFERROR(VLOOKUP(B4,Players!$A$4:$B$200,2,FALSE),""))</f>
+        <v>Sam Peters</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>263</v>
@@ -9999,6 +10000,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="10">
+        <f>IF(AND(E4="",E4=""),"",SUM(E4:F4))</f>
         <v>0</v>
       </c>
       <c r="H4" s="7">
@@ -10028,7 +10030,7 @@
         <v>3</v>
       </c>
       <c r="G5" s="10">
-        <f t="shared" ref="G5:G67" si="0">IF(AND(E5="",F5=""),"",SUM(E5:F5))</f>
+        <f>IF(AND(E5="",F5=""),"",SUM(E5:F5))</f>
         <v>4</v>
       </c>
       <c r="H5" s="7">
@@ -10058,7 +10060,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="G5:G67" si="0">IF(AND(E6="",F6=""),"",SUM(E6:F6))</f>
         <v>1</v>
       </c>
       <c r="H6" s="7">
@@ -19075,10 +19077,11 @@
         <v>222</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
+      </c>
+      <c r="C4" s="10" t="str">
+        <f>IF(B4="","",IFERROR(VLOOKUP(B4,Players!$A$4:$B$200,2,FALSE),""))</f>
+        <v>Aaron Burton</v>
       </c>
       <c r="D4" s="22">
         <v>1.6666666666666667</v>
